--- a/src/bonn_thesis/data/raw/ISCO-08 EN Structure and definitions.xlsx
+++ b/src/bonn_thesis/data/raw/ISCO-08 EN Structure and definitions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11116"/>
   <workbookPr backupFile="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willbackes/Documents/candidate-select/experience-scoring-ideas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willbackes/Documents/code/bonn_thesis/src/bonn_thesis/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{6D9F8EBA-27AF-A647-80EA-CBB226383976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{ADC6377B-6707-BB42-89EA-D26EE915AF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30240" yWindow="-7500" windowWidth="22280" windowHeight="19340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,9 +22,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Badre, Lara - Personal View" guid="{61C7386F-07EB-4198-B2FD-4D1A7B0F335F}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1382" windowHeight="744" activeSheetId="1"/>
+    <customWorkbookView name="Kalinga, Agnes - Personal View" guid="{B0EC71A6-F8E8-4D42-9918-972E5566A443}" mergeInterval="0" personalView="1" xWindow="6" yWindow="20" windowWidth="1714" windowHeight="995" activeSheetId="1"/>
     <customWorkbookView name="William Backes - Personal View" guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" mergeInterval="0" personalView="1" xWindow="1512" yWindow="-375" windowWidth="1114" windowHeight="967" activeSheetId="1"/>
-    <customWorkbookView name="Kalinga, Agnes - Personal View" guid="{B0EC71A6-F8E8-4D42-9918-972E5566A443}" mergeInterval="0" personalView="1" xWindow="6" yWindow="20" windowWidth="1714" windowHeight="995" activeSheetId="1"/>
-    <customWorkbookView name="Badre, Lara - Personal View" guid="{61C7386F-07EB-4198-B2FD-4D1A7B0F335F}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1382" windowHeight="744" activeSheetId="1"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -11663,9 +11663,6 @@
   </si>
   <si>
     <t>Only operators of small shops for whom the management and supervision of staff is not a significant component of the work are classified in Unit Group 5221: Shopkeepers. Operators of shops where management tasks and supervision of staff are significant and frequent elements of the work are classified in Unit Group 1420: Retail and Wholesale Trade Managers. Staff who control and direct the activities of shop sales assistants, checkout operators and other workers, but who do not take responsibility for determining product mix, overall setting of prices, budgets and staffing levels, selection and recruitment are classified in Unit Group 5222: Shop Supervisors.</t>
-  </si>
-  <si>
-    <t>Shop Aalespersons</t>
   </si>
   <si>
     <t>Shop Supervisors</t>
@@ -17125,6 +17122,9 @@
   <si>
     <t>Occupations in this sub-major group are classified into the following minor group:
 0310  Armed Forces Occupations, Other Ranks</t>
+  </si>
+  <si>
+    <t>Shop Salespersons</t>
   </si>
 </sst>
 </file>
@@ -17365,8 +17365,14 @@
 </file>
 
 <file path=xl/revisions/revisionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
-<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{F8BADF6E-2CEC-0149-8604-9EC9585B97B3}" diskRevisions="1" revisionId="2591" version="8">
+<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{C19FE2B2-46D6-EF48-BA92-7305958441E5}" diskRevisions="1" revisionId="2592" version="9">
   <header guid="{F8BADF6E-2CEC-0149-8604-9EC9585B97B3}" dateTime="2025-10-24T06:27:12" maxSheetId="3" userName="William Backes" r:id="rId545">
+    <sheetIdMap count="2">
+      <sheetId val="1"/>
+      <sheetId val="2"/>
+    </sheetIdMap>
+  </header>
+  <header guid="{C19FE2B2-46D6-EF48-BA92-7305958441E5}" dateTime="2025-12-03T05:53:33" maxSheetId="3" userName="William Backes" r:id="rId546" minRId="2592">
     <sheetIdMap count="2">
       <sheetId val="1"/>
       <sheetId val="2"/>
@@ -17383,6 +17389,23 @@
     <oldFormula>'ISCO-08 EN Struct and defin'!$A$1:$H$620</oldFormula>
   </rdn>
   <rcv guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" action="add"/>
+</revisions>
+</file>
+
+<file path=xl/revisions/revisionLog2.xml><?xml version="1.0" encoding="utf-8"?>
+<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <rcc rId="2592" sId="1">
+    <oc r="C356" t="inlineStr">
+      <is>
+        <t>Shop Aalespersons</t>
+      </is>
+    </oc>
+    <nc r="C356" t="inlineStr">
+      <is>
+        <t>Shop Salespersons</t>
+      </is>
+    </nc>
+  </rcc>
 </revisions>
 </file>
 
@@ -17735,13 +17758,13 @@
         <v>1644</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>2915</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>2916</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>2917</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="28.5" customHeight="1">
@@ -17758,10 +17781,10 @@
         <v>1368</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>8</v>
@@ -17787,7 +17810,7 @@
         <v>1676</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>8</v>
@@ -17813,7 +17836,7 @@
         <v>1373</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>8</v>
@@ -17839,13 +17862,13 @@
         <v>1677</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="70.5" customHeight="1">
@@ -17862,7 +17885,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>32</v>
@@ -17888,7 +17911,7 @@
         <v>34</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>35</v>
@@ -17940,16 +17963,16 @@
         <v>1377</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>3263</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>3264</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>3265</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>3266</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="61.5" customHeight="1">
@@ -17975,7 +17998,7 @@
         <v>8</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="40" customHeight="1">
@@ -17992,10 +18015,10 @@
         <v>1380</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>3268</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>3269</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>3270</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -18044,10 +18067,10 @@
         <v>48</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>3270</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>3271</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>3272</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -18096,10 +18119,10 @@
         <v>1386</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>3272</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>3273</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>3274</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>8</v>
@@ -18125,7 +18148,7 @@
         <v>54</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>8</v>
@@ -18151,7 +18174,7 @@
         <v>1678</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>8</v>
@@ -18174,10 +18197,10 @@
         <v>58</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>3276</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>3277</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>3278</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>8</v>
@@ -18200,10 +18223,10 @@
         <v>60</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>3278</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>3279</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>3280</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>8</v>
@@ -18235,7 +18258,7 @@
         <v>8</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="40" customHeight="1">
@@ -18252,7 +18275,7 @@
         <v>1396</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>1397</v>
@@ -18278,10 +18301,10 @@
         <v>1399</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>3282</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>3283</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>3284</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>8</v>
@@ -18304,13 +18327,13 @@
         <v>1401</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>3284</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>3285</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="4" t="s">
         <v>3286</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>3287</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>8</v>
@@ -18333,7 +18356,7 @@
         <v>69</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>8</v>
@@ -18356,13 +18379,13 @@
         <v>1404</v>
       </c>
       <c r="E26" s="4" t="s">
+        <v>3288</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>3289</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>3290</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>3291</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>8</v>
@@ -18382,10 +18405,10 @@
         <v>1406</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>3291</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>3292</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>3293</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>72</v>
@@ -18411,10 +18434,10 @@
         <v>1647</v>
       </c>
       <c r="F28" s="4" t="s">
+        <v>3293</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>3294</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>3295</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>8</v>
@@ -18437,13 +18460,13 @@
         <v>1409</v>
       </c>
       <c r="F29" s="4" t="s">
+        <v>3295</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>3296</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>3297</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="40" customHeight="1">
@@ -18489,7 +18512,7 @@
         <v>1680</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>8</v>
@@ -18515,7 +18538,7 @@
         <v>1648</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>8</v>
@@ -18593,7 +18616,7 @@
         <v>1650</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>88</v>
@@ -18616,10 +18639,10 @@
         <v>1681</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>8</v>
@@ -18645,7 +18668,7 @@
         <v>1651</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>8</v>
@@ -18674,7 +18697,7 @@
         <v>1426</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>8</v>
@@ -18697,7 +18720,7 @@
         <v>1429</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>8</v>
@@ -18720,7 +18743,7 @@
         <v>97</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>1431</v>
@@ -18729,7 +18752,7 @@
         <v>8</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="40" customHeight="1">
@@ -18746,7 +18769,7 @@
         <v>99</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>1433</v>
@@ -18772,16 +18795,16 @@
         <v>101</v>
       </c>
       <c r="E42" s="4" t="s">
+        <v>3306</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>3307</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>3308</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>102</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="40" customHeight="1">
@@ -18801,10 +18824,10 @@
         <v>105</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>1436</v>
@@ -18833,7 +18856,7 @@
         <v>8</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="40" customHeight="1">
@@ -18853,13 +18876,13 @@
         <v>111</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="G45" s="4" t="s">
+        <v>3311</v>
+      </c>
+      <c r="H45" s="4" t="s">
         <v>3312</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>3313</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="40" customHeight="1">
@@ -18905,10 +18928,10 @@
         <v>1682</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -18931,7 +18954,7 @@
         <v>8</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
@@ -18954,7 +18977,7 @@
         <v>1446</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>1447</v>
@@ -18977,7 +19000,7 @@
         <v>1448</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>1449</v>
@@ -19009,7 +19032,7 @@
         <v>121</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>8</v>
@@ -19035,10 +19058,10 @@
         <v>124</v>
       </c>
       <c r="F52" s="4" t="s">
+        <v>3318</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>3319</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>3320</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>1454</v>
@@ -19061,7 +19084,7 @@
         <v>1683</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>8</v>
@@ -19084,13 +19107,13 @@
         <v>130</v>
       </c>
       <c r="E54" s="4" t="s">
+        <v>3321</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>3322</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>3323</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>3324</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>8</v>
@@ -19110,10 +19133,10 @@
         <v>133</v>
       </c>
       <c r="E55" s="4" t="s">
+        <v>3324</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>3325</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>3326</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>8</v>
@@ -19136,7 +19159,7 @@
         <v>1455</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>1456</v>
@@ -19165,7 +19188,7 @@
         <v>1652</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>1458</v>
@@ -19188,7 +19211,7 @@
         <v>138</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>1460</v>
@@ -19217,10 +19240,10 @@
         <v>1462</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>1463</v>
@@ -19243,7 +19266,7 @@
         <v>1684</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>8</v>
@@ -19269,10 +19292,10 @@
         <v>1466</v>
       </c>
       <c r="F61" s="4" t="s">
+        <v>3330</v>
+      </c>
+      <c r="G61" s="4" t="s">
         <v>3331</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>3332</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>8</v>
@@ -19295,7 +19318,7 @@
         <v>1469</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>8</v>
@@ -19321,7 +19344,7 @@
         <v>1654</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>147</v>
@@ -19347,7 +19370,7 @@
         <v>1472</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>1473</v>
@@ -19373,7 +19396,7 @@
         <v>1655</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>1475</v>
@@ -19399,10 +19422,10 @@
         <v>1478</v>
       </c>
       <c r="F66" s="4" t="s">
+        <v>3336</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>3337</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>3338</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>8</v>
@@ -19425,7 +19448,7 @@
         <v>1480</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>8</v>
@@ -19451,10 +19474,10 @@
         <v>1483</v>
       </c>
       <c r="F68" s="4" t="s">
+        <v>3339</v>
+      </c>
+      <c r="G68" s="4" t="s">
         <v>3340</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>3341</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>8</v>
@@ -19477,10 +19500,10 @@
         <v>1486</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>1487</v>
@@ -19532,7 +19555,7 @@
         <v>1492</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>8</v>
@@ -19558,7 +19581,7 @@
         <v>1509</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>8</v>
@@ -19601,10 +19624,10 @@
         <v>1499</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>3344</v>
+      </c>
+      <c r="E74" s="4" t="s">
         <v>3345</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>3346</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>1500</v>
@@ -19636,7 +19659,7 @@
         <v>1511</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>8</v>
@@ -19662,7 +19685,7 @@
         <v>1512</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>8</v>
@@ -19688,7 +19711,7 @@
         <v>1513</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>8</v>
@@ -19714,7 +19737,7 @@
         <v>1514</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>8</v>
@@ -19734,7 +19757,7 @@
         <v>174</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>3351</v>
+        <v>3350</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>1516</v>
@@ -19783,10 +19806,10 @@
         <v>1522</v>
       </c>
       <c r="D81" s="4" t="s">
+        <v>3351</v>
+      </c>
+      <c r="E81" s="4" t="s">
         <v>3352</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>3353</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>1521</v>
@@ -19795,7 +19818,7 @@
         <v>8</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="40" customHeight="1">
@@ -19812,7 +19835,7 @@
         <v>178</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>1524</v>
@@ -19835,7 +19858,7 @@
         <v>1525</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>1659</v>
@@ -19873,7 +19896,7 @@
         <v>1531</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>3357</v>
+        <v>3356</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="40" customHeight="1">
@@ -19922,10 +19945,10 @@
         <v>1536</v>
       </c>
       <c r="G86" s="4" t="s">
+        <v>3357</v>
+      </c>
+      <c r="H86" s="4" t="s">
         <v>3358</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>3359</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="40" customHeight="1">
@@ -19951,7 +19974,7 @@
         <v>1538</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="40" customHeight="1">
@@ -19991,7 +20014,7 @@
         <v>1540</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>193</v>
@@ -20023,7 +20046,7 @@
         <v>1548</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>8</v>
@@ -20049,13 +20072,13 @@
         <v>1550</v>
       </c>
       <c r="F91" s="8" t="s">
+        <v>3362</v>
+      </c>
+      <c r="G91" s="4" t="s">
         <v>3363</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="H91" s="4" t="s">
         <v>3364</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>3365</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="40" customHeight="1">
@@ -20075,7 +20098,7 @@
         <v>1660</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>8</v>
@@ -20153,7 +20176,7 @@
         <v>1555</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>8</v>
@@ -20517,7 +20540,7 @@
         <v>1589</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="G109" s="4" t="s">
         <v>1590</v>
@@ -20881,7 +20904,7 @@
         <v>258</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="G123" s="4" t="s">
         <v>1631</v>
@@ -21011,7 +21034,7 @@
         <v>1711</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>8</v>
@@ -21063,7 +21086,7 @@
         <v>1724</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>8</v>
@@ -21115,7 +21138,7 @@
         <v>1730</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>8</v>
@@ -21841,7 +21864,7 @@
         <v>1821</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>330</v>
@@ -21971,7 +21994,7 @@
         <v>1837</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="G165" s="4" t="s">
         <v>1838</v>
@@ -22130,7 +22153,7 @@
         <v>1856</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="H171" s="3" t="s">
         <v>8</v>
@@ -22335,7 +22358,7 @@
         <v>1882</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>1883</v>
@@ -22572,7 +22595,7 @@
         <v>386</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="H188" s="3" t="s">
         <v>8</v>
@@ -23141,7 +23164,7 @@
         <v>1998</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>1999</v>
@@ -23193,7 +23216,7 @@
         <v>2004</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>2005</v>
@@ -23791,7 +23814,7 @@
         <v>475</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>2097</v>
@@ -23898,7 +23921,7 @@
         <v>2112</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="H239" s="3" t="s">
         <v>8</v>
@@ -23924,7 +23947,7 @@
         <v>2115</v>
       </c>
       <c r="G240" s="4" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="H240" s="3" t="s">
         <v>8</v>
@@ -24129,7 +24152,7 @@
         <v>2136</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="G248" s="3" t="s">
         <v>8</v>
@@ -24366,7 +24389,7 @@
         <v>2171</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>3393</v>
+        <v>3392</v>
       </c>
       <c r="H257" s="3" t="s">
         <v>8</v>
@@ -24727,7 +24750,7 @@
         <v>2219</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="G271" s="4" t="s">
         <v>2220</v>
@@ -25221,7 +25244,7 @@
         <v>2281</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
       <c r="G290" s="4" t="s">
         <v>2282</v>
@@ -25273,7 +25296,7 @@
         <v>2288</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="G292" s="4" t="s">
         <v>2289</v>
@@ -25559,7 +25582,7 @@
         <v>603</v>
       </c>
       <c r="F303" s="4" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="G303" s="3" t="s">
         <v>8</v>
@@ -26928,7 +26951,7 @@
         <v>733</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>2478</v>
+        <v>3423</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>734</v>
@@ -26980,22 +27003,22 @@
         <v>738</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>739</v>
       </c>
       <c r="E358" s="4" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="F358" s="4" t="s">
         <v>740</v>
       </c>
       <c r="G358" s="4" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H358" s="4" t="s">
         <v>2481</v>
-      </c>
-      <c r="H358" s="4" t="s">
-        <v>2482</v>
       </c>
     </row>
     <row r="359" spans="1:8" ht="40" customHeight="1">
@@ -27006,7 +27029,7 @@
         <v>741</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>742</v>
@@ -27032,16 +27055,16 @@
         <v>746</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>747</v>
       </c>
       <c r="E360" s="4" t="s">
+        <v>2484</v>
+      </c>
+      <c r="F360" s="4" t="s">
         <v>2485</v>
-      </c>
-      <c r="F360" s="4" t="s">
-        <v>2486</v>
       </c>
       <c r="G360" s="3" t="s">
         <v>8</v>
@@ -27058,16 +27081,16 @@
         <v>748</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>747</v>
       </c>
       <c r="E361" s="4" t="s">
+        <v>2486</v>
+      </c>
+      <c r="F361" s="4" t="s">
         <v>2487</v>
-      </c>
-      <c r="F361" s="4" t="s">
-        <v>2488</v>
       </c>
       <c r="G361" s="4" t="s">
         <v>749</v>
@@ -27084,22 +27107,22 @@
         <v>750</v>
       </c>
       <c r="C362" s="4" t="s">
+        <v>2488</v>
+      </c>
+      <c r="D362" s="4" t="s">
         <v>2489</v>
       </c>
-      <c r="D362" s="4" t="s">
+      <c r="E362" s="4" t="s">
         <v>2490</v>
       </c>
-      <c r="E362" s="4" t="s">
+      <c r="F362" s="4" t="s">
         <v>2491</v>
       </c>
-      <c r="F362" s="4" t="s">
+      <c r="G362" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H362" s="4" t="s">
         <v>2492</v>
-      </c>
-      <c r="G362" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H362" s="4" t="s">
-        <v>2493</v>
       </c>
     </row>
     <row r="363" spans="1:8" ht="40" customHeight="1">
@@ -27110,13 +27133,13 @@
         <v>751</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="D363" s="3" t="s">
         <v>752</v>
       </c>
       <c r="E363" s="4" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="F363" s="4" t="s">
         <v>753</v>
@@ -27136,7 +27159,7 @@
         <v>755</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="D364" s="3" t="s">
         <v>756</v>
@@ -27148,7 +27171,7 @@
         <v>758</v>
       </c>
       <c r="G364" s="4" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="H364" s="3" t="s">
         <v>8</v>
@@ -27162,16 +27185,16 @@
         <v>759</v>
       </c>
       <c r="C365" s="4" t="s">
+        <v>2497</v>
+      </c>
+      <c r="D365" s="4" t="s">
         <v>2498</v>
-      </c>
-      <c r="D365" s="4" t="s">
-        <v>2499</v>
       </c>
       <c r="E365" s="4" t="s">
         <v>760</v>
       </c>
       <c r="F365" s="4" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="G365" s="4" t="s">
         <v>761</v>
@@ -27188,7 +27211,7 @@
         <v>762</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>763</v>
@@ -27214,22 +27237,22 @@
         <v>767</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>768</v>
       </c>
       <c r="E367" s="4" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="F367" s="4" t="s">
         <v>769</v>
       </c>
       <c r="G367" s="4" t="s">
+        <v>2503</v>
+      </c>
+      <c r="H367" s="4" t="s">
         <v>2504</v>
-      </c>
-      <c r="H367" s="4" t="s">
-        <v>2505</v>
       </c>
     </row>
     <row r="368" spans="1:8" ht="40" customHeight="1">
@@ -27240,22 +27263,22 @@
         <v>770</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>771</v>
       </c>
       <c r="E368" s="4" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="F368" s="4" t="s">
         <v>772</v>
       </c>
       <c r="G368" s="4" t="s">
+        <v>2507</v>
+      </c>
+      <c r="H368" s="4" t="s">
         <v>2508</v>
-      </c>
-      <c r="H368" s="4" t="s">
-        <v>2509</v>
       </c>
     </row>
     <row r="369" spans="1:8" ht="40" customHeight="1">
@@ -27266,10 +27289,10 @@
         <v>773</v>
       </c>
       <c r="C369" s="4" t="s">
+        <v>2509</v>
+      </c>
+      <c r="D369" s="4" t="s">
         <v>2510</v>
-      </c>
-      <c r="D369" s="4" t="s">
-        <v>2511</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>8</v>
@@ -27292,16 +27315,16 @@
         <v>775</v>
       </c>
       <c r="C370" s="4" t="s">
+        <v>2511</v>
+      </c>
+      <c r="D370" s="4" t="s">
         <v>2512</v>
-      </c>
-      <c r="D370" s="4" t="s">
-        <v>2513</v>
       </c>
       <c r="E370" s="4" t="s">
         <v>776</v>
       </c>
       <c r="F370" s="4" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="G370" s="3" t="s">
         <v>8</v>
@@ -27318,13 +27341,13 @@
         <v>777</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="D371" s="3" t="s">
         <v>778</v>
       </c>
       <c r="E371" s="4" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="F371" s="4" t="s">
         <v>779</v>
@@ -27344,19 +27367,19 @@
         <v>780</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>781</v>
       </c>
       <c r="E372" s="4" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="F372" s="4" t="s">
         <v>782</v>
       </c>
       <c r="G372" s="4" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="H372" s="3" t="s">
         <v>8</v>
@@ -27370,13 +27393,13 @@
         <v>783</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>784</v>
       </c>
       <c r="E373" s="4" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="F373" s="4" t="s">
         <v>785</v>
@@ -27396,16 +27419,16 @@
         <v>786</v>
       </c>
       <c r="C374" s="4" t="s">
+        <v>2521</v>
+      </c>
+      <c r="D374" s="4" t="s">
         <v>2522</v>
-      </c>
-      <c r="D374" s="4" t="s">
-        <v>2523</v>
       </c>
       <c r="E374" s="4" t="s">
         <v>787</v>
       </c>
       <c r="F374" s="4" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="G374" s="3" t="s">
         <v>8</v>
@@ -27422,22 +27445,22 @@
         <v>788</v>
       </c>
       <c r="C375" s="4" t="s">
+        <v>2524</v>
+      </c>
+      <c r="D375" s="4" t="s">
         <v>2525</v>
       </c>
-      <c r="D375" s="4" t="s">
+      <c r="E375" s="4" t="s">
         <v>2526</v>
       </c>
-      <c r="E375" s="4" t="s">
+      <c r="F375" s="4" t="s">
         <v>2527</v>
-      </c>
-      <c r="F375" s="4" t="s">
-        <v>2528</v>
       </c>
       <c r="G375" s="4" t="s">
         <v>789</v>
       </c>
       <c r="H375" s="4" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="376" spans="1:8" ht="40" customHeight="1">
@@ -27448,22 +27471,22 @@
         <v>790</v>
       </c>
       <c r="C376" s="4" t="s">
+        <v>2529</v>
+      </c>
+      <c r="D376" s="4" t="s">
         <v>2530</v>
       </c>
-      <c r="D376" s="4" t="s">
+      <c r="E376" s="4" t="s">
         <v>2531</v>
       </c>
-      <c r="E376" s="4" t="s">
+      <c r="F376" s="4" t="s">
         <v>2532</v>
-      </c>
-      <c r="F376" s="4" t="s">
-        <v>2533</v>
       </c>
       <c r="G376" s="4" t="s">
         <v>791</v>
       </c>
       <c r="H376" s="4" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="377" spans="1:8" ht="40" customHeight="1">
@@ -27474,19 +27497,19 @@
         <v>792</v>
       </c>
       <c r="C377" s="4" t="s">
+        <v>2534</v>
+      </c>
+      <c r="D377" s="4" t="s">
         <v>2535</v>
       </c>
-      <c r="D377" s="4" t="s">
+      <c r="E377" s="4" t="s">
         <v>2536</v>
       </c>
-      <c r="E377" s="4" t="s">
+      <c r="F377" s="4" t="s">
         <v>2537</v>
       </c>
-      <c r="F377" s="4" t="s">
+      <c r="G377" s="4" t="s">
         <v>2538</v>
-      </c>
-      <c r="G377" s="4" t="s">
-        <v>2539</v>
       </c>
       <c r="H377" s="3" t="s">
         <v>8</v>
@@ -27500,16 +27523,16 @@
         <v>793</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>794</v>
       </c>
       <c r="E378" s="4" t="s">
+        <v>2540</v>
+      </c>
+      <c r="F378" s="4" t="s">
         <v>2541</v>
-      </c>
-      <c r="F378" s="4" t="s">
-        <v>2542</v>
       </c>
       <c r="G378" s="3" t="s">
         <v>8</v>
@@ -27526,16 +27549,16 @@
         <v>795</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>796</v>
       </c>
       <c r="E379" s="4" t="s">
+        <v>2542</v>
+      </c>
+      <c r="F379" s="4" t="s">
         <v>2543</v>
-      </c>
-      <c r="F379" s="4" t="s">
-        <v>2544</v>
       </c>
       <c r="G379" s="3" t="s">
         <v>8</v>
@@ -27552,7 +27575,7 @@
         <v>797</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>798</v>
@@ -27561,7 +27584,7 @@
         <v>799</v>
       </c>
       <c r="F380" s="4" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="G380" s="4" t="s">
         <v>800</v>
@@ -27578,16 +27601,16 @@
         <v>801</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="D381" s="3" t="s">
         <v>802</v>
       </c>
       <c r="E381" s="4" t="s">
+        <v>2547</v>
+      </c>
+      <c r="F381" s="4" t="s">
         <v>2548</v>
-      </c>
-      <c r="F381" s="4" t="s">
-        <v>2549</v>
       </c>
       <c r="G381" s="4" t="s">
         <v>803</v>
@@ -27604,13 +27627,13 @@
         <v>804</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="D382" s="3" t="s">
         <v>805</v>
       </c>
       <c r="E382" s="4" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="F382" s="4" t="s">
         <v>806</v>
@@ -27630,7 +27653,7 @@
         <v>807</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>808</v>
@@ -27656,19 +27679,19 @@
         <v>812</v>
       </c>
       <c r="C384" s="4" t="s">
+        <v>2552</v>
+      </c>
+      <c r="D384" s="4" t="s">
         <v>2553</v>
-      </c>
-      <c r="D384" s="4" t="s">
-        <v>2554</v>
       </c>
       <c r="E384" s="4" t="s">
         <v>813</v>
       </c>
       <c r="F384" s="4" t="s">
+        <v>2554</v>
+      </c>
+      <c r="G384" s="4" t="s">
         <v>2555</v>
-      </c>
-      <c r="G384" s="4" t="s">
-        <v>2556</v>
       </c>
       <c r="H384" s="3" t="s">
         <v>8</v>
@@ -27682,16 +27705,16 @@
         <v>814</v>
       </c>
       <c r="C385" s="4" t="s">
+        <v>2556</v>
+      </c>
+      <c r="D385" s="4" t="s">
         <v>2557</v>
       </c>
-      <c r="D385" s="4" t="s">
+      <c r="E385" s="4" t="s">
         <v>2558</v>
       </c>
-      <c r="E385" s="4" t="s">
+      <c r="F385" s="4" t="s">
         <v>2559</v>
-      </c>
-      <c r="F385" s="4" t="s">
-        <v>2560</v>
       </c>
       <c r="G385" s="3" t="s">
         <v>8</v>
@@ -27708,22 +27731,22 @@
         <v>815</v>
       </c>
       <c r="C386" s="4" t="s">
+        <v>2560</v>
+      </c>
+      <c r="D386" s="4" t="s">
         <v>2561</v>
       </c>
-      <c r="D386" s="4" t="s">
+      <c r="E386" s="4" t="s">
         <v>2562</v>
       </c>
-      <c r="E386" s="4" t="s">
+      <c r="F386" s="4" t="s">
         <v>2563</v>
       </c>
-      <c r="F386" s="4" t="s">
+      <c r="G386" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H386" s="4" t="s">
         <v>2564</v>
-      </c>
-      <c r="G386" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H386" s="4" t="s">
-        <v>2565</v>
       </c>
     </row>
     <row r="387" spans="1:8" ht="40" customHeight="1">
@@ -27734,16 +27757,16 @@
         <v>816</v>
       </c>
       <c r="C387" s="4" t="s">
+        <v>2565</v>
+      </c>
+      <c r="D387" s="4" t="s">
         <v>2566</v>
       </c>
-      <c r="D387" s="4" t="s">
+      <c r="E387" s="4" t="s">
         <v>2567</v>
       </c>
-      <c r="E387" s="4" t="s">
+      <c r="F387" s="4" t="s">
         <v>2568</v>
-      </c>
-      <c r="F387" s="4" t="s">
-        <v>2569</v>
       </c>
       <c r="G387" s="3" t="s">
         <v>8</v>
@@ -27760,13 +27783,13 @@
         <v>817</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>818</v>
       </c>
       <c r="E388" s="4" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="F388" s="4" t="s">
         <v>819</v>
@@ -27775,7 +27798,7 @@
         <v>820</v>
       </c>
       <c r="H388" s="4" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="389" spans="1:8" ht="40" customHeight="1">
@@ -27786,16 +27809,16 @@
         <v>821</v>
       </c>
       <c r="C389" s="4" t="s">
+        <v>2572</v>
+      </c>
+      <c r="D389" s="4" t="s">
         <v>2573</v>
       </c>
-      <c r="D389" s="4" t="s">
+      <c r="E389" s="4" t="s">
         <v>2574</v>
       </c>
-      <c r="E389" s="4" t="s">
+      <c r="F389" s="4" t="s">
         <v>2575</v>
-      </c>
-      <c r="F389" s="4" t="s">
-        <v>2576</v>
       </c>
       <c r="G389" s="4" t="s">
         <v>822</v>
@@ -27812,13 +27835,13 @@
         <v>823</v>
       </c>
       <c r="C390" s="4" t="s">
+        <v>2576</v>
+      </c>
+      <c r="D390" s="4" t="s">
         <v>2577</v>
       </c>
-      <c r="D390" s="4" t="s">
+      <c r="E390" s="4" t="s">
         <v>2578</v>
-      </c>
-      <c r="E390" s="4" t="s">
-        <v>2579</v>
       </c>
       <c r="F390" s="4" t="s">
         <v>824</v>
@@ -27827,7 +27850,7 @@
         <v>825</v>
       </c>
       <c r="H390" s="4" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="391" spans="1:8" ht="40" customHeight="1">
@@ -27838,13 +27861,13 @@
         <v>826</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>827</v>
       </c>
       <c r="E391" s="4" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="F391" s="4" t="s">
         <v>828</v>
@@ -27864,16 +27887,16 @@
         <v>830</v>
       </c>
       <c r="C392" s="4" t="s">
+        <v>2582</v>
+      </c>
+      <c r="D392" s="4" t="s">
         <v>2583</v>
       </c>
-      <c r="D392" s="4" t="s">
+      <c r="E392" s="4" t="s">
         <v>2584</v>
       </c>
-      <c r="E392" s="4" t="s">
+      <c r="F392" s="4" t="s">
         <v>2585</v>
-      </c>
-      <c r="F392" s="4" t="s">
-        <v>2586</v>
       </c>
       <c r="G392" s="3" t="s">
         <v>8</v>
@@ -27890,13 +27913,13 @@
         <v>831</v>
       </c>
       <c r="C393" s="4" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D393" s="4" t="s">
         <v>2587</v>
       </c>
-      <c r="D393" s="4" t="s">
+      <c r="E393" s="4" t="s">
         <v>2588</v>
-      </c>
-      <c r="E393" s="4" t="s">
-        <v>2589</v>
       </c>
       <c r="F393" s="4" t="s">
         <v>832</v>
@@ -27905,7 +27928,7 @@
         <v>833</v>
       </c>
       <c r="H393" s="4" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="394" spans="1:8" ht="40" customHeight="1">
@@ -27916,22 +27939,22 @@
         <v>834</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>835</v>
       </c>
       <c r="E394" s="4" t="s">
+        <v>2591</v>
+      </c>
+      <c r="F394" s="4" t="s">
         <v>2592</v>
       </c>
-      <c r="F394" s="4" t="s">
+      <c r="G394" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H394" s="4" t="s">
         <v>2593</v>
-      </c>
-      <c r="G394" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H394" s="4" t="s">
-        <v>2594</v>
       </c>
     </row>
     <row r="395" spans="1:8" ht="40" customHeight="1">
@@ -27942,13 +27965,13 @@
         <v>836</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>837</v>
       </c>
       <c r="E395" s="4" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="F395" s="4" t="s">
         <v>838</v>
@@ -27968,13 +27991,13 @@
         <v>839</v>
       </c>
       <c r="C396" s="4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="D396" s="4" t="s">
         <v>2597</v>
       </c>
-      <c r="D396" s="4" t="s">
+      <c r="E396" s="4" t="s">
         <v>2598</v>
-      </c>
-      <c r="E396" s="4" t="s">
-        <v>2599</v>
       </c>
       <c r="F396" s="4" t="s">
         <v>840</v>
@@ -27994,16 +28017,16 @@
         <v>842</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>843</v>
       </c>
       <c r="E397" s="4" t="s">
+        <v>2600</v>
+      </c>
+      <c r="F397" s="4" t="s">
         <v>2601</v>
-      </c>
-      <c r="F397" s="4" t="s">
-        <v>2602</v>
       </c>
       <c r="G397" s="3" t="s">
         <v>8</v>
@@ -28020,13 +28043,13 @@
         <v>844</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>843</v>
       </c>
       <c r="E398" s="4" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="F398" s="4" t="s">
         <v>845</v>
@@ -28035,7 +28058,7 @@
         <v>846</v>
       </c>
       <c r="H398" s="4" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="399" spans="1:8" ht="40" customHeight="1">
@@ -28046,22 +28069,22 @@
         <v>847</v>
       </c>
       <c r="C399" s="4" t="s">
+        <v>2604</v>
+      </c>
+      <c r="D399" s="4" t="s">
         <v>2605</v>
       </c>
-      <c r="D399" s="4" t="s">
+      <c r="E399" s="4" t="s">
         <v>2606</v>
       </c>
-      <c r="E399" s="4" t="s">
+      <c r="F399" s="4" t="s">
         <v>2607</v>
       </c>
-      <c r="F399" s="4" t="s">
+      <c r="G399" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H399" s="4" t="s">
         <v>2608</v>
-      </c>
-      <c r="G399" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H399" s="4" t="s">
-        <v>2609</v>
       </c>
     </row>
     <row r="400" spans="1:8" ht="40" customHeight="1">
@@ -28072,16 +28095,16 @@
         <v>848</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>849</v>
       </c>
       <c r="E400" s="4" t="s">
+        <v>2610</v>
+      </c>
+      <c r="F400" s="4" t="s">
         <v>2611</v>
-      </c>
-      <c r="F400" s="4" t="s">
-        <v>2612</v>
       </c>
       <c r="G400" s="3" t="s">
         <v>8</v>
@@ -28098,13 +28121,13 @@
         <v>850</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>849</v>
       </c>
       <c r="E401" s="4" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="F401" s="4" t="s">
         <v>851</v>
@@ -28124,16 +28147,16 @@
         <v>853</v>
       </c>
       <c r="C402" s="4" t="s">
+        <v>2613</v>
+      </c>
+      <c r="D402" s="4" t="s">
         <v>2614</v>
       </c>
-      <c r="D402" s="4" t="s">
+      <c r="E402" s="4" t="s">
         <v>2615</v>
       </c>
-      <c r="E402" s="4" t="s">
+      <c r="F402" s="4" t="s">
         <v>2616</v>
-      </c>
-      <c r="F402" s="4" t="s">
-        <v>2617</v>
       </c>
       <c r="G402" s="3" t="s">
         <v>8</v>
@@ -28150,13 +28173,13 @@
         <v>854</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>855</v>
       </c>
       <c r="E403" s="4" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="F403" s="4" t="s">
         <v>856</v>
@@ -28176,19 +28199,19 @@
         <v>858</v>
       </c>
       <c r="C404" s="4" t="s">
+        <v>2619</v>
+      </c>
+      <c r="D404" s="4" t="s">
         <v>2620</v>
       </c>
-      <c r="D404" s="4" t="s">
+      <c r="E404" s="4" t="s">
         <v>2621</v>
       </c>
-      <c r="E404" s="4" t="s">
+      <c r="F404" s="4" t="s">
         <v>2622</v>
       </c>
-      <c r="F404" s="4" t="s">
-        <v>2623</v>
-      </c>
       <c r="G404" s="4" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="H404" s="3" t="s">
         <v>8</v>
@@ -28202,19 +28225,19 @@
         <v>859</v>
       </c>
       <c r="C405" s="4" t="s">
+        <v>2623</v>
+      </c>
+      <c r="D405" s="4" t="s">
         <v>2624</v>
       </c>
-      <c r="D405" s="4" t="s">
+      <c r="E405" s="4" t="s">
         <v>2625</v>
       </c>
-      <c r="E405" s="4" t="s">
+      <c r="F405" s="4" t="s">
         <v>2626</v>
       </c>
-      <c r="F405" s="4" t="s">
+      <c r="G405" s="4" t="s">
         <v>2627</v>
-      </c>
-      <c r="G405" s="4" t="s">
-        <v>2628</v>
       </c>
       <c r="H405" s="3" t="s">
         <v>8</v>
@@ -28228,10 +28251,10 @@
         <v>860</v>
       </c>
       <c r="C406" s="4" t="s">
+        <v>2628</v>
+      </c>
+      <c r="D406" s="4" t="s">
         <v>2629</v>
-      </c>
-      <c r="D406" s="4" t="s">
-        <v>2630</v>
       </c>
       <c r="E406" s="4" t="s">
         <v>861</v>
@@ -28254,22 +28277,22 @@
         <v>863</v>
       </c>
       <c r="C407" s="4" t="s">
+        <v>2630</v>
+      </c>
+      <c r="D407" s="4" t="s">
         <v>2631</v>
       </c>
-      <c r="D407" s="4" t="s">
+      <c r="E407" s="4" t="s">
         <v>2632</v>
       </c>
-      <c r="E407" s="4" t="s">
+      <c r="F407" s="4" t="s">
         <v>2633</v>
       </c>
-      <c r="F407" s="4" t="s">
+      <c r="G407" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H407" s="4" t="s">
         <v>2634</v>
-      </c>
-      <c r="G407" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H407" s="4" t="s">
-        <v>2635</v>
       </c>
     </row>
     <row r="408" spans="1:8" ht="40" customHeight="1">
@@ -28280,16 +28303,16 @@
         <v>864</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E408" s="4" t="s">
+        <v>2636</v>
+      </c>
+      <c r="F408" s="4" t="s">
         <v>2637</v>
-      </c>
-      <c r="F408" s="4" t="s">
-        <v>2638</v>
       </c>
       <c r="G408" s="3" t="s">
         <v>8</v>
@@ -28306,22 +28329,22 @@
         <v>866</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E409" s="4" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="F409" s="4" t="s">
         <v>867</v>
       </c>
       <c r="G409" s="4" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="H409" s="4" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="410" spans="1:8" ht="40" customHeight="1">
@@ -28332,7 +28355,7 @@
         <v>868</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>871</v>
@@ -28341,7 +28364,7 @@
         <v>869</v>
       </c>
       <c r="F410" s="4" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
       <c r="G410" s="3" t="s">
         <v>8</v>
@@ -28358,22 +28381,22 @@
         <v>870</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="D411" s="3" t="s">
         <v>871</v>
       </c>
       <c r="E411" s="4" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="F411" s="4" t="s">
         <v>872</v>
       </c>
       <c r="G411" s="4" t="s">
-        <v>3401</v>
+        <v>3400</v>
       </c>
       <c r="H411" s="4" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="412" spans="1:8" ht="40" customHeight="1">
@@ -28384,16 +28407,16 @@
         <v>873</v>
       </c>
       <c r="C412" s="4" t="s">
+        <v>2644</v>
+      </c>
+      <c r="D412" s="4" t="s">
         <v>2645</v>
       </c>
-      <c r="D412" s="4" t="s">
+      <c r="E412" s="4" t="s">
         <v>2646</v>
       </c>
-      <c r="E412" s="4" t="s">
+      <c r="F412" s="4" t="s">
         <v>2647</v>
-      </c>
-      <c r="F412" s="4" t="s">
-        <v>2648</v>
       </c>
       <c r="G412" s="3" t="s">
         <v>8</v>
@@ -28410,13 +28433,13 @@
         <v>874</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="D413" s="4" t="s">
+        <v>2648</v>
+      </c>
+      <c r="E413" s="4" t="s">
         <v>2649</v>
-      </c>
-      <c r="E413" s="4" t="s">
-        <v>2650</v>
       </c>
       <c r="F413" s="4" t="s">
         <v>875</v>
@@ -28425,7 +28448,7 @@
         <v>8</v>
       </c>
       <c r="H413" s="4" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="414" spans="1:8" ht="40" customHeight="1">
@@ -28436,7 +28459,7 @@
         <v>876</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>877</v>
@@ -28445,7 +28468,7 @@
         <v>878</v>
       </c>
       <c r="F414" s="4" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="G414" s="3" t="s">
         <v>8</v>
@@ -28462,22 +28485,22 @@
         <v>879</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="D415" s="4" t="s">
+        <v>2653</v>
+      </c>
+      <c r="E415" s="4" t="s">
         <v>2654</v>
       </c>
-      <c r="E415" s="4" t="s">
+      <c r="F415" s="4" t="s">
         <v>2655</v>
       </c>
-      <c r="F415" s="4" t="s">
-        <v>2656</v>
-      </c>
       <c r="G415" s="4" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="H415" s="4" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="416" spans="1:8" ht="40" customHeight="1">
@@ -28488,16 +28511,16 @@
         <v>880</v>
       </c>
       <c r="C416" s="4" t="s">
+        <v>2656</v>
+      </c>
+      <c r="D416" s="4" t="s">
         <v>2657</v>
       </c>
-      <c r="D416" s="4" t="s">
+      <c r="E416" s="4" t="s">
         <v>2658</v>
       </c>
-      <c r="E416" s="4" t="s">
+      <c r="F416" s="4" t="s">
         <v>2659</v>
-      </c>
-      <c r="F416" s="4" t="s">
-        <v>2660</v>
       </c>
       <c r="G416" s="4" t="s">
         <v>8</v>
@@ -28514,16 +28537,16 @@
         <v>881</v>
       </c>
       <c r="C417" s="4" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D417" s="4" t="s">
         <v>2661</v>
       </c>
-      <c r="D417" s="4" t="s">
+      <c r="E417" s="4" t="s">
         <v>2662</v>
       </c>
-      <c r="E417" s="4" t="s">
+      <c r="F417" s="4" t="s">
         <v>2663</v>
-      </c>
-      <c r="F417" s="4" t="s">
-        <v>2664</v>
       </c>
       <c r="G417" s="4" t="s">
         <v>8</v>
@@ -28540,16 +28563,16 @@
         <v>882</v>
       </c>
       <c r="C418" s="4" t="s">
+        <v>2664</v>
+      </c>
+      <c r="D418" s="4" t="s">
         <v>2665</v>
-      </c>
-      <c r="D418" s="4" t="s">
-        <v>2666</v>
       </c>
       <c r="E418" s="4" t="s">
         <v>883</v>
       </c>
       <c r="F418" s="4" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="G418" s="4" t="s">
         <v>8</v>
@@ -28566,13 +28589,13 @@
         <v>884</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>885</v>
       </c>
       <c r="E419" s="4" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="F419" s="4" t="s">
         <v>886</v>
@@ -28592,7 +28615,7 @@
         <v>888</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>889</v>
@@ -28601,7 +28624,7 @@
         <v>890</v>
       </c>
       <c r="F420" s="4" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="G420" s="4" t="s">
         <v>891</v>
@@ -28618,19 +28641,19 @@
         <v>892</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>893</v>
       </c>
       <c r="E421" s="4" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="F421" s="4" t="s">
+        <v>3401</v>
+      </c>
+      <c r="G421" s="4" t="s">
         <v>3402</v>
-      </c>
-      <c r="G421" s="4" t="s">
-        <v>3403</v>
       </c>
       <c r="H421" s="4" t="s">
         <v>8</v>
@@ -28644,10 +28667,10 @@
         <v>894</v>
       </c>
       <c r="C422" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="D422" s="4" t="s">
         <v>2674</v>
-      </c>
-      <c r="D422" s="4" t="s">
-        <v>2675</v>
       </c>
       <c r="E422" s="4" t="s">
         <v>895</v>
@@ -28670,19 +28693,19 @@
         <v>898</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>899</v>
       </c>
       <c r="E423" s="4" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="F423" s="4" t="s">
         <v>900</v>
       </c>
       <c r="G423" s="4" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="H423" s="4" t="s">
         <v>8</v>
@@ -28696,19 +28719,19 @@
         <v>901</v>
       </c>
       <c r="C424" s="4" t="s">
+        <v>2677</v>
+      </c>
+      <c r="D424" s="4" t="s">
         <v>2678</v>
-      </c>
-      <c r="D424" s="4" t="s">
-        <v>2679</v>
       </c>
       <c r="E424" s="4" t="s">
         <v>902</v>
       </c>
       <c r="F424" s="4" t="s">
+        <v>2679</v>
+      </c>
+      <c r="G424" s="4" t="s">
         <v>2680</v>
-      </c>
-      <c r="G424" s="4" t="s">
-        <v>2681</v>
       </c>
       <c r="H424" s="4" t="s">
         <v>8</v>
@@ -28722,7 +28745,7 @@
         <v>903</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>904</v>
@@ -28731,7 +28754,7 @@
         <v>905</v>
       </c>
       <c r="F425" s="4" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="G425" s="4" t="s">
         <v>8</v>
@@ -28754,16 +28777,16 @@
         <v>908</v>
       </c>
       <c r="E426" s="4" t="s">
+        <v>2683</v>
+      </c>
+      <c r="F426" s="4" t="s">
         <v>2684</v>
       </c>
-      <c r="F426" s="4" t="s">
+      <c r="G426" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H426" s="4" t="s">
         <v>2685</v>
-      </c>
-      <c r="G426" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H426" s="4" t="s">
-        <v>2686</v>
       </c>
     </row>
     <row r="427" spans="1:8" ht="40" customHeight="1">
@@ -28774,7 +28797,7 @@
         <v>909</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>910</v>
@@ -28783,7 +28806,7 @@
         <v>911</v>
       </c>
       <c r="F427" s="4" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="G427" s="4" t="s">
         <v>8</v>
@@ -28809,7 +28832,7 @@
         <v>915</v>
       </c>
       <c r="F428" s="4" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="G428" s="4" t="s">
         <v>8</v>
@@ -28826,16 +28849,16 @@
         <v>916</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>917</v>
       </c>
       <c r="E429" s="4" t="s">
+        <v>2689</v>
+      </c>
+      <c r="F429" s="4" t="s">
         <v>2690</v>
-      </c>
-      <c r="F429" s="4" t="s">
-        <v>2691</v>
       </c>
       <c r="G429" s="4" t="s">
         <v>8</v>
@@ -28878,22 +28901,22 @@
         <v>924</v>
       </c>
       <c r="C431" s="4" t="s">
+        <v>2691</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>2693</v>
+      </c>
+      <c r="E431" s="4" t="s">
         <v>2692</v>
       </c>
-      <c r="D431" s="4" t="s">
+      <c r="F431" s="4" t="s">
         <v>2694</v>
-      </c>
-      <c r="E431" s="4" t="s">
-        <v>2693</v>
-      </c>
-      <c r="F431" s="4" t="s">
-        <v>2695</v>
       </c>
       <c r="G431" s="4" t="s">
         <v>925</v>
       </c>
       <c r="H431" s="4" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="432" spans="1:8" ht="40" customHeight="1">
@@ -28904,13 +28927,13 @@
         <v>926</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>927</v>
       </c>
       <c r="E432" s="4" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="F432" s="4" t="s">
         <v>928</v>
@@ -28930,16 +28953,16 @@
         <v>930</v>
       </c>
       <c r="C433" s="4" t="s">
+        <v>2698</v>
+      </c>
+      <c r="D433" s="4" t="s">
         <v>2699</v>
-      </c>
-      <c r="D433" s="4" t="s">
-        <v>2700</v>
       </c>
       <c r="E433" s="4" t="s">
         <v>931</v>
       </c>
       <c r="F433" s="4" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="G433" s="3" t="s">
         <v>8</v>
@@ -28956,7 +28979,7 @@
         <v>932</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>933</v>
@@ -28982,7 +29005,7 @@
         <v>936</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>937</v>
@@ -28991,10 +29014,10 @@
         <v>938</v>
       </c>
       <c r="F435" s="4" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="G435" s="4" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="H435" s="3" t="s">
         <v>8</v>
@@ -29008,16 +29031,16 @@
         <v>939</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>2705</v>
+        <v>2704</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>940</v>
       </c>
       <c r="E436" s="4" t="s">
+        <v>2705</v>
+      </c>
+      <c r="F436" s="4" t="s">
         <v>2706</v>
-      </c>
-      <c r="F436" s="4" t="s">
-        <v>2707</v>
       </c>
       <c r="G436" s="4" t="s">
         <v>941</v>
@@ -29034,16 +29057,16 @@
         <v>942</v>
       </c>
       <c r="C437" s="4" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D437" s="4" t="s">
         <v>2708</v>
       </c>
-      <c r="D437" s="4" t="s">
+      <c r="E437" s="4" t="s">
         <v>2709</v>
       </c>
-      <c r="E437" s="4" t="s">
+      <c r="F437" s="4" t="s">
         <v>2710</v>
-      </c>
-      <c r="F437" s="4" t="s">
-        <v>2711</v>
       </c>
       <c r="G437" s="3" t="s">
         <v>8</v>
@@ -29060,16 +29083,16 @@
         <v>943</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>2712</v>
+        <v>2711</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>944</v>
       </c>
       <c r="E438" s="4" t="s">
+        <v>2712</v>
+      </c>
+      <c r="F438" s="4" t="s">
         <v>2713</v>
-      </c>
-      <c r="F438" s="4" t="s">
-        <v>2714</v>
       </c>
       <c r="G438" s="3" t="s">
         <v>8</v>
@@ -29086,7 +29109,7 @@
         <v>945</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>946</v>
@@ -29112,13 +29135,13 @@
         <v>949</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>950</v>
       </c>
       <c r="E440" s="4" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="F440" s="4" t="s">
         <v>951</v>
@@ -29138,10 +29161,10 @@
         <v>952</v>
       </c>
       <c r="C441" s="4" t="s">
+        <v>2717</v>
+      </c>
+      <c r="D441" s="4" t="s">
         <v>2718</v>
-      </c>
-      <c r="D441" s="4" t="s">
-        <v>2719</v>
       </c>
       <c r="E441" s="4" t="s">
         <v>953</v>
@@ -29153,7 +29176,7 @@
         <v>8</v>
       </c>
       <c r="H441" s="4" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="442" spans="1:8" ht="40" customHeight="1">
@@ -29164,13 +29187,13 @@
         <v>955</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>956</v>
       </c>
       <c r="E442" s="4" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="F442" s="4" t="s">
         <v>957</v>
@@ -29190,16 +29213,16 @@
         <v>959</v>
       </c>
       <c r="C443" s="4" t="s">
+        <v>2722</v>
+      </c>
+      <c r="D443" s="4" t="s">
         <v>2723</v>
       </c>
-      <c r="D443" s="4" t="s">
+      <c r="E443" s="4" t="s">
         <v>2724</v>
       </c>
-      <c r="E443" s="4" t="s">
+      <c r="F443" s="4" t="s">
         <v>2725</v>
-      </c>
-      <c r="F443" s="4" t="s">
-        <v>2726</v>
       </c>
       <c r="G443" s="4" t="s">
         <v>960</v>
@@ -29216,16 +29239,16 @@
         <v>961</v>
       </c>
       <c r="C444" s="4" t="s">
+        <v>2726</v>
+      </c>
+      <c r="D444" s="4" t="s">
         <v>2727</v>
       </c>
-      <c r="D444" s="4" t="s">
+      <c r="E444" s="4" t="s">
         <v>2728</v>
       </c>
-      <c r="E444" s="4" t="s">
+      <c r="F444" s="4" t="s">
         <v>2729</v>
-      </c>
-      <c r="F444" s="4" t="s">
-        <v>2730</v>
       </c>
       <c r="G444" s="3" t="s">
         <v>8</v>
@@ -29242,19 +29265,19 @@
         <v>962</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>963</v>
       </c>
       <c r="E445" s="4" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="F445" s="4" t="s">
         <v>964</v>
       </c>
       <c r="G445" s="4" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
       <c r="H445" s="3" t="s">
         <v>8</v>
@@ -29268,13 +29291,13 @@
         <v>965</v>
       </c>
       <c r="C446" s="4" t="s">
+        <v>2733</v>
+      </c>
+      <c r="D446" s="4" t="s">
         <v>2734</v>
       </c>
-      <c r="D446" s="4" t="s">
+      <c r="E446" s="4" t="s">
         <v>2735</v>
-      </c>
-      <c r="E446" s="4" t="s">
-        <v>2736</v>
       </c>
       <c r="F446" s="4" t="s">
         <v>966</v>
@@ -29294,16 +29317,16 @@
         <v>968</v>
       </c>
       <c r="C447" s="4" t="s">
+        <v>2736</v>
+      </c>
+      <c r="D447" s="4" t="s">
         <v>2737</v>
       </c>
-      <c r="D447" s="4" t="s">
+      <c r="E447" s="4" t="s">
         <v>2738</v>
       </c>
-      <c r="E447" s="4" t="s">
+      <c r="F447" s="4" t="s">
         <v>2739</v>
-      </c>
-      <c r="F447" s="4" t="s">
-        <v>2740</v>
       </c>
       <c r="G447" s="3" t="s">
         <v>8</v>
@@ -29320,16 +29343,16 @@
         <v>969</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>970</v>
       </c>
       <c r="E448" s="4" t="s">
+        <v>2741</v>
+      </c>
+      <c r="F448" s="4" t="s">
         <v>2742</v>
-      </c>
-      <c r="F448" s="4" t="s">
-        <v>2743</v>
       </c>
       <c r="G448" s="4" t="s">
         <v>971</v>
@@ -29346,7 +29369,7 @@
         <v>972</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>973</v>
@@ -29355,13 +29378,13 @@
         <v>974</v>
       </c>
       <c r="F449" s="4" t="s">
+        <v>2744</v>
+      </c>
+      <c r="G449" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H449" s="4" t="s">
         <v>2745</v>
-      </c>
-      <c r="G449" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H449" s="4" t="s">
-        <v>2746</v>
       </c>
     </row>
     <row r="450" spans="1:8" ht="40" customHeight="1">
@@ -29372,7 +29395,7 @@
         <v>975</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>976</v>
@@ -29381,7 +29404,7 @@
         <v>977</v>
       </c>
       <c r="F450" s="4" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="G450" s="4" t="s">
         <v>978</v>
@@ -29398,16 +29421,16 @@
         <v>979</v>
       </c>
       <c r="C451" s="4" t="s">
+        <v>2747</v>
+      </c>
+      <c r="D451" s="4" t="s">
         <v>2748</v>
       </c>
-      <c r="D451" s="4" t="s">
+      <c r="E451" s="4" t="s">
         <v>2749</v>
       </c>
-      <c r="E451" s="4" t="s">
-        <v>2750</v>
-      </c>
       <c r="F451" s="4" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="G451" s="4" t="s">
         <v>980</v>
@@ -29424,7 +29447,7 @@
         <v>981</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>982</v>
@@ -29450,13 +29473,13 @@
         <v>986</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>987</v>
       </c>
       <c r="E453" s="4" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="F453" s="4" t="s">
         <v>988</v>
@@ -29476,16 +29499,16 @@
         <v>990</v>
       </c>
       <c r="C454" s="4" t="s">
+        <v>2753</v>
+      </c>
+      <c r="D454" s="4" t="s">
         <v>2754</v>
       </c>
-      <c r="D454" s="4" t="s">
+      <c r="E454" s="4" t="s">
         <v>2755</v>
       </c>
-      <c r="E454" s="4" t="s">
+      <c r="F454" s="4" t="s">
         <v>2756</v>
-      </c>
-      <c r="F454" s="4" t="s">
-        <v>2757</v>
       </c>
       <c r="G454" s="3" t="s">
         <v>8</v>
@@ -29502,16 +29525,16 @@
         <v>991</v>
       </c>
       <c r="C455" s="4" t="s">
+        <v>2757</v>
+      </c>
+      <c r="D455" s="4" t="s">
         <v>2758</v>
       </c>
-      <c r="D455" s="4" t="s">
+      <c r="E455" s="4" t="s">
         <v>2759</v>
       </c>
-      <c r="E455" s="4" t="s">
+      <c r="F455" s="4" t="s">
         <v>2760</v>
-      </c>
-      <c r="F455" s="4" t="s">
-        <v>2761</v>
       </c>
       <c r="G455" s="3" t="s">
         <v>8</v>
@@ -29528,19 +29551,19 @@
         <v>992</v>
       </c>
       <c r="C456" s="4" t="s">
+        <v>2761</v>
+      </c>
+      <c r="D456" s="4" t="s">
         <v>2762</v>
       </c>
-      <c r="D456" s="4" t="s">
+      <c r="E456" s="4" t="s">
         <v>2763</v>
       </c>
-      <c r="E456" s="4" t="s">
+      <c r="F456" s="4" t="s">
         <v>2764</v>
       </c>
-      <c r="F456" s="4" t="s">
-        <v>2765</v>
-      </c>
       <c r="G456" s="4" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="H456" s="3" t="s">
         <v>8</v>
@@ -29554,13 +29577,13 @@
         <v>993</v>
       </c>
       <c r="C457" s="4" t="s">
+        <v>2765</v>
+      </c>
+      <c r="D457" s="4" t="s">
         <v>2766</v>
       </c>
-      <c r="D457" s="4" t="s">
+      <c r="E457" s="4" t="s">
         <v>2767</v>
-      </c>
-      <c r="E457" s="4" t="s">
-        <v>2768</v>
       </c>
       <c r="F457" s="4" t="s">
         <v>994</v>
@@ -29580,16 +29603,16 @@
         <v>995</v>
       </c>
       <c r="C458" s="4" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D458" s="4" t="s">
         <v>2769</v>
       </c>
-      <c r="D458" s="4" t="s">
+      <c r="E458" s="4" t="s">
         <v>2770</v>
       </c>
-      <c r="E458" s="4" t="s">
+      <c r="F458" s="4" t="s">
         <v>2771</v>
-      </c>
-      <c r="F458" s="4" t="s">
-        <v>2772</v>
       </c>
       <c r="G458" s="3" t="s">
         <v>8</v>
@@ -29606,16 +29629,16 @@
         <v>996</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>997</v>
       </c>
       <c r="E459" s="4" t="s">
+        <v>2773</v>
+      </c>
+      <c r="F459" s="4" t="s">
         <v>2774</v>
-      </c>
-      <c r="F459" s="4" t="s">
-        <v>2775</v>
       </c>
       <c r="G459" s="4" t="s">
         <v>998</v>
@@ -29632,13 +29655,13 @@
         <v>999</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>1000</v>
       </c>
       <c r="E460" s="4" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="F460" s="4" t="s">
         <v>1001</v>
@@ -29658,19 +29681,19 @@
         <v>1003</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>1004</v>
       </c>
       <c r="E461" s="4" t="s">
+        <v>2778</v>
+      </c>
+      <c r="F461" s="4" t="s">
         <v>2779</v>
       </c>
-      <c r="F461" s="4" t="s">
+      <c r="G461" s="4" t="s">
         <v>2780</v>
-      </c>
-      <c r="G461" s="4" t="s">
-        <v>2781</v>
       </c>
       <c r="H461" s="3" t="s">
         <v>8</v>
@@ -29684,19 +29707,19 @@
         <v>1005</v>
       </c>
       <c r="C462" s="4" t="s">
+        <v>2781</v>
+      </c>
+      <c r="D462" s="4" t="s">
         <v>2782</v>
       </c>
-      <c r="D462" s="4" t="s">
+      <c r="E462" s="4" t="s">
         <v>2783</v>
       </c>
-      <c r="E462" s="4" t="s">
+      <c r="F462" s="4" t="s">
         <v>2784</v>
       </c>
-      <c r="F462" s="4" t="s">
+      <c r="G462" s="4" t="s">
         <v>2785</v>
-      </c>
-      <c r="G462" s="4" t="s">
-        <v>2786</v>
       </c>
       <c r="H462" s="3" t="s">
         <v>8</v>
@@ -29710,16 +29733,16 @@
         <v>1006</v>
       </c>
       <c r="C463" s="4" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D463" s="4" t="s">
         <v>2787</v>
       </c>
-      <c r="D463" s="4" t="s">
+      <c r="E463" s="4" t="s">
         <v>2788</v>
       </c>
-      <c r="E463" s="4" t="s">
+      <c r="F463" s="4" t="s">
         <v>2789</v>
-      </c>
-      <c r="F463" s="4" t="s">
-        <v>2790</v>
       </c>
       <c r="G463" s="4" t="s">
         <v>1007</v>
@@ -29736,7 +29759,7 @@
         <v>1008</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>1009</v>
@@ -29745,7 +29768,7 @@
         <v>8</v>
       </c>
       <c r="F464" s="4" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
       <c r="G464" s="3" t="s">
         <v>8</v>
@@ -29762,16 +29785,16 @@
         <v>1010</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>1011</v>
       </c>
       <c r="E465" s="4" t="s">
+        <v>2793</v>
+      </c>
+      <c r="F465" s="4" t="s">
         <v>2794</v>
-      </c>
-      <c r="F465" s="4" t="s">
-        <v>2795</v>
       </c>
       <c r="G465" s="3" t="s">
         <v>8</v>
@@ -29788,16 +29811,16 @@
         <v>1012</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>1013</v>
       </c>
       <c r="E466" s="4" t="s">
+        <v>2796</v>
+      </c>
+      <c r="F466" s="4" t="s">
         <v>2797</v>
-      </c>
-      <c r="F466" s="4" t="s">
-        <v>2798</v>
       </c>
       <c r="G466" s="3" t="s">
         <v>8</v>
@@ -29820,10 +29843,10 @@
         <v>1016</v>
       </c>
       <c r="E467" s="4" t="s">
+        <v>2798</v>
+      </c>
+      <c r="F467" s="4" t="s">
         <v>2799</v>
-      </c>
-      <c r="F467" s="4" t="s">
-        <v>2800</v>
       </c>
       <c r="G467" s="3" t="s">
         <v>8</v>
@@ -29840,16 +29863,16 @@
         <v>1017</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>1018</v>
       </c>
       <c r="E468" s="4" t="s">
+        <v>2801</v>
+      </c>
+      <c r="F468" s="4" t="s">
         <v>2802</v>
-      </c>
-      <c r="F468" s="4" t="s">
-        <v>2803</v>
       </c>
       <c r="G468" s="3" t="s">
         <v>8</v>
@@ -29866,16 +29889,16 @@
         <v>1019</v>
       </c>
       <c r="C469" s="4" t="s">
+        <v>2803</v>
+      </c>
+      <c r="D469" s="4" t="s">
         <v>2804</v>
-      </c>
-      <c r="D469" s="4" t="s">
-        <v>2805</v>
       </c>
       <c r="E469" s="4" t="s">
         <v>1020</v>
       </c>
       <c r="F469" s="4" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="G469" s="3" t="s">
         <v>8</v>
@@ -29892,7 +29915,7 @@
         <v>1021</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>1022</v>
@@ -29901,7 +29924,7 @@
         <v>1023</v>
       </c>
       <c r="F470" s="4" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="G470" s="3" t="s">
         <v>8</v>
@@ -29918,16 +29941,16 @@
         <v>1024</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>1025</v>
       </c>
       <c r="E471" s="4" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="F471" s="4" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="G471" s="4" t="s">
         <v>1026</v>
@@ -29944,7 +29967,7 @@
         <v>1027</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>1028</v>
@@ -29970,13 +29993,13 @@
         <v>1032</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>1033</v>
       </c>
       <c r="E473" s="4" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="F473" s="4" t="s">
         <v>1034</v>
@@ -29996,16 +30019,16 @@
         <v>1036</v>
       </c>
       <c r="C474" s="4" t="s">
+        <v>2813</v>
+      </c>
+      <c r="D474" s="4" t="s">
         <v>2814</v>
       </c>
-      <c r="D474" s="4" t="s">
+      <c r="E474" s="4" t="s">
         <v>2815</v>
       </c>
-      <c r="E474" s="4" t="s">
+      <c r="F474" s="4" t="s">
         <v>2816</v>
-      </c>
-      <c r="F474" s="4" t="s">
-        <v>2817</v>
       </c>
       <c r="G474" s="3" t="s">
         <v>8</v>
@@ -30022,16 +30045,16 @@
         <v>1037</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>1038</v>
       </c>
       <c r="E475" s="4" t="s">
+        <v>2818</v>
+      </c>
+      <c r="F475" s="4" t="s">
         <v>2819</v>
-      </c>
-      <c r="F475" s="4" t="s">
-        <v>2820</v>
       </c>
       <c r="G475" s="4" t="s">
         <v>1039</v>
@@ -30048,16 +30071,16 @@
         <v>1040</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="D476" s="4" t="s">
         <v>1041</v>
       </c>
       <c r="E476" s="4" t="s">
+        <v>2821</v>
+      </c>
+      <c r="F476" s="4" t="s">
         <v>2822</v>
-      </c>
-      <c r="F476" s="4" t="s">
-        <v>2823</v>
       </c>
       <c r="G476" s="4" t="s">
         <v>1042</v>
@@ -30074,16 +30097,16 @@
         <v>1043</v>
       </c>
       <c r="C477" s="4" t="s">
+        <v>2823</v>
+      </c>
+      <c r="D477" s="4" t="s">
         <v>2824</v>
       </c>
-      <c r="D477" s="4" t="s">
+      <c r="E477" s="4" t="s">
         <v>2825</v>
       </c>
-      <c r="E477" s="4" t="s">
+      <c r="F477" s="4" t="s">
         <v>2826</v>
-      </c>
-      <c r="F477" s="4" t="s">
-        <v>2827</v>
       </c>
       <c r="G477" s="3" t="s">
         <v>8</v>
@@ -30100,16 +30123,16 @@
         <v>1044</v>
       </c>
       <c r="C478" s="4" t="s">
+        <v>2827</v>
+      </c>
+      <c r="D478" s="4" t="s">
         <v>2828</v>
-      </c>
-      <c r="D478" s="4" t="s">
-        <v>2829</v>
       </c>
       <c r="E478" s="4" t="s">
         <v>1045</v>
       </c>
       <c r="F478" s="4" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="G478" s="3" t="s">
         <v>8</v>
@@ -30126,13 +30149,13 @@
         <v>1046</v>
       </c>
       <c r="C479" s="4" t="s">
+        <v>2829</v>
+      </c>
+      <c r="D479" s="4" t="s">
         <v>2830</v>
       </c>
-      <c r="D479" s="4" t="s">
+      <c r="E479" s="4" t="s">
         <v>2831</v>
-      </c>
-      <c r="E479" s="4" t="s">
-        <v>2832</v>
       </c>
       <c r="F479" s="4" t="s">
         <v>1047</v>
@@ -30152,19 +30175,19 @@
         <v>1049</v>
       </c>
       <c r="C480" s="4" t="s">
+        <v>2832</v>
+      </c>
+      <c r="D480" s="4" t="s">
         <v>2833</v>
       </c>
-      <c r="D480" s="4" t="s">
+      <c r="E480" s="4" t="s">
         <v>2834</v>
       </c>
-      <c r="E480" s="4" t="s">
+      <c r="F480" s="4" t="s">
         <v>2835</v>
       </c>
-      <c r="F480" s="4" t="s">
-        <v>2836</v>
-      </c>
       <c r="G480" s="4" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="H480" s="3" t="s">
         <v>8</v>
@@ -30178,7 +30201,7 @@
         <v>1050</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="D481" s="4" t="s">
         <v>1051</v>
@@ -30190,7 +30213,7 @@
         <v>1053</v>
       </c>
       <c r="G481" s="4" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="H481" s="3" t="s">
         <v>8</v>
@@ -30204,13 +30227,13 @@
         <v>1054</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="D482" s="4" t="s">
         <v>1055</v>
       </c>
       <c r="E482" s="4" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="F482" s="4" t="s">
         <v>1056</v>
@@ -30230,13 +30253,13 @@
         <v>1058</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="D483" s="4" t="s">
         <v>1059</v>
       </c>
       <c r="E483" s="4" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="F483" s="4" t="s">
         <v>1060</v>
@@ -30256,7 +30279,7 @@
         <v>1061</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="D484" s="4" t="s">
         <v>1062</v>
@@ -30268,7 +30291,7 @@
         <v>1064</v>
       </c>
       <c r="G484" s="4" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="H484" s="3" t="s">
         <v>8</v>
@@ -30282,16 +30305,16 @@
         <v>1065</v>
       </c>
       <c r="C485" s="4" t="s">
+        <v>2843</v>
+      </c>
+      <c r="D485" s="4" t="s">
         <v>2844</v>
       </c>
-      <c r="D485" s="4" t="s">
+      <c r="E485" s="4" t="s">
         <v>2845</v>
       </c>
-      <c r="E485" s="4" t="s">
+      <c r="F485" s="4" t="s">
         <v>2846</v>
-      </c>
-      <c r="F485" s="4" t="s">
-        <v>2847</v>
       </c>
       <c r="G485" s="3" t="s">
         <v>8</v>
@@ -30308,16 +30331,16 @@
         <v>1066</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="D486" s="4" t="s">
         <v>1067</v>
       </c>
       <c r="E486" s="4" t="s">
+        <v>2848</v>
+      </c>
+      <c r="F486" s="4" t="s">
         <v>2849</v>
-      </c>
-      <c r="F486" s="4" t="s">
-        <v>2850</v>
       </c>
       <c r="G486" s="4" t="s">
         <v>1068</v>
@@ -30334,7 +30357,7 @@
         <v>1069</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="D487" s="4" t="s">
         <v>1070</v>
@@ -30343,10 +30366,10 @@
         <v>1071</v>
       </c>
       <c r="F487" s="4" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="G487" s="4" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="H487" s="3" t="s">
         <v>8</v>
@@ -30360,13 +30383,13 @@
         <v>1072</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="D488" s="4" t="s">
         <v>1073</v>
       </c>
       <c r="E488" s="4" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="F488" s="4" t="s">
         <v>1074</v>
@@ -30386,16 +30409,16 @@
         <v>1076</v>
       </c>
       <c r="C489" s="4" t="s">
+        <v>2854</v>
+      </c>
+      <c r="D489" s="4" t="s">
         <v>2855</v>
       </c>
-      <c r="D489" s="4" t="s">
+      <c r="E489" s="4" t="s">
         <v>2856</v>
       </c>
-      <c r="E489" s="4" t="s">
+      <c r="F489" s="4" t="s">
         <v>2857</v>
-      </c>
-      <c r="F489" s="4" t="s">
-        <v>2858</v>
       </c>
       <c r="G489" s="3" t="s">
         <v>8</v>
@@ -30412,16 +30435,16 @@
         <v>1077</v>
       </c>
       <c r="C490" s="4" t="s">
+        <v>2858</v>
+      </c>
+      <c r="D490" s="4" t="s">
         <v>2859</v>
       </c>
-      <c r="D490" s="4" t="s">
+      <c r="E490" s="4" t="s">
         <v>2860</v>
       </c>
-      <c r="E490" s="4" t="s">
-        <v>2861</v>
-      </c>
       <c r="F490" s="4" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
       <c r="G490" s="4" t="s">
         <v>1078</v>
@@ -30438,19 +30461,19 @@
         <v>1079</v>
       </c>
       <c r="C491" s="4" t="s">
+        <v>2861</v>
+      </c>
+      <c r="D491" s="4" t="s">
         <v>2862</v>
       </c>
-      <c r="D491" s="4" t="s">
+      <c r="E491" s="4" t="s">
         <v>2863</v>
       </c>
-      <c r="E491" s="4" t="s">
+      <c r="F491" s="4" t="s">
+        <v>3415</v>
+      </c>
+      <c r="G491" s="4" t="s">
         <v>2864</v>
-      </c>
-      <c r="F491" s="4" t="s">
-        <v>3416</v>
-      </c>
-      <c r="G491" s="4" t="s">
-        <v>2865</v>
       </c>
       <c r="H491" s="3" t="s">
         <v>8</v>
@@ -30464,19 +30487,19 @@
         <v>1080</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="D492" s="4" t="s">
         <v>1081</v>
       </c>
       <c r="E492" s="4" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="F492" s="4" t="s">
         <v>1082</v>
       </c>
       <c r="G492" s="4" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="H492" s="3" t="s">
         <v>8</v>
@@ -30490,16 +30513,16 @@
         <v>1083</v>
       </c>
       <c r="C493" s="4" t="s">
+        <v>2868</v>
+      </c>
+      <c r="D493" s="4" t="s">
         <v>2869</v>
       </c>
-      <c r="D493" s="4" t="s">
+      <c r="E493" s="4" t="s">
         <v>2870</v>
       </c>
-      <c r="E493" s="4" t="s">
+      <c r="F493" s="4" t="s">
         <v>2871</v>
-      </c>
-      <c r="F493" s="4" t="s">
-        <v>2872</v>
       </c>
       <c r="G493" s="4" t="s">
         <v>1084</v>
@@ -30516,13 +30539,13 @@
         <v>1085</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="D494" s="4" t="s">
         <v>1086</v>
       </c>
       <c r="E494" s="4" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="F494" s="4" t="s">
         <v>1087</v>
@@ -30542,19 +30565,19 @@
         <v>1089</v>
       </c>
       <c r="C495" s="4" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="D495" s="4" t="s">
         <v>1090</v>
       </c>
       <c r="E495" s="4" t="s">
+        <v>2875</v>
+      </c>
+      <c r="F495" s="4" t="s">
         <v>2876</v>
       </c>
-      <c r="F495" s="4" t="s">
+      <c r="G495" s="4" t="s">
         <v>2877</v>
-      </c>
-      <c r="G495" s="4" t="s">
-        <v>2878</v>
       </c>
       <c r="H495" s="3" t="s">
         <v>8</v>
@@ -30568,16 +30591,16 @@
         <v>1091</v>
       </c>
       <c r="C496" s="4" t="s">
+        <v>2878</v>
+      </c>
+      <c r="D496" s="4" t="s">
         <v>2879</v>
-      </c>
-      <c r="D496" s="4" t="s">
-        <v>2880</v>
       </c>
       <c r="E496" s="4" t="s">
         <v>1092</v>
       </c>
       <c r="F496" s="4" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="G496" s="3" t="s">
         <v>8</v>
@@ -30594,13 +30617,13 @@
         <v>1093</v>
       </c>
       <c r="C497" s="4" t="s">
+        <v>2881</v>
+      </c>
+      <c r="D497" s="4" t="s">
         <v>2882</v>
       </c>
-      <c r="D497" s="4" t="s">
+      <c r="E497" s="4" t="s">
         <v>2883</v>
-      </c>
-      <c r="E497" s="4" t="s">
-        <v>2884</v>
       </c>
       <c r="F497" s="4" t="s">
         <v>1094</v>
@@ -30620,19 +30643,19 @@
         <v>1096</v>
       </c>
       <c r="C498" s="4" t="s">
+        <v>2884</v>
+      </c>
+      <c r="D498" s="4" t="s">
         <v>2885</v>
       </c>
-      <c r="D498" s="4" t="s">
+      <c r="E498" s="4" t="s">
         <v>2886</v>
-      </c>
-      <c r="E498" s="4" t="s">
-        <v>2887</v>
       </c>
       <c r="F498" s="4" t="s">
         <v>1097</v>
       </c>
       <c r="G498" s="4" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="H498" s="3" t="s">
         <v>8</v>
@@ -30646,19 +30669,19 @@
         <v>1098</v>
       </c>
       <c r="C499" s="4" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D499" s="4" t="s">
         <v>2889</v>
       </c>
-      <c r="D499" s="4" t="s">
+      <c r="E499" s="4" t="s">
         <v>2890</v>
       </c>
-      <c r="E499" s="4" t="s">
+      <c r="F499" s="4" t="s">
         <v>2891</v>
       </c>
-      <c r="F499" s="4" t="s">
+      <c r="G499" s="4" t="s">
         <v>2892</v>
-      </c>
-      <c r="G499" s="4" t="s">
-        <v>2893</v>
       </c>
       <c r="H499" s="3" t="s">
         <v>8</v>
@@ -30672,13 +30695,13 @@
         <v>1099</v>
       </c>
       <c r="C500" s="4" t="s">
+        <v>2893</v>
+      </c>
+      <c r="D500" s="4" t="s">
         <v>2894</v>
       </c>
-      <c r="D500" s="4" t="s">
+      <c r="E500" s="4" t="s">
         <v>2895</v>
-      </c>
-      <c r="E500" s="4" t="s">
-        <v>2896</v>
       </c>
       <c r="F500" s="4" t="s">
         <v>1100</v>
@@ -30698,10 +30721,10 @@
         <v>1102</v>
       </c>
       <c r="C501" s="4" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D501" s="4" t="s">
         <v>2897</v>
-      </c>
-      <c r="D501" s="4" t="s">
-        <v>2898</v>
       </c>
       <c r="E501" s="4" t="s">
         <v>1103</v>
@@ -30724,22 +30747,22 @@
         <v>1105</v>
       </c>
       <c r="C502" s="4" t="s">
+        <v>2898</v>
+      </c>
+      <c r="D502" s="4" t="s">
         <v>2899</v>
       </c>
-      <c r="D502" s="4" t="s">
+      <c r="E502" s="4" t="s">
         <v>2900</v>
       </c>
-      <c r="E502" s="4" t="s">
+      <c r="F502" s="4" t="s">
         <v>2901</v>
       </c>
-      <c r="F502" s="4" t="s">
+      <c r="G502" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H502" s="4" t="s">
         <v>2902</v>
-      </c>
-      <c r="G502" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H502" s="4" t="s">
-        <v>2903</v>
       </c>
     </row>
     <row r="503" spans="1:8" ht="40" customHeight="1">
@@ -30750,22 +30773,22 @@
         <v>1106</v>
       </c>
       <c r="C503" s="4" t="s">
+        <v>2903</v>
+      </c>
+      <c r="D503" s="4" t="s">
         <v>2904</v>
-      </c>
-      <c r="D503" s="4" t="s">
-        <v>2905</v>
       </c>
       <c r="E503" s="4" t="s">
         <v>1107</v>
       </c>
       <c r="F503" s="4" t="s">
+        <v>2905</v>
+      </c>
+      <c r="G503" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H503" s="4" t="s">
         <v>2906</v>
-      </c>
-      <c r="G503" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H503" s="4" t="s">
-        <v>2907</v>
       </c>
     </row>
     <row r="504" spans="1:8" ht="40" customHeight="1">
@@ -30776,7 +30799,7 @@
         <v>1108</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="D504" s="4" t="s">
         <v>1109</v>
@@ -30785,13 +30808,13 @@
         <v>1110</v>
       </c>
       <c r="F504" s="4" t="s">
+        <v>2908</v>
+      </c>
+      <c r="G504" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H504" s="4" t="s">
         <v>2909</v>
-      </c>
-      <c r="G504" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H504" s="4" t="s">
-        <v>2910</v>
       </c>
     </row>
     <row r="505" spans="1:8" ht="40" customHeight="1">
@@ -30802,16 +30825,16 @@
         <v>1111</v>
       </c>
       <c r="C505" s="4" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="D505" s="4" t="s">
         <v>1112</v>
       </c>
       <c r="E505" s="4" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="F505" s="4" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="G505" s="4" t="s">
         <v>1113</v>
@@ -30828,19 +30851,19 @@
         <v>1114</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="D506" s="4" t="s">
         <v>1115</v>
       </c>
       <c r="E506" s="4" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="F506" s="4" t="s">
         <v>1116</v>
       </c>
       <c r="G506" s="4" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="H506" s="3" t="s">
         <v>8</v>
@@ -30854,16 +30877,16 @@
         <v>1117</v>
       </c>
       <c r="C507" s="4" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="D507" s="4" t="s">
         <v>1118</v>
       </c>
       <c r="E507" s="4" t="s">
+        <v>2921</v>
+      </c>
+      <c r="F507" s="4" t="s">
         <v>2922</v>
-      </c>
-      <c r="F507" s="4" t="s">
-        <v>2923</v>
       </c>
       <c r="G507" s="4" t="s">
         <v>1119</v>
@@ -30880,19 +30903,19 @@
         <v>1120</v>
       </c>
       <c r="C508" s="4" t="s">
+        <v>2923</v>
+      </c>
+      <c r="D508" s="4" t="s">
         <v>2924</v>
       </c>
-      <c r="D508" s="4" t="s">
+      <c r="E508" s="4" t="s">
         <v>2925</v>
       </c>
-      <c r="E508" s="4" t="s">
+      <c r="F508" s="4" t="s">
         <v>2926</v>
       </c>
-      <c r="F508" s="4" t="s">
+      <c r="G508" s="4" t="s">
         <v>2927</v>
-      </c>
-      <c r="G508" s="4" t="s">
-        <v>2928</v>
       </c>
       <c r="H508" s="4" t="s">
         <v>1121</v>
@@ -30906,16 +30929,16 @@
         <v>1122</v>
       </c>
       <c r="C509" s="4" t="s">
+        <v>2928</v>
+      </c>
+      <c r="D509" s="4" t="s">
         <v>2929</v>
       </c>
-      <c r="D509" s="4" t="s">
+      <c r="E509" s="4" t="s">
         <v>2930</v>
       </c>
-      <c r="E509" s="4" t="s">
+      <c r="F509" s="4" t="s">
         <v>2931</v>
-      </c>
-      <c r="F509" s="4" t="s">
-        <v>2932</v>
       </c>
       <c r="G509" s="3" t="s">
         <v>8</v>
@@ -30932,16 +30955,16 @@
         <v>1123</v>
       </c>
       <c r="C510" s="4" t="s">
+        <v>2932</v>
+      </c>
+      <c r="D510" s="4" t="s">
         <v>2933</v>
       </c>
-      <c r="D510" s="4" t="s">
+      <c r="E510" s="4" t="s">
         <v>2934</v>
       </c>
-      <c r="E510" s="4" t="s">
+      <c r="F510" s="4" t="s">
         <v>2935</v>
-      </c>
-      <c r="F510" s="4" t="s">
-        <v>2936</v>
       </c>
       <c r="G510" s="4" t="s">
         <v>1124</v>
@@ -30958,19 +30981,19 @@
         <v>1125</v>
       </c>
       <c r="C511" s="4" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="D511" s="4" t="s">
         <v>1131</v>
       </c>
       <c r="E511" s="4" t="s">
+        <v>2937</v>
+      </c>
+      <c r="F511" s="4" t="s">
         <v>2938</v>
       </c>
-      <c r="F511" s="4" t="s">
+      <c r="G511" s="4" t="s">
         <v>2939</v>
-      </c>
-      <c r="G511" s="4" t="s">
-        <v>2940</v>
       </c>
       <c r="H511" s="3" t="s">
         <v>8</v>
@@ -30984,16 +31007,16 @@
         <v>1126</v>
       </c>
       <c r="C512" s="4" t="s">
+        <v>2940</v>
+      </c>
+      <c r="D512" s="4" t="s">
         <v>2941</v>
-      </c>
-      <c r="D512" s="4" t="s">
-        <v>2942</v>
       </c>
       <c r="E512" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="F512" s="4" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="G512" s="3" t="s">
         <v>8</v>
@@ -31010,16 +31033,16 @@
         <v>1128</v>
       </c>
       <c r="C513" s="4" t="s">
+        <v>2943</v>
+      </c>
+      <c r="D513" s="4" t="s">
+        <v>2947</v>
+      </c>
+      <c r="E513" s="4" t="s">
         <v>2944</v>
       </c>
-      <c r="D513" s="4" t="s">
-        <v>2948</v>
-      </c>
-      <c r="E513" s="4" t="s">
+      <c r="F513" s="4" t="s">
         <v>2945</v>
-      </c>
-      <c r="F513" s="4" t="s">
-        <v>2946</v>
       </c>
       <c r="G513" s="4" t="s">
         <v>1129</v>
@@ -31036,19 +31059,19 @@
         <v>1130</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="D514" s="4" t="s">
+        <v>2948</v>
+      </c>
+      <c r="E514" s="4" t="s">
+        <v>2951</v>
+      </c>
+      <c r="F514" s="4" t="s">
         <v>2949</v>
       </c>
-      <c r="E514" s="4" t="s">
-        <v>2952</v>
-      </c>
-      <c r="F514" s="4" t="s">
+      <c r="G514" s="4" t="s">
         <v>2950</v>
-      </c>
-      <c r="G514" s="4" t="s">
-        <v>2951</v>
       </c>
       <c r="H514" s="3" t="s">
         <v>8</v>
@@ -31062,16 +31085,16 @@
         <v>1132</v>
       </c>
       <c r="C515" s="4" t="s">
+        <v>2952</v>
+      </c>
+      <c r="D515" s="4" t="s">
         <v>2953</v>
       </c>
-      <c r="D515" s="4" t="s">
+      <c r="E515" s="4" t="s">
         <v>2954</v>
       </c>
-      <c r="E515" s="4" t="s">
+      <c r="F515" s="4" t="s">
         <v>2955</v>
-      </c>
-      <c r="F515" s="4" t="s">
-        <v>2956</v>
       </c>
       <c r="G515" s="3" t="s">
         <v>8</v>
@@ -31088,16 +31111,16 @@
         <v>1133</v>
       </c>
       <c r="C516" s="4" t="s">
+        <v>2956</v>
+      </c>
+      <c r="D516" s="4" t="s">
         <v>2957</v>
       </c>
-      <c r="D516" s="4" t="s">
+      <c r="E516" s="4" t="s">
         <v>2958</v>
       </c>
-      <c r="E516" s="4" t="s">
+      <c r="F516" s="4" t="s">
         <v>2959</v>
-      </c>
-      <c r="F516" s="4" t="s">
-        <v>2960</v>
       </c>
       <c r="G516" s="3" t="s">
         <v>8</v>
@@ -31114,16 +31137,16 @@
         <v>1134</v>
       </c>
       <c r="C517" s="4" t="s">
+        <v>2960</v>
+      </c>
+      <c r="D517" s="4" t="s">
         <v>2961</v>
       </c>
-      <c r="D517" s="4" t="s">
+      <c r="E517" s="4" t="s">
         <v>2962</v>
       </c>
-      <c r="E517" s="4" t="s">
+      <c r="F517" s="4" t="s">
         <v>2963</v>
-      </c>
-      <c r="F517" s="4" t="s">
-        <v>2964</v>
       </c>
       <c r="G517" s="3" t="s">
         <v>8</v>
@@ -31140,10 +31163,10 @@
         <v>1135</v>
       </c>
       <c r="C518" s="4" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D518" s="4" t="s">
         <v>2965</v>
-      </c>
-      <c r="D518" s="4" t="s">
-        <v>2966</v>
       </c>
       <c r="E518" s="4" t="s">
         <v>1136</v>
@@ -31166,16 +31189,16 @@
         <v>1138</v>
       </c>
       <c r="C519" s="4" t="s">
+        <v>2966</v>
+      </c>
+      <c r="D519" s="4" t="s">
         <v>2967</v>
       </c>
-      <c r="D519" s="4" t="s">
+      <c r="E519" s="4" t="s">
         <v>2968</v>
       </c>
-      <c r="E519" s="4" t="s">
+      <c r="F519" s="4" t="s">
         <v>2969</v>
-      </c>
-      <c r="F519" s="4" t="s">
-        <v>2970</v>
       </c>
       <c r="G519" s="3" t="s">
         <v>8</v>
@@ -31192,16 +31215,16 @@
         <v>1139</v>
       </c>
       <c r="C520" s="4" t="s">
+        <v>2970</v>
+      </c>
+      <c r="D520" s="4" t="s">
         <v>2971</v>
       </c>
-      <c r="D520" s="4" t="s">
+      <c r="E520" s="4" t="s">
         <v>2972</v>
       </c>
-      <c r="E520" s="4" t="s">
+      <c r="F520" s="4" t="s">
         <v>2973</v>
-      </c>
-      <c r="F520" s="4" t="s">
-        <v>2974</v>
       </c>
       <c r="G520" s="3" t="s">
         <v>8</v>
@@ -31218,19 +31241,19 @@
         <v>1140</v>
       </c>
       <c r="C521" s="4" t="s">
+        <v>2974</v>
+      </c>
+      <c r="D521" s="4" t="s">
         <v>2975</v>
       </c>
-      <c r="D521" s="4" t="s">
+      <c r="E521" s="4" t="s">
         <v>2976</v>
       </c>
-      <c r="E521" s="4" t="s">
+      <c r="F521" s="4" t="s">
         <v>2977</v>
       </c>
-      <c r="F521" s="4" t="s">
+      <c r="G521" s="4" t="s">
         <v>2978</v>
-      </c>
-      <c r="G521" s="4" t="s">
-        <v>2979</v>
       </c>
       <c r="H521" s="3" t="s">
         <v>8</v>
@@ -31244,19 +31267,19 @@
         <v>1141</v>
       </c>
       <c r="C522" s="4" t="s">
+        <v>2979</v>
+      </c>
+      <c r="D522" s="4" t="s">
         <v>2980</v>
       </c>
-      <c r="D522" s="4" t="s">
+      <c r="E522" s="4" t="s">
         <v>2981</v>
       </c>
-      <c r="E522" s="4" t="s">
+      <c r="F522" s="4" t="s">
         <v>2982</v>
       </c>
-      <c r="F522" s="4" t="s">
+      <c r="G522" s="4" t="s">
         <v>2983</v>
-      </c>
-      <c r="G522" s="4" t="s">
-        <v>2984</v>
       </c>
       <c r="H522" s="3" t="s">
         <v>8</v>
@@ -31270,13 +31293,13 @@
         <v>1142</v>
       </c>
       <c r="C523" s="4" t="s">
+        <v>2984</v>
+      </c>
+      <c r="D523" s="4" t="s">
         <v>2985</v>
       </c>
-      <c r="D523" s="4" t="s">
+      <c r="E523" s="4" t="s">
         <v>2986</v>
-      </c>
-      <c r="E523" s="4" t="s">
-        <v>2987</v>
       </c>
       <c r="F523" s="4" t="s">
         <v>1143</v>
@@ -31296,13 +31319,13 @@
         <v>1145</v>
       </c>
       <c r="C524" s="4" t="s">
+        <v>2987</v>
+      </c>
+      <c r="D524" s="4" t="s">
         <v>2988</v>
       </c>
-      <c r="D524" s="4" t="s">
+      <c r="E524" s="4" t="s">
         <v>2989</v>
-      </c>
-      <c r="E524" s="4" t="s">
-        <v>2990</v>
       </c>
       <c r="F524" s="4" t="s">
         <v>1146</v>
@@ -31322,19 +31345,19 @@
         <v>1148</v>
       </c>
       <c r="C525" s="4" t="s">
+        <v>2990</v>
+      </c>
+      <c r="D525" s="4" t="s">
         <v>2991</v>
       </c>
-      <c r="D525" s="4" t="s">
+      <c r="E525" s="4" t="s">
         <v>2992</v>
-      </c>
-      <c r="E525" s="4" t="s">
-        <v>2993</v>
       </c>
       <c r="F525" s="4" t="s">
         <v>1149</v>
       </c>
       <c r="G525" s="4" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="H525" s="3" t="s">
         <v>8</v>
@@ -31348,13 +31371,13 @@
         <v>1150</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="D526" s="4" t="s">
         <v>1151</v>
       </c>
       <c r="E526" s="4" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="F526" s="4" t="s">
         <v>1152</v>
@@ -31374,16 +31397,16 @@
         <v>1154</v>
       </c>
       <c r="C527" s="4" t="s">
+        <v>2996</v>
+      </c>
+      <c r="D527" s="4" t="s">
         <v>2997</v>
       </c>
-      <c r="D527" s="4" t="s">
+      <c r="E527" s="4" t="s">
         <v>2998</v>
       </c>
-      <c r="E527" s="4" t="s">
-        <v>2999</v>
-      </c>
       <c r="F527" s="4" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="G527" s="3" t="s">
         <v>8</v>
@@ -31400,16 +31423,16 @@
         <v>1155</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="D528" s="4" t="s">
         <v>1156</v>
       </c>
       <c r="E528" s="4" t="s">
+        <v>3000</v>
+      </c>
+      <c r="F528" s="4" t="s">
         <v>3001</v>
-      </c>
-      <c r="F528" s="4" t="s">
-        <v>3002</v>
       </c>
       <c r="G528" s="3" t="s">
         <v>8</v>
@@ -31426,16 +31449,16 @@
         <v>1157</v>
       </c>
       <c r="C529" s="4" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="D529" s="4" t="s">
+        <v>3002</v>
+      </c>
+      <c r="E529" s="4" t="s">
         <v>3003</v>
       </c>
-      <c r="E529" s="4" t="s">
+      <c r="F529" s="4" t="s">
         <v>3004</v>
-      </c>
-      <c r="F529" s="4" t="s">
-        <v>3005</v>
       </c>
       <c r="G529" s="4" t="s">
         <v>1158</v>
@@ -31452,16 +31475,16 @@
         <v>1159</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="D530" s="4" t="s">
         <v>1160</v>
       </c>
       <c r="E530" s="4" t="s">
+        <v>3006</v>
+      </c>
+      <c r="F530" s="4" t="s">
         <v>3007</v>
-      </c>
-      <c r="F530" s="4" t="s">
-        <v>3008</v>
       </c>
       <c r="G530" s="3" t="s">
         <v>8</v>
@@ -31478,19 +31501,19 @@
         <v>1161</v>
       </c>
       <c r="C531" s="4" t="s">
+        <v>3008</v>
+      </c>
+      <c r="D531" s="4" t="s">
         <v>3009</v>
       </c>
-      <c r="D531" s="4" t="s">
+      <c r="E531" s="4" t="s">
         <v>3010</v>
-      </c>
-      <c r="E531" s="4" t="s">
-        <v>3011</v>
       </c>
       <c r="F531" s="4" t="s">
         <v>1162</v>
       </c>
       <c r="G531" s="4" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="H531" s="3" t="s">
         <v>8</v>
@@ -31504,19 +31527,19 @@
         <v>1163</v>
       </c>
       <c r="C532" s="4" t="s">
+        <v>3012</v>
+      </c>
+      <c r="D532" s="4" t="s">
         <v>3013</v>
       </c>
-      <c r="D532" s="4" t="s">
+      <c r="E532" s="4" t="s">
         <v>3014</v>
       </c>
-      <c r="E532" s="4" t="s">
+      <c r="F532" s="4" t="s">
         <v>3015</v>
       </c>
-      <c r="F532" s="4" t="s">
+      <c r="G532" s="4" t="s">
         <v>3016</v>
-      </c>
-      <c r="G532" s="4" t="s">
-        <v>3017</v>
       </c>
       <c r="H532" s="3" t="s">
         <v>8</v>
@@ -31530,16 +31553,16 @@
         <v>1164</v>
       </c>
       <c r="C533" s="4" t="s">
+        <v>3017</v>
+      </c>
+      <c r="D533" s="4" t="s">
         <v>3018</v>
       </c>
-      <c r="D533" s="4" t="s">
+      <c r="E533" s="4" t="s">
         <v>3019</v>
       </c>
-      <c r="E533" s="4" t="s">
+      <c r="F533" s="4" t="s">
         <v>3020</v>
-      </c>
-      <c r="F533" s="4" t="s">
-        <v>3021</v>
       </c>
       <c r="G533" s="3" t="s">
         <v>8</v>
@@ -31556,16 +31579,16 @@
         <v>1165</v>
       </c>
       <c r="C534" s="4" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="D534" s="4" t="s">
         <v>1166</v>
       </c>
       <c r="E534" s="4" t="s">
+        <v>3022</v>
+      </c>
+      <c r="F534" s="4" t="s">
         <v>3023</v>
-      </c>
-      <c r="F534" s="4" t="s">
-        <v>3024</v>
       </c>
       <c r="G534" s="4" t="s">
         <v>1167</v>
@@ -31582,13 +31605,13 @@
         <v>1168</v>
       </c>
       <c r="C535" s="4" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="D535" s="4" t="s">
         <v>1169</v>
       </c>
       <c r="E535" s="4" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="F535" s="4" t="s">
         <v>1170</v>
@@ -31608,16 +31631,16 @@
         <v>1172</v>
       </c>
       <c r="C536" s="4" t="s">
+        <v>3026</v>
+      </c>
+      <c r="D536" s="4" t="s">
         <v>3027</v>
       </c>
-      <c r="D536" s="4" t="s">
+      <c r="E536" s="4" t="s">
         <v>3028</v>
       </c>
-      <c r="E536" s="4" t="s">
+      <c r="F536" s="4" t="s">
         <v>3029</v>
-      </c>
-      <c r="F536" s="4" t="s">
-        <v>3030</v>
       </c>
       <c r="G536" s="4" t="s">
         <v>1173</v>
@@ -31634,16 +31657,16 @@
         <v>1174</v>
       </c>
       <c r="C537" s="4" t="s">
+        <v>3030</v>
+      </c>
+      <c r="D537" s="4" t="s">
+        <v>3018</v>
+      </c>
+      <c r="E537" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F537" s="4" t="s">
         <v>3031</v>
-      </c>
-      <c r="D537" s="4" t="s">
-        <v>3019</v>
-      </c>
-      <c r="E537" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F537" s="4" t="s">
-        <v>3032</v>
       </c>
       <c r="G537" s="3" t="s">
         <v>8</v>
@@ -31663,10 +31686,10 @@
         <v>1176</v>
       </c>
       <c r="D538" s="4" t="s">
+        <v>3032</v>
+      </c>
+      <c r="E538" s="4" t="s">
         <v>3033</v>
-      </c>
-      <c r="E538" s="4" t="s">
-        <v>3034</v>
       </c>
       <c r="F538" s="4" t="s">
         <v>1177</v>
@@ -31689,13 +31712,13 @@
         <v>1176</v>
       </c>
       <c r="D539" s="4" t="s">
+        <v>3034</v>
+      </c>
+      <c r="E539" s="4" t="s">
         <v>3035</v>
       </c>
-      <c r="E539" s="4" t="s">
+      <c r="F539" s="4" t="s">
         <v>3036</v>
-      </c>
-      <c r="F539" s="4" t="s">
-        <v>3037</v>
       </c>
       <c r="G539" s="3" t="s">
         <v>8</v>
@@ -31712,19 +31735,19 @@
         <v>1179</v>
       </c>
       <c r="C540" s="4" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D540" s="4" t="s">
         <v>3038</v>
-      </c>
-      <c r="D540" s="4" t="s">
-        <v>3039</v>
       </c>
       <c r="E540" s="4" t="s">
         <v>1180</v>
       </c>
       <c r="F540" s="4" t="s">
+        <v>3039</v>
+      </c>
+      <c r="G540" s="4" t="s">
         <v>3040</v>
-      </c>
-      <c r="G540" s="4" t="s">
-        <v>3041</v>
       </c>
       <c r="H540" s="3" t="s">
         <v>8</v>
@@ -31738,19 +31761,19 @@
         <v>1181</v>
       </c>
       <c r="C541" s="4" t="s">
+        <v>3041</v>
+      </c>
+      <c r="D541" s="4" t="s">
         <v>3042</v>
       </c>
-      <c r="D541" s="4" t="s">
+      <c r="E541" s="4" t="s">
         <v>3043</v>
       </c>
-      <c r="E541" s="4" t="s">
+      <c r="F541" s="4" t="s">
         <v>3044</v>
       </c>
-      <c r="F541" s="4" t="s">
+      <c r="G541" s="4" t="s">
         <v>3045</v>
-      </c>
-      <c r="G541" s="4" t="s">
-        <v>3046</v>
       </c>
       <c r="H541" s="3" t="s">
         <v>8</v>
@@ -31764,16 +31787,16 @@
         <v>1182</v>
       </c>
       <c r="C542" s="4" t="s">
+        <v>3046</v>
+      </c>
+      <c r="D542" s="4" t="s">
         <v>3047</v>
       </c>
-      <c r="D542" s="4" t="s">
+      <c r="E542" s="4" t="s">
         <v>3048</v>
       </c>
-      <c r="E542" s="4" t="s">
+      <c r="F542" s="4" t="s">
         <v>3049</v>
-      </c>
-      <c r="F542" s="4" t="s">
-        <v>3050</v>
       </c>
       <c r="G542" s="3" t="s">
         <v>8</v>
@@ -31790,16 +31813,16 @@
         <v>1183</v>
       </c>
       <c r="C543" s="4" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="D543" s="4" t="s">
         <v>1184</v>
       </c>
       <c r="E543" s="4" t="s">
+        <v>3051</v>
+      </c>
+      <c r="F543" s="4" t="s">
         <v>3052</v>
-      </c>
-      <c r="F543" s="4" t="s">
-        <v>3053</v>
       </c>
       <c r="G543" s="3" t="s">
         <v>8</v>
@@ -31816,16 +31839,16 @@
         <v>1185</v>
       </c>
       <c r="C544" s="4" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D544" s="4" t="s">
         <v>3054</v>
       </c>
-      <c r="D544" s="4" t="s">
+      <c r="E544" s="4" t="s">
         <v>3055</v>
       </c>
-      <c r="E544" s="4" t="s">
+      <c r="F544" s="4" t="s">
         <v>3056</v>
-      </c>
-      <c r="F544" s="4" t="s">
-        <v>3057</v>
       </c>
       <c r="G544" s="3" t="s">
         <v>8</v>
@@ -31842,10 +31865,10 @@
         <v>1186</v>
       </c>
       <c r="C545" s="4" t="s">
+        <v>3057</v>
+      </c>
+      <c r="D545" s="4" t="s">
         <v>3058</v>
-      </c>
-      <c r="D545" s="4" t="s">
-        <v>3059</v>
       </c>
       <c r="E545" s="4" t="s">
         <v>1187</v>
@@ -31857,7 +31880,7 @@
         <v>1189</v>
       </c>
       <c r="H545" s="4" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="546" spans="1:8" ht="40" customHeight="1">
@@ -31868,7 +31891,7 @@
         <v>1190</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="D546" s="4" t="s">
         <v>1191</v>
@@ -31894,16 +31917,16 @@
         <v>1194</v>
       </c>
       <c r="C547" s="4" t="s">
+        <v>3061</v>
+      </c>
+      <c r="D547" s="4" t="s">
         <v>3062</v>
       </c>
-      <c r="D547" s="4" t="s">
+      <c r="E547" s="4" t="s">
         <v>3063</v>
       </c>
-      <c r="E547" s="4" t="s">
+      <c r="F547" s="4" t="s">
         <v>3064</v>
-      </c>
-      <c r="F547" s="4" t="s">
-        <v>3065</v>
       </c>
       <c r="G547" s="3" t="s">
         <v>8</v>
@@ -31920,13 +31943,13 @@
         <v>1195</v>
       </c>
       <c r="C548" s="4" t="s">
+        <v>3065</v>
+      </c>
+      <c r="D548" s="4" t="s">
         <v>3066</v>
       </c>
-      <c r="D548" s="4" t="s">
+      <c r="E548" s="4" t="s">
         <v>3067</v>
-      </c>
-      <c r="E548" s="4" t="s">
-        <v>3068</v>
       </c>
       <c r="F548" s="4" t="s">
         <v>1196</v>
@@ -31946,19 +31969,19 @@
         <v>1198</v>
       </c>
       <c r="C549" s="4" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="D549" s="4" t="s">
         <v>1199</v>
       </c>
       <c r="E549" s="4" t="s">
+        <v>3069</v>
+      </c>
+      <c r="F549" s="4" t="s">
         <v>3070</v>
       </c>
-      <c r="F549" s="4" t="s">
+      <c r="G549" s="4" t="s">
         <v>3071</v>
-      </c>
-      <c r="G549" s="4" t="s">
-        <v>3072</v>
       </c>
       <c r="H549" s="3" t="s">
         <v>8</v>
@@ -31972,7 +31995,7 @@
         <v>1200</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="D550" s="4" t="s">
         <v>1201</v>
@@ -31981,7 +32004,7 @@
         <v>1202</v>
       </c>
       <c r="F550" s="4" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="G550" s="3" t="s">
         <v>8</v>
@@ -31998,16 +32021,16 @@
         <v>1203</v>
       </c>
       <c r="C551" s="4" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="D551" s="4" t="s">
         <v>1204</v>
       </c>
       <c r="E551" s="4" t="s">
+        <v>3075</v>
+      </c>
+      <c r="F551" s="4" t="s">
         <v>3076</v>
-      </c>
-      <c r="F551" s="4" t="s">
-        <v>3077</v>
       </c>
       <c r="G551" s="3" t="s">
         <v>8</v>
@@ -32024,16 +32047,16 @@
         <v>1205</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="D552" s="4" t="s">
         <v>1206</v>
       </c>
       <c r="E552" s="4" t="s">
+        <v>3078</v>
+      </c>
+      <c r="F552" s="4" t="s">
         <v>3079</v>
-      </c>
-      <c r="F552" s="4" t="s">
-        <v>3080</v>
       </c>
       <c r="G552" s="4" t="s">
         <v>1207</v>
@@ -32050,16 +32073,16 @@
         <v>1208</v>
       </c>
       <c r="C553" s="4" t="s">
+        <v>3080</v>
+      </c>
+      <c r="D553" s="4" t="s">
         <v>3081</v>
-      </c>
-      <c r="D553" s="4" t="s">
-        <v>3082</v>
       </c>
       <c r="E553" s="4" t="s">
         <v>1209</v>
       </c>
       <c r="F553" s="4" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="G553" s="3" t="s">
         <v>8</v>
@@ -32076,13 +32099,13 @@
         <v>1210</v>
       </c>
       <c r="C554" s="4" t="s">
+        <v>3083</v>
+      </c>
+      <c r="D554" s="4" t="s">
         <v>3084</v>
       </c>
-      <c r="D554" s="4" t="s">
+      <c r="E554" s="4" t="s">
         <v>3085</v>
-      </c>
-      <c r="E554" s="4" t="s">
-        <v>3086</v>
       </c>
       <c r="F554" s="4" t="s">
         <v>1211</v>
@@ -32102,7 +32125,7 @@
         <v>1213</v>
       </c>
       <c r="C555" s="4" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="D555" s="4" t="s">
         <v>1214</v>
@@ -32111,7 +32134,7 @@
         <v>1215</v>
       </c>
       <c r="F555" s="4" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="G555" s="3" t="s">
         <v>8</v>
@@ -32137,7 +32160,7 @@
         <v>1219</v>
       </c>
       <c r="F556" s="4" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="G556" s="3" t="s">
         <v>8</v>
@@ -32154,13 +32177,13 @@
         <v>1220</v>
       </c>
       <c r="C557" s="4" t="s">
+        <v>3089</v>
+      </c>
+      <c r="D557" s="4" t="s">
         <v>3090</v>
       </c>
-      <c r="D557" s="4" t="s">
+      <c r="E557" s="4" t="s">
         <v>3091</v>
-      </c>
-      <c r="E557" s="4" t="s">
-        <v>3092</v>
       </c>
       <c r="F557" s="4" t="s">
         <v>1221</v>
@@ -32180,16 +32203,16 @@
         <v>1222</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="D558" s="4" t="s">
         <v>1223</v>
       </c>
       <c r="E558" s="4" t="s">
+        <v>3093</v>
+      </c>
+      <c r="F558" s="4" t="s">
         <v>3094</v>
-      </c>
-      <c r="F558" s="4" t="s">
-        <v>3095</v>
       </c>
       <c r="G558" s="3" t="s">
         <v>8</v>
@@ -32206,16 +32229,16 @@
         <v>1224</v>
       </c>
       <c r="C559" s="4" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="D559" s="4" t="s">
         <v>1223</v>
       </c>
       <c r="E559" s="4" t="s">
+        <v>3095</v>
+      </c>
+      <c r="F559" s="4" t="s">
         <v>3096</v>
-      </c>
-      <c r="F559" s="4" t="s">
-        <v>3097</v>
       </c>
       <c r="G559" s="3" t="s">
         <v>8</v>
@@ -32232,16 +32255,16 @@
         <v>1225</v>
       </c>
       <c r="C560" s="4" t="s">
+        <v>3097</v>
+      </c>
+      <c r="D560" s="4" t="s">
         <v>3098</v>
       </c>
-      <c r="D560" s="4" t="s">
+      <c r="E560" s="4" t="s">
         <v>3099</v>
       </c>
-      <c r="E560" s="4" t="s">
+      <c r="F560" s="4" t="s">
         <v>3100</v>
-      </c>
-      <c r="F560" s="4" t="s">
-        <v>3101</v>
       </c>
       <c r="G560" s="3" t="s">
         <v>8</v>
@@ -32258,16 +32281,16 @@
         <v>1226</v>
       </c>
       <c r="C561" s="4" t="s">
+        <v>3101</v>
+      </c>
+      <c r="D561" s="4" t="s">
         <v>3102</v>
       </c>
-      <c r="D561" s="4" t="s">
+      <c r="E561" s="4" t="s">
         <v>3103</v>
       </c>
-      <c r="E561" s="4" t="s">
+      <c r="F561" s="4" t="s">
         <v>3104</v>
-      </c>
-      <c r="F561" s="4" t="s">
-        <v>3105</v>
       </c>
       <c r="G561" s="3" t="s">
         <v>8</v>
@@ -32284,16 +32307,16 @@
         <v>1227</v>
       </c>
       <c r="C562" s="4" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="D562" s="4" t="s">
         <v>1228</v>
       </c>
       <c r="E562" s="4" t="s">
+        <v>3106</v>
+      </c>
+      <c r="F562" s="4" t="s">
         <v>3107</v>
-      </c>
-      <c r="F562" s="4" t="s">
-        <v>3108</v>
       </c>
       <c r="G562" s="3" t="s">
         <v>8</v>
@@ -32310,19 +32333,19 @@
         <v>1229</v>
       </c>
       <c r="C563" s="4" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="D563" s="4" t="s">
         <v>1230</v>
       </c>
       <c r="E563" s="4" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="F563" s="4" t="s">
         <v>1231</v>
       </c>
       <c r="G563" s="4" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="H563" s="3" t="s">
         <v>8</v>
@@ -32336,22 +32359,22 @@
         <v>1232</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="D564" s="4" t="s">
         <v>1233</v>
       </c>
       <c r="E564" s="4" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="F564" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="G564" s="4" t="s">
+        <v>3113</v>
+      </c>
+      <c r="H564" s="4" t="s">
         <v>3114</v>
-      </c>
-      <c r="H564" s="4" t="s">
-        <v>3115</v>
       </c>
     </row>
     <row r="565" spans="1:8" ht="40" customHeight="1">
@@ -32362,16 +32385,16 @@
         <v>1235</v>
       </c>
       <c r="C565" s="4" t="s">
+        <v>3115</v>
+      </c>
+      <c r="D565" s="4" t="s">
         <v>3116</v>
       </c>
-      <c r="D565" s="4" t="s">
+      <c r="E565" s="4" t="s">
         <v>3117</v>
       </c>
-      <c r="E565" s="4" t="s">
+      <c r="F565" s="4" t="s">
         <v>3118</v>
-      </c>
-      <c r="F565" s="4" t="s">
-        <v>3119</v>
       </c>
       <c r="G565" s="3" t="s">
         <v>8</v>
@@ -32388,7 +32411,7 @@
         <v>1236</v>
       </c>
       <c r="C566" s="4" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="D566" s="4" t="s">
         <v>1237</v>
@@ -32414,16 +32437,16 @@
         <v>1241</v>
       </c>
       <c r="C567" s="4" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="D567" s="4" t="s">
         <v>1242</v>
       </c>
       <c r="E567" s="4" t="s">
+        <v>3121</v>
+      </c>
+      <c r="F567" s="4" t="s">
         <v>3122</v>
-      </c>
-      <c r="F567" s="4" t="s">
-        <v>3123</v>
       </c>
       <c r="G567" s="3" t="s">
         <v>8</v>
@@ -32440,13 +32463,13 @@
         <v>1243</v>
       </c>
       <c r="C568" s="4" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="D568" s="4" t="s">
         <v>1244</v>
       </c>
       <c r="E568" s="4" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="F568" s="4" t="s">
         <v>1245</v>
@@ -32466,16 +32489,16 @@
         <v>1246</v>
       </c>
       <c r="C569" s="4" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="D569" s="4" t="s">
         <v>1247</v>
       </c>
       <c r="E569" s="4" t="s">
+        <v>3126</v>
+      </c>
+      <c r="F569" s="4" t="s">
         <v>3127</v>
-      </c>
-      <c r="F569" s="4" t="s">
-        <v>3128</v>
       </c>
       <c r="G569" s="3" t="s">
         <v>8</v>
@@ -32492,16 +32515,16 @@
         <v>1248</v>
       </c>
       <c r="C570" s="4" t="s">
+        <v>3128</v>
+      </c>
+      <c r="D570" s="4" t="s">
         <v>3129</v>
       </c>
-      <c r="D570" s="4" t="s">
+      <c r="E570" s="4" t="s">
         <v>3130</v>
       </c>
-      <c r="E570" s="4" t="s">
+      <c r="F570" s="4" t="s">
         <v>3131</v>
-      </c>
-      <c r="F570" s="4" t="s">
-        <v>3132</v>
       </c>
       <c r="G570" s="3" t="s">
         <v>8</v>
@@ -32518,22 +32541,22 @@
         <v>1249</v>
       </c>
       <c r="C571" s="4" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="D571" s="4" t="s">
+        <v>3132</v>
+      </c>
+      <c r="E571" s="4" t="s">
         <v>3133</v>
       </c>
-      <c r="E571" s="4" t="s">
+      <c r="F571" s="4" t="s">
         <v>3134</v>
       </c>
-      <c r="F571" s="4" t="s">
+      <c r="G571" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H571" s="4" t="s">
         <v>3135</v>
-      </c>
-      <c r="G571" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H571" s="4" t="s">
-        <v>3136</v>
       </c>
     </row>
     <row r="572" spans="1:8" ht="40" customHeight="1">
@@ -32544,10 +32567,10 @@
         <v>1250</v>
       </c>
       <c r="C572" s="4" t="s">
+        <v>3136</v>
+      </c>
+      <c r="D572" s="4" t="s">
         <v>3137</v>
-      </c>
-      <c r="D572" s="4" t="s">
-        <v>3138</v>
       </c>
       <c r="E572" s="4" t="s">
         <v>1251</v>
@@ -32556,7 +32579,7 @@
         <v>1252</v>
       </c>
       <c r="G572" s="4" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="H572" s="3" t="s">
         <v>8</v>
@@ -32570,19 +32593,19 @@
         <v>1253</v>
       </c>
       <c r="C573" s="4" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="D573" s="4" t="s">
         <v>1254</v>
       </c>
       <c r="E573" s="4" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="F573" s="4" t="s">
         <v>1255</v>
       </c>
       <c r="G573" s="4" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="H573" s="3" t="s">
         <v>8</v>
@@ -32596,19 +32619,19 @@
         <v>1256</v>
       </c>
       <c r="C574" s="4" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="D574" s="4" t="s">
         <v>1257</v>
       </c>
       <c r="E574" s="4" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="F574" s="4" t="s">
         <v>1258</v>
       </c>
       <c r="G574" s="4" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="H574" s="3" t="s">
         <v>8</v>
@@ -32622,7 +32645,7 @@
         <v>1259</v>
       </c>
       <c r="C575" s="4" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="D575" s="4" t="s">
         <v>1260</v>
@@ -32634,7 +32657,7 @@
         <v>1262</v>
       </c>
       <c r="G575" s="4" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="H575" s="3" t="s">
         <v>8</v>
@@ -32648,13 +32671,13 @@
         <v>1263</v>
       </c>
       <c r="C576" s="4" t="s">
+        <v>3145</v>
+      </c>
+      <c r="D576" s="4" t="s">
         <v>3146</v>
       </c>
-      <c r="D576" s="4" t="s">
+      <c r="E576" s="4" t="s">
         <v>3147</v>
-      </c>
-      <c r="E576" s="4" t="s">
-        <v>3148</v>
       </c>
       <c r="F576" s="4" t="s">
         <v>1264</v>
@@ -32674,19 +32697,19 @@
         <v>1266</v>
       </c>
       <c r="C577" s="4" t="s">
+        <v>3148</v>
+      </c>
+      <c r="D577" s="4" t="s">
         <v>3149</v>
       </c>
-      <c r="D577" s="4" t="s">
+      <c r="E577" s="4" t="s">
         <v>3150</v>
-      </c>
-      <c r="E577" s="4" t="s">
-        <v>3151</v>
       </c>
       <c r="F577" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="G577" s="4" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="H577" s="3" t="s">
         <v>8</v>
@@ -32700,16 +32723,16 @@
         <v>1268</v>
       </c>
       <c r="C578" s="4" t="s">
+        <v>3151</v>
+      </c>
+      <c r="D578" s="4" t="s">
         <v>3152</v>
       </c>
-      <c r="D578" s="4" t="s">
+      <c r="E578" s="4" t="s">
         <v>3153</v>
       </c>
-      <c r="E578" s="4" t="s">
+      <c r="F578" s="4" t="s">
         <v>3154</v>
-      </c>
-      <c r="F578" s="4" t="s">
-        <v>3155</v>
       </c>
       <c r="G578" s="3" t="s">
         <v>8</v>
@@ -32726,16 +32749,16 @@
         <v>1269</v>
       </c>
       <c r="C579" s="4" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="D579" s="4" t="s">
         <v>1270</v>
       </c>
       <c r="E579" s="4" t="s">
+        <v>3156</v>
+      </c>
+      <c r="F579" s="4" t="s">
         <v>3157</v>
-      </c>
-      <c r="F579" s="4" t="s">
-        <v>3158</v>
       </c>
       <c r="G579" s="3" t="s">
         <v>8</v>
@@ -32752,7 +32775,7 @@
         <v>1271</v>
       </c>
       <c r="C580" s="4" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="D580" s="4" t="s">
         <v>1272</v>
@@ -32761,7 +32784,7 @@
         <v>1273</v>
       </c>
       <c r="F580" s="4" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="G580" s="4" t="s">
         <v>1274</v>
@@ -32778,7 +32801,7 @@
         <v>1275</v>
       </c>
       <c r="C581" s="4" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="D581" s="4" t="s">
         <v>1276</v>
@@ -32787,7 +32810,7 @@
         <v>1277</v>
       </c>
       <c r="F581" s="4" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="G581" s="3" t="s">
         <v>8</v>
@@ -32804,7 +32827,7 @@
         <v>1278</v>
       </c>
       <c r="C582" s="4" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="D582" s="4" t="s">
         <v>1279</v>
@@ -32816,7 +32839,7 @@
         <v>1281</v>
       </c>
       <c r="G582" s="4" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="H582" s="3" t="s">
         <v>8</v>
@@ -32830,7 +32853,7 @@
         <v>1282</v>
       </c>
       <c r="C583" s="4" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="D583" s="4" t="s">
         <v>1283</v>
@@ -32839,7 +32862,7 @@
         <v>1284</v>
       </c>
       <c r="F583" s="4" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="G583" s="3" t="s">
         <v>8</v>
@@ -32856,7 +32879,7 @@
         <v>1285</v>
       </c>
       <c r="C584" s="4" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="D584" s="4" t="s">
         <v>1286</v>
@@ -32882,19 +32905,19 @@
         <v>1290</v>
       </c>
       <c r="C585" s="4" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="D585" s="4" t="s">
         <v>1291</v>
       </c>
       <c r="E585" s="4" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="F585" s="4" t="s">
         <v>1292</v>
       </c>
       <c r="G585" s="4" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="H585" s="3" t="s">
         <v>8</v>
@@ -32908,16 +32931,16 @@
         <v>1293</v>
       </c>
       <c r="C586" s="4" t="s">
+        <v>3170</v>
+      </c>
+      <c r="D586" s="4" t="s">
         <v>3171</v>
       </c>
-      <c r="D586" s="4" t="s">
+      <c r="E586" s="4" t="s">
         <v>3172</v>
       </c>
-      <c r="E586" s="4" t="s">
+      <c r="F586" s="4" t="s">
         <v>3173</v>
-      </c>
-      <c r="F586" s="4" t="s">
-        <v>3174</v>
       </c>
       <c r="G586" s="3" t="s">
         <v>8</v>
@@ -32934,7 +32957,7 @@
         <v>1294</v>
       </c>
       <c r="C587" s="4" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="D587" s="4" t="s">
         <v>1295</v>
@@ -32943,7 +32966,7 @@
         <v>1296</v>
       </c>
       <c r="F587" s="4" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="G587" s="4" t="s">
         <v>1297</v>
@@ -32960,13 +32983,13 @@
         <v>1298</v>
       </c>
       <c r="C588" s="4" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="D588" s="4" t="s">
         <v>1299</v>
       </c>
       <c r="E588" s="4" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="F588" s="4" t="s">
         <v>1300</v>
@@ -32986,19 +33009,19 @@
         <v>1302</v>
       </c>
       <c r="C589" s="4" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="D589" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="E589" s="4" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="F589" s="4" t="s">
         <v>1304</v>
       </c>
       <c r="G589" s="4" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="H589" s="3" t="s">
         <v>8</v>
@@ -33012,7 +33035,7 @@
         <v>1305</v>
       </c>
       <c r="C590" s="4" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="D590" s="4" t="s">
         <v>1306</v>
@@ -33038,16 +33061,16 @@
         <v>1309</v>
       </c>
       <c r="C591" s="4" t="s">
+        <v>3182</v>
+      </c>
+      <c r="D591" s="4" t="s">
         <v>3183</v>
       </c>
-      <c r="D591" s="4" t="s">
+      <c r="E591" s="4" t="s">
         <v>3184</v>
       </c>
-      <c r="E591" s="4" t="s">
+      <c r="F591" s="4" t="s">
         <v>3185</v>
-      </c>
-      <c r="F591" s="4" t="s">
-        <v>3186</v>
       </c>
       <c r="G591" s="3" t="s">
         <v>8</v>
@@ -33064,7 +33087,7 @@
         <v>1310</v>
       </c>
       <c r="C592" s="4" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="D592" s="4" t="s">
         <v>1311</v>
@@ -33073,7 +33096,7 @@
         <v>1312</v>
       </c>
       <c r="F592" s="4" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="G592" s="3" t="s">
         <v>8</v>
@@ -33090,22 +33113,22 @@
         <v>1313</v>
       </c>
       <c r="C593" s="4" t="s">
+        <v>3187</v>
+      </c>
+      <c r="D593" s="4" t="s">
         <v>3188</v>
       </c>
-      <c r="D593" s="4" t="s">
+      <c r="E593" s="4" t="s">
         <v>3189</v>
       </c>
-      <c r="E593" s="4" t="s">
+      <c r="F593" s="4" t="s">
         <v>3190</v>
-      </c>
-      <c r="F593" s="4" t="s">
-        <v>3191</v>
       </c>
       <c r="G593" s="4" t="s">
         <v>1314</v>
       </c>
       <c r="H593" s="4" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="594" spans="1:8" ht="40" customHeight="1">
@@ -33116,16 +33139,16 @@
         <v>1315</v>
       </c>
       <c r="C594" s="4" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="D594" s="4" t="s">
         <v>1316</v>
       </c>
       <c r="E594" s="4" t="s">
+        <v>3193</v>
+      </c>
+      <c r="F594" s="4" t="s">
         <v>3194</v>
-      </c>
-      <c r="F594" s="4" t="s">
-        <v>3195</v>
       </c>
       <c r="G594" s="4" t="s">
         <v>1317</v>
@@ -33142,16 +33165,16 @@
         <v>1318</v>
       </c>
       <c r="C595" s="4" t="s">
+        <v>3195</v>
+      </c>
+      <c r="D595" s="4" t="s">
         <v>3196</v>
-      </c>
-      <c r="D595" s="4" t="s">
-        <v>3197</v>
       </c>
       <c r="E595" s="4" t="s">
         <v>1319</v>
       </c>
       <c r="F595" s="4" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="G595" s="3" t="s">
         <v>8</v>
@@ -33168,7 +33191,7 @@
         <v>1320</v>
       </c>
       <c r="C596" s="4" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="D596" s="4" t="s">
         <v>1321</v>
@@ -33177,7 +33200,7 @@
         <v>1322</v>
       </c>
       <c r="F596" s="4" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="G596" s="3" t="s">
         <v>8</v>
@@ -33194,19 +33217,19 @@
         <v>1323</v>
       </c>
       <c r="C597" s="4" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="D597" s="4" t="s">
         <v>1324</v>
       </c>
       <c r="E597" s="4" t="s">
+        <v>3200</v>
+      </c>
+      <c r="F597" s="4" t="s">
         <v>3201</v>
       </c>
-      <c r="F597" s="4" t="s">
+      <c r="G597" s="4" t="s">
         <v>3202</v>
-      </c>
-      <c r="G597" s="4" t="s">
-        <v>3203</v>
       </c>
       <c r="H597" s="3" t="s">
         <v>8</v>
@@ -33220,16 +33243,16 @@
         <v>1325</v>
       </c>
       <c r="C598" s="4" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="D598" s="4" t="s">
         <v>1326</v>
       </c>
       <c r="E598" s="4" t="s">
+        <v>3204</v>
+      </c>
+      <c r="F598" s="4" t="s">
         <v>3205</v>
-      </c>
-      <c r="F598" s="4" t="s">
-        <v>3206</v>
       </c>
       <c r="G598" s="3" t="s">
         <v>8</v>
@@ -33246,22 +33269,22 @@
         <v>1327</v>
       </c>
       <c r="C599" s="4" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="D599" s="4" t="s">
         <v>1326</v>
       </c>
       <c r="E599" s="4" t="s">
+        <v>3206</v>
+      </c>
+      <c r="F599" s="4" t="s">
         <v>3207</v>
       </c>
-      <c r="F599" s="4" t="s">
+      <c r="G599" s="4" t="s">
         <v>3208</v>
       </c>
-      <c r="G599" s="4" t="s">
+      <c r="H599" s="4" t="s">
         <v>3209</v>
-      </c>
-      <c r="H599" s="4" t="s">
-        <v>3210</v>
       </c>
     </row>
     <row r="600" spans="1:8" ht="40" customHeight="1">
@@ -33272,16 +33295,16 @@
         <v>1328</v>
       </c>
       <c r="C600" s="4" t="s">
+        <v>3210</v>
+      </c>
+      <c r="D600" s="4" t="s">
         <v>3211</v>
       </c>
-      <c r="D600" s="4" t="s">
+      <c r="E600" s="4" t="s">
         <v>3212</v>
       </c>
-      <c r="E600" s="4" t="s">
+      <c r="F600" s="4" t="s">
         <v>3213</v>
-      </c>
-      <c r="F600" s="4" t="s">
-        <v>3214</v>
       </c>
       <c r="G600" s="3" t="s">
         <v>8</v>
@@ -33298,16 +33321,16 @@
         <v>1329</v>
       </c>
       <c r="C601" s="4" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="D601" s="4" t="s">
         <v>1330</v>
       </c>
       <c r="E601" s="4" t="s">
+        <v>3215</v>
+      </c>
+      <c r="F601" s="4" t="s">
         <v>3216</v>
-      </c>
-      <c r="F601" s="4" t="s">
-        <v>3217</v>
       </c>
       <c r="G601" s="3" t="s">
         <v>8</v>
@@ -33324,7 +33347,7 @@
         <v>1331</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="D602" s="4" t="s">
         <v>1332</v>
@@ -33333,7 +33356,7 @@
         <v>1333</v>
       </c>
       <c r="F602" s="4" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="G602" s="4" t="s">
         <v>1334</v>
@@ -33350,19 +33373,19 @@
         <v>1335</v>
       </c>
       <c r="C603" s="4" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="D603" s="4" t="s">
         <v>1336</v>
       </c>
       <c r="E603" s="4" t="s">
+        <v>3220</v>
+      </c>
+      <c r="F603" s="4" t="s">
         <v>3221</v>
       </c>
-      <c r="F603" s="4" t="s">
+      <c r="G603" s="4" t="s">
         <v>3222</v>
-      </c>
-      <c r="G603" s="4" t="s">
-        <v>3223</v>
       </c>
       <c r="H603" s="3" t="s">
         <v>8</v>
@@ -33376,7 +33399,7 @@
         <v>1337</v>
       </c>
       <c r="C604" s="4" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="D604" s="4" t="s">
         <v>1338</v>
@@ -33402,16 +33425,16 @@
         <v>1341</v>
       </c>
       <c r="C605" s="4" t="s">
+        <v>3224</v>
+      </c>
+      <c r="D605" s="4" t="s">
         <v>3225</v>
       </c>
-      <c r="D605" s="4" t="s">
+      <c r="E605" s="4" t="s">
         <v>3226</v>
       </c>
-      <c r="E605" s="4" t="s">
+      <c r="F605" s="4" t="s">
         <v>3227</v>
-      </c>
-      <c r="F605" s="4" t="s">
-        <v>3228</v>
       </c>
       <c r="G605" s="3" t="s">
         <v>8</v>
@@ -33428,16 +33451,16 @@
         <v>1342</v>
       </c>
       <c r="C606" s="4" t="s">
+        <v>3228</v>
+      </c>
+      <c r="D606" s="4" t="s">
         <v>3229</v>
-      </c>
-      <c r="D606" s="4" t="s">
-        <v>3230</v>
       </c>
       <c r="E606" s="4" t="s">
         <v>1343</v>
       </c>
       <c r="F606" s="4" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="G606" s="4" t="s">
         <v>1344</v>
@@ -33454,7 +33477,7 @@
         <v>1345</v>
       </c>
       <c r="C607" s="4" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="D607" s="4" t="s">
         <v>1346</v>
@@ -33480,13 +33503,13 @@
         <v>1349</v>
       </c>
       <c r="C608" s="4" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="D608" s="4" t="s">
         <v>1350</v>
       </c>
       <c r="E608" s="4" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="F608" s="4" t="s">
         <v>1351</v>
@@ -33506,13 +33529,13 @@
         <v>1352</v>
       </c>
       <c r="C609" s="4" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="D609" s="4" t="s">
         <v>1353</v>
       </c>
       <c r="E609" s="4" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="F609" s="4" t="s">
         <v>1354</v>
@@ -33532,13 +33555,13 @@
         <v>1355</v>
       </c>
       <c r="C610" s="4" t="s">
+        <v>3236</v>
+      </c>
+      <c r="D610" s="4" t="s">
         <v>3237</v>
       </c>
-      <c r="D610" s="4" t="s">
+      <c r="E610" s="4" t="s">
         <v>3238</v>
-      </c>
-      <c r="E610" s="4" t="s">
-        <v>3239</v>
       </c>
       <c r="F610" s="4" t="s">
         <v>1356</v>
@@ -33558,20 +33581,20 @@
         <v>7</v>
       </c>
       <c r="C611" s="4" t="s">
+        <v>3239</v>
+      </c>
+      <c r="D611" s="4" t="s">
         <v>3240</v>
-      </c>
-      <c r="D611" s="4" t="s">
-        <v>3241</v>
       </c>
       <c r="E611" s="3"/>
       <c r="F611" s="4" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="G611" s="4" t="s">
         <v>9</v>
       </c>
       <c r="H611" s="4" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="612" spans="1:8" ht="40" customHeight="1">
@@ -33582,7 +33605,7 @@
         <v>10</v>
       </c>
       <c r="C612" s="4" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="D612" s="4" t="s">
         <v>11</v>
@@ -33591,7 +33614,7 @@
         <v>8</v>
       </c>
       <c r="F612" s="4" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="G612" s="4" t="s">
         <v>12</v>
@@ -33608,7 +33631,7 @@
         <v>13</v>
       </c>
       <c r="C613" s="4" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="D613" s="4" t="s">
         <v>14</v>
@@ -33617,7 +33640,7 @@
         <v>8</v>
       </c>
       <c r="F613" s="4" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="G613" s="4" t="s">
         <v>9</v>
@@ -33634,7 +33657,7 @@
         <v>15</v>
       </c>
       <c r="C614" s="4" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="D614" s="4" t="s">
         <v>14</v>
@@ -33643,7 +33666,7 @@
         <v>8</v>
       </c>
       <c r="F614" s="4" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="G614" s="4" t="s">
         <v>9</v>
@@ -33660,16 +33683,16 @@
         <v>16</v>
       </c>
       <c r="C615" s="4" t="s">
+        <v>3247</v>
+      </c>
+      <c r="D615" s="4" t="s">
         <v>3248</v>
       </c>
-      <c r="D615" s="4" t="s">
+      <c r="E615" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F615" s="4" t="s">
         <v>3249</v>
-      </c>
-      <c r="E615" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F615" s="4" t="s">
-        <v>3250</v>
       </c>
       <c r="G615" s="4" t="s">
         <v>9</v>
@@ -33686,16 +33709,16 @@
         <v>17</v>
       </c>
       <c r="C616" s="4" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="D616" s="4" t="s">
+        <v>3250</v>
+      </c>
+      <c r="E616" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F616" s="4" t="s">
         <v>3251</v>
-      </c>
-      <c r="E616" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F616" s="4" t="s">
-        <v>3252</v>
       </c>
       <c r="G616" s="4" t="s">
         <v>9</v>
@@ -33712,16 +33735,16 @@
         <v>18</v>
       </c>
       <c r="C617" s="4" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="D617" s="4" t="s">
+        <v>3252</v>
+      </c>
+      <c r="E617" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F617" s="4" t="s">
         <v>3253</v>
-      </c>
-      <c r="E617" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F617" s="4" t="s">
-        <v>3254</v>
       </c>
       <c r="G617" s="4" t="s">
         <v>9</v>
@@ -33738,16 +33761,16 @@
         <v>19</v>
       </c>
       <c r="C618" s="4" t="s">
+        <v>3254</v>
+      </c>
+      <c r="D618" s="4" t="s">
         <v>3255</v>
       </c>
-      <c r="D618" s="4" t="s">
-        <v>3256</v>
-      </c>
       <c r="E618" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F618" s="4" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="G618" s="4" t="s">
         <v>9</v>
@@ -33764,19 +33787,19 @@
         <v>20</v>
       </c>
       <c r="C619" s="4" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="D619" s="4" t="s">
+        <v>3256</v>
+      </c>
+      <c r="E619" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F619" s="4" t="s">
         <v>3257</v>
       </c>
-      <c r="E619" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F619" s="4" t="s">
+      <c r="G619" s="4" t="s">
         <v>3258</v>
-      </c>
-      <c r="G619" s="4" t="s">
-        <v>3259</v>
       </c>
       <c r="H619" s="3" t="s">
         <v>8</v>
@@ -33790,16 +33813,16 @@
         <v>21</v>
       </c>
       <c r="C620" s="4" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="D620" s="4" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="E620" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F620" s="4" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="G620" s="4" t="s">
         <v>9</v>
@@ -33811,13 +33834,12 @@
   </sheetData>
   <autoFilter ref="A1:H620" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <customSheetViews>
-    <customSheetView guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" showAutoFilter="1">
-      <pane ySplit="3" topLeftCell="A4" activePane="bottomLeft" state="frozen"/>
-      <selection pane="bottomLeft" activeCell="F5" sqref="F5"/>
+    <customSheetView guid="{61C7386F-07EB-4198-B2FD-4D1A7B0F335F}">
+      <pane ySplit="1" topLeftCell="A2" activePane="bottomLeft" state="frozen"/>
+      <selection pane="bottomLeft" activeCell="E4" sqref="E4"/>
       <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
       <pageSetup paperSize="0" orientation="portrait" r:id="rId1"/>
       <headerFooter alignWithMargins="0"/>
-      <autoFilter ref="A1:H620" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
     </customSheetView>
     <customSheetView guid="{B0EC71A6-F8E8-4D42-9918-972E5566A443}" topLeftCell="B1">
       <pane ySplit="1" topLeftCell="A101" activePane="bottomLeft" state="frozen"/>
@@ -33826,12 +33848,13 @@
       <pageSetup paperSize="0" orientation="portrait" r:id="rId2"/>
       <headerFooter alignWithMargins="0"/>
     </customSheetView>
-    <customSheetView guid="{61C7386F-07EB-4198-B2FD-4D1A7B0F335F}">
-      <pane ySplit="1" topLeftCell="A2" activePane="bottomLeft" state="frozen"/>
-      <selection pane="bottomLeft" activeCell="E4" sqref="E4"/>
+    <customSheetView guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" showAutoFilter="1">
+      <pane ySplit="3" topLeftCell="A4" activePane="bottomLeft" state="frozen"/>
+      <selection pane="bottomLeft" activeCell="F5" sqref="F5"/>
       <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
       <pageSetup paperSize="0" orientation="portrait" r:id="rId3"/>
       <headerFooter alignWithMargins="0"/>
+      <autoFilter ref="A1:H620" xr:uid="{3A37A857-4445-744C-836A-3A25027DD9B4}"/>
     </customSheetView>
   </customSheetViews>
   <phoneticPr fontId="0" type="noConversion"/>
@@ -33852,7 +33875,7 @@
     <row r="1" ht="158.25" customHeight="1"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" state="hidden">
+    <customSheetView guid="{61C7386F-07EB-4198-B2FD-4D1A7B0F335F}" state="hidden">
       <selection activeCell="C11" sqref="C11"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
@@ -33860,7 +33883,7 @@
       <selection activeCell="C11" sqref="C11"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
-    <customSheetView guid="{61C7386F-07EB-4198-B2FD-4D1A7B0F335F}" state="hidden">
+    <customSheetView guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" state="hidden">
       <selection activeCell="C11" sqref="C11"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>

--- a/src/bonn_thesis/data/raw/ISCO-08 EN Structure and definitions.xlsx
+++ b/src/bonn_thesis/data/raw/ISCO-08 EN Structure and definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willbackes/Documents/code/bonn_thesis/src/bonn_thesis/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{ADC6377B-6707-BB42-89EA-D26EE915AF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{2B4C9C18-08A6-7C40-B4D6-867492AD10A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-7500" windowWidth="22280" windowHeight="19340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30780" yWindow="-6280" windowWidth="22280" windowHeight="19340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ISCO-08 EN Struct and defin" sheetId="1" r:id="rId1"/>
@@ -22,9 +22,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="William Backes - Personal View" guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" mergeInterval="0" personalView="1" xWindow="1539" yWindow="-314" windowWidth="1114" windowHeight="967" activeSheetId="1"/>
+    <customWorkbookView name="Kalinga, Agnes - Personal View" guid="{B0EC71A6-F8E8-4D42-9918-972E5566A443}" mergeInterval="0" personalView="1" xWindow="6" yWindow="20" windowWidth="1714" windowHeight="995" activeSheetId="1"/>
     <customWorkbookView name="Badre, Lara - Personal View" guid="{61C7386F-07EB-4198-B2FD-4D1A7B0F335F}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1382" windowHeight="744" activeSheetId="1"/>
-    <customWorkbookView name="Kalinga, Agnes - Personal View" guid="{B0EC71A6-F8E8-4D42-9918-972E5566A443}" mergeInterval="0" personalView="1" xWindow="6" yWindow="20" windowWidth="1714" windowHeight="995" activeSheetId="1"/>
-    <customWorkbookView name="William Backes - Personal View" guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" mergeInterval="0" personalView="1" xWindow="1512" yWindow="-375" windowWidth="1114" windowHeight="967" activeSheetId="1"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -9948,9 +9948,6 @@
 - Medical assistant - 3256
 - Secretary (general) - 4120
 - Medical office receptionist - 4226</t>
-  </si>
-  <si>
-    <t>Government Regulatory  Associate Professionals</t>
   </si>
   <si>
     <t>Government regulatory associate professionals administer, enforce or apply relevant government rules and regulations relating to national borders, taxes and social benefits; investigate facts and circumstances relating to crimes; and issue or examine applications for licences or authorizations in connection with travel, exports and imports of goods, establishment of businesses, erection of buildings and other activities subject to government regulations.</t>
@@ -17125,6 +17122,9 @@
   </si>
   <si>
     <t>Shop Salespersons</t>
+  </si>
+  <si>
+    <t>Government Regulatory Associate Professionals</t>
   </si>
 </sst>
 </file>
@@ -17365,7 +17365,7 @@
 </file>
 
 <file path=xl/revisions/revisionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
-<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{C19FE2B2-46D6-EF48-BA92-7305958441E5}" diskRevisions="1" revisionId="2592" version="9">
+<headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{2A03940B-BA22-2443-A262-D3437AAE9996}" diskRevisions="1" revisionId="2594" version="10">
   <header guid="{F8BADF6E-2CEC-0149-8604-9EC9585B97B3}" dateTime="2025-10-24T06:27:12" maxSheetId="3" userName="William Backes" r:id="rId545">
     <sheetIdMap count="2">
       <sheetId val="1"/>
@@ -17373,6 +17373,12 @@
     </sheetIdMap>
   </header>
   <header guid="{C19FE2B2-46D6-EF48-BA92-7305958441E5}" dateTime="2025-12-03T05:53:33" maxSheetId="3" userName="William Backes" r:id="rId546" minRId="2592">
+    <sheetIdMap count="2">
+      <sheetId val="1"/>
+      <sheetId val="2"/>
+    </sheetIdMap>
+  </header>
+  <header guid="{2A03940B-BA22-2443-A262-D3437AAE9996}" dateTime="2025-12-03T21:21:38" maxSheetId="3" userName="William Backes" r:id="rId547" minRId="2593">
     <sheetIdMap count="2">
       <sheetId val="1"/>
       <sheetId val="2"/>
@@ -17406,6 +17412,29 @@
       </is>
     </nc>
   </rcc>
+</revisions>
+</file>
+
+<file path=xl/revisions/revisionLog3.xml><?xml version="1.0" encoding="utf-8"?>
+<revisions xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <rcc rId="2593" sId="1">
+    <oc r="C254" t="inlineStr">
+      <is>
+        <t>Government Regulatory  Associate Professionals</t>
+      </is>
+    </oc>
+    <nc r="C254" t="inlineStr">
+      <is>
+        <t>Government Regulatory Associate Professionals</t>
+      </is>
+    </nc>
+  </rcc>
+  <rcv guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" action="delete"/>
+  <rdn rId="0" localSheetId="1" customView="1" name="Z_89EF2E2A_048C_1241_BCF7_95B4122206B1_.wvu.FilterData" hidden="1" oldHidden="1">
+    <formula>'ISCO-08 EN Struct and defin'!$A$1:$H$620</formula>
+    <oldFormula>'ISCO-08 EN Struct and defin'!$A$1:$H$620</oldFormula>
+  </rdn>
+  <rcv guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" action="add"/>
 </revisions>
 </file>
 
@@ -17758,13 +17787,13 @@
         <v>1644</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>2914</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>2915</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>2916</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="28.5" customHeight="1">
@@ -17781,10 +17810,10 @@
         <v>1368</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>3367</v>
+        <v>3366</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>8</v>
@@ -17810,7 +17839,7 @@
         <v>1676</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>8</v>
@@ -17836,7 +17865,7 @@
         <v>1373</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>8</v>
@@ -17862,13 +17891,13 @@
         <v>1677</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="70.5" customHeight="1">
@@ -17885,7 +17914,7 @@
         <v>31</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>32</v>
@@ -17911,7 +17940,7 @@
         <v>34</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>35</v>
@@ -17963,16 +17992,16 @@
         <v>1377</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>3262</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>3263</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>3264</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>3265</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="61.5" customHeight="1">
@@ -17998,7 +18027,7 @@
         <v>8</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="40" customHeight="1">
@@ -18015,10 +18044,10 @@
         <v>1380</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>3267</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>3268</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>3269</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -18067,10 +18096,10 @@
         <v>48</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>3269</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>3270</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>3271</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -18119,10 +18148,10 @@
         <v>1386</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>3271</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>3272</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>3273</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>8</v>
@@ -18148,7 +18177,7 @@
         <v>54</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>8</v>
@@ -18174,7 +18203,7 @@
         <v>1678</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>8</v>
@@ -18197,10 +18226,10 @@
         <v>58</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>3275</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>3276</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>3277</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>8</v>
@@ -18223,10 +18252,10 @@
         <v>60</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>3277</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>3278</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>3279</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>8</v>
@@ -18258,7 +18287,7 @@
         <v>8</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="40" customHeight="1">
@@ -18275,7 +18304,7 @@
         <v>1396</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>1397</v>
@@ -18301,10 +18330,10 @@
         <v>1399</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>3281</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>3282</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>3283</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>8</v>
@@ -18327,13 +18356,13 @@
         <v>1401</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>3283</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>3284</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="4" t="s">
         <v>3285</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>3286</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>8</v>
@@ -18356,7 +18385,7 @@
         <v>69</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>8</v>
@@ -18379,13 +18408,13 @@
         <v>1404</v>
       </c>
       <c r="E26" s="4" t="s">
+        <v>3287</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>3288</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="4" t="s">
         <v>3289</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>3290</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>8</v>
@@ -18405,10 +18434,10 @@
         <v>1406</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>3290</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>3291</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>3292</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>72</v>
@@ -18434,10 +18463,10 @@
         <v>1647</v>
       </c>
       <c r="F28" s="4" t="s">
+        <v>3292</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>3293</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>3294</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>8</v>
@@ -18460,13 +18489,13 @@
         <v>1409</v>
       </c>
       <c r="F29" s="4" t="s">
+        <v>3294</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>3295</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>3296</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="40" customHeight="1">
@@ -18512,7 +18541,7 @@
         <v>1680</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>8</v>
@@ -18538,7 +18567,7 @@
         <v>1648</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>8</v>
@@ -18616,7 +18645,7 @@
         <v>1650</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>88</v>
@@ -18639,10 +18668,10 @@
         <v>1681</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>8</v>
@@ -18668,7 +18697,7 @@
         <v>1651</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>8</v>
@@ -18697,7 +18726,7 @@
         <v>1426</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>8</v>
@@ -18720,7 +18749,7 @@
         <v>1429</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>3369</v>
+        <v>3368</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>8</v>
@@ -18743,7 +18772,7 @@
         <v>97</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>1431</v>
@@ -18752,7 +18781,7 @@
         <v>8</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="40" customHeight="1">
@@ -18769,7 +18798,7 @@
         <v>99</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>1433</v>
@@ -18795,16 +18824,16 @@
         <v>101</v>
       </c>
       <c r="E42" s="4" t="s">
+        <v>3305</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>3306</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>3307</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>102</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="40" customHeight="1">
@@ -18824,10 +18853,10 @@
         <v>105</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>3370</v>
+        <v>3369</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>1436</v>
@@ -18856,7 +18885,7 @@
         <v>8</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="40" customHeight="1">
@@ -18876,13 +18905,13 @@
         <v>111</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>3371</v>
+        <v>3370</v>
       </c>
       <c r="G45" s="4" t="s">
+        <v>3310</v>
+      </c>
+      <c r="H45" s="4" t="s">
         <v>3311</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>3312</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="40" customHeight="1">
@@ -18928,10 +18957,10 @@
         <v>1682</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>3372</v>
+        <v>3371</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -18954,7 +18983,7 @@
         <v>8</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
@@ -18977,7 +19006,7 @@
         <v>1446</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>1447</v>
@@ -19000,7 +19029,7 @@
         <v>1448</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>1449</v>
@@ -19032,7 +19061,7 @@
         <v>121</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>8</v>
@@ -19058,10 +19087,10 @@
         <v>124</v>
       </c>
       <c r="F52" s="4" t="s">
+        <v>3317</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>3318</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>3319</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>1454</v>
@@ -19084,7 +19113,7 @@
         <v>1683</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>8</v>
@@ -19107,13 +19136,13 @@
         <v>130</v>
       </c>
       <c r="E54" s="4" t="s">
+        <v>3320</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>3321</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>3322</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>3323</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>8</v>
@@ -19133,10 +19162,10 @@
         <v>133</v>
       </c>
       <c r="E55" s="4" t="s">
+        <v>3323</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>3324</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>3325</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>8</v>
@@ -19159,7 +19188,7 @@
         <v>1455</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>1456</v>
@@ -19188,7 +19217,7 @@
         <v>1652</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>1458</v>
@@ -19211,7 +19240,7 @@
         <v>138</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>1460</v>
@@ -19240,10 +19269,10 @@
         <v>1462</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>1463</v>
@@ -19266,7 +19295,7 @@
         <v>1684</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>8</v>
@@ -19292,10 +19321,10 @@
         <v>1466</v>
       </c>
       <c r="F61" s="4" t="s">
+        <v>3329</v>
+      </c>
+      <c r="G61" s="4" t="s">
         <v>3330</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>3331</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>8</v>
@@ -19318,7 +19347,7 @@
         <v>1469</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>8</v>
@@ -19344,7 +19373,7 @@
         <v>1654</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>147</v>
@@ -19370,7 +19399,7 @@
         <v>1472</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>1473</v>
@@ -19396,7 +19425,7 @@
         <v>1655</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>1475</v>
@@ -19422,10 +19451,10 @@
         <v>1478</v>
       </c>
       <c r="F66" s="4" t="s">
+        <v>3335</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>3336</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>3337</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>8</v>
@@ -19448,7 +19477,7 @@
         <v>1480</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>8</v>
@@ -19474,10 +19503,10 @@
         <v>1483</v>
       </c>
       <c r="F68" s="4" t="s">
+        <v>3338</v>
+      </c>
+      <c r="G68" s="4" t="s">
         <v>3339</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>3340</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>8</v>
@@ -19500,10 +19529,10 @@
         <v>1486</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>1487</v>
@@ -19555,7 +19584,7 @@
         <v>1492</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>8</v>
@@ -19581,7 +19610,7 @@
         <v>1509</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>8</v>
@@ -19624,10 +19653,10 @@
         <v>1499</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>3343</v>
+      </c>
+      <c r="E74" s="4" t="s">
         <v>3344</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>3345</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>1500</v>
@@ -19659,7 +19688,7 @@
         <v>1511</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>8</v>
@@ -19685,7 +19714,7 @@
         <v>1512</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>8</v>
@@ -19711,7 +19740,7 @@
         <v>1513</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>3348</v>
+        <v>3347</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>8</v>
@@ -19737,7 +19766,7 @@
         <v>1514</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>8</v>
@@ -19757,7 +19786,7 @@
         <v>174</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>3350</v>
+        <v>3349</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>1516</v>
@@ -19806,10 +19835,10 @@
         <v>1522</v>
       </c>
       <c r="D81" s="4" t="s">
+        <v>3350</v>
+      </c>
+      <c r="E81" s="4" t="s">
         <v>3351</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>3352</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>1521</v>
@@ -19818,7 +19847,7 @@
         <v>8</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="40" customHeight="1">
@@ -19835,7 +19864,7 @@
         <v>178</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>1524</v>
@@ -19858,7 +19887,7 @@
         <v>1525</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>3355</v>
+        <v>3354</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>1659</v>
@@ -19896,7 +19925,7 @@
         <v>1531</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>3356</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="40" customHeight="1">
@@ -19945,10 +19974,10 @@
         <v>1536</v>
       </c>
       <c r="G86" s="4" t="s">
+        <v>3356</v>
+      </c>
+      <c r="H86" s="4" t="s">
         <v>3357</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>3358</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="40" customHeight="1">
@@ -19974,7 +20003,7 @@
         <v>1538</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>3359</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="40" customHeight="1">
@@ -20014,7 +20043,7 @@
         <v>1540</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>193</v>
@@ -20046,7 +20075,7 @@
         <v>1548</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>8</v>
@@ -20072,13 +20101,13 @@
         <v>1550</v>
       </c>
       <c r="F91" s="8" t="s">
+        <v>3361</v>
+      </c>
+      <c r="G91" s="4" t="s">
         <v>3362</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="H91" s="4" t="s">
         <v>3363</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>3364</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="40" customHeight="1">
@@ -20098,7 +20127,7 @@
         <v>1660</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>8</v>
@@ -20176,7 +20205,7 @@
         <v>1555</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>8</v>
@@ -20540,7 +20569,7 @@
         <v>1589</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="G109" s="4" t="s">
         <v>1590</v>
@@ -20904,7 +20933,7 @@
         <v>258</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>3377</v>
+        <v>3376</v>
       </c>
       <c r="G123" s="4" t="s">
         <v>1631</v>
@@ -21034,7 +21063,7 @@
         <v>1711</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>8</v>
@@ -21086,7 +21115,7 @@
         <v>1724</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>8</v>
@@ -21138,7 +21167,7 @@
         <v>1730</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>3380</v>
+        <v>3379</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>8</v>
@@ -21864,7 +21893,7 @@
         <v>1821</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>3381</v>
+        <v>3380</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>330</v>
@@ -21994,7 +22023,7 @@
         <v>1837</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>3382</v>
+        <v>3381</v>
       </c>
       <c r="G165" s="4" t="s">
         <v>1838</v>
@@ -22153,7 +22182,7 @@
         <v>1856</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>3383</v>
+        <v>3382</v>
       </c>
       <c r="H171" s="3" t="s">
         <v>8</v>
@@ -22358,7 +22387,7 @@
         <v>1882</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>3384</v>
+        <v>3383</v>
       </c>
       <c r="G179" s="4" t="s">
         <v>1883</v>
@@ -22595,7 +22624,7 @@
         <v>386</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
       <c r="H188" s="3" t="s">
         <v>8</v>
@@ -23164,7 +23193,7 @@
         <v>1998</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>3386</v>
+        <v>3385</v>
       </c>
       <c r="G210" s="4" t="s">
         <v>1999</v>
@@ -23216,7 +23245,7 @@
         <v>2004</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>3387</v>
+        <v>3386</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>2005</v>
@@ -23814,7 +23843,7 @@
         <v>475</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>2097</v>
@@ -23921,7 +23950,7 @@
         <v>2112</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="H239" s="3" t="s">
         <v>8</v>
@@ -23947,7 +23976,7 @@
         <v>2115</v>
       </c>
       <c r="G240" s="4" t="s">
-        <v>3390</v>
+        <v>3389</v>
       </c>
       <c r="H240" s="3" t="s">
         <v>8</v>
@@ -24152,7 +24181,7 @@
         <v>2136</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
       <c r="G248" s="3" t="s">
         <v>8</v>
@@ -24299,16 +24328,16 @@
         <v>517</v>
       </c>
       <c r="C254" s="4" t="s">
+        <v>3423</v>
+      </c>
+      <c r="D254" s="4" t="s">
         <v>2157</v>
       </c>
-      <c r="D254" s="4" t="s">
+      <c r="E254" s="4" t="s">
         <v>2158</v>
       </c>
-      <c r="E254" s="4" t="s">
+      <c r="F254" s="4" t="s">
         <v>2159</v>
-      </c>
-      <c r="F254" s="4" t="s">
-        <v>2160</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>8</v>
@@ -24325,16 +24354,16 @@
         <v>518</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="D255" s="4" t="s">
         <v>519</v>
       </c>
       <c r="E255" s="4" t="s">
+        <v>2161</v>
+      </c>
+      <c r="F255" s="4" t="s">
         <v>2162</v>
-      </c>
-      <c r="F255" s="4" t="s">
-        <v>2163</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>8</v>
@@ -24351,19 +24380,19 @@
         <v>520</v>
       </c>
       <c r="C256" s="4" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D256" s="4" t="s">
         <v>2164</v>
       </c>
-      <c r="D256" s="4" t="s">
+      <c r="E256" s="4" t="s">
         <v>2165</v>
       </c>
-      <c r="E256" s="4" t="s">
+      <c r="F256" s="4" t="s">
         <v>2166</v>
       </c>
-      <c r="F256" s="4" t="s">
+      <c r="G256" s="4" t="s">
         <v>2167</v>
-      </c>
-      <c r="G256" s="4" t="s">
-        <v>2168</v>
       </c>
       <c r="H256" s="3" t="s">
         <v>8</v>
@@ -24377,19 +24406,19 @@
         <v>521</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="D257" s="3" t="s">
         <v>1672</v>
       </c>
       <c r="E257" s="4" t="s">
+        <v>2169</v>
+      </c>
+      <c r="F257" s="4" t="s">
         <v>2170</v>
       </c>
-      <c r="F257" s="4" t="s">
-        <v>2171</v>
-      </c>
       <c r="G257" s="4" t="s">
-        <v>3392</v>
+        <v>3391</v>
       </c>
       <c r="H257" s="3" t="s">
         <v>8</v>
@@ -24403,19 +24432,19 @@
         <v>522</v>
       </c>
       <c r="C258" s="4" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D258" s="4" t="s">
         <v>2172</v>
       </c>
-      <c r="D258" s="4" t="s">
+      <c r="E258" s="4" t="s">
         <v>2173</v>
       </c>
-      <c r="E258" s="4" t="s">
+      <c r="F258" s="4" t="s">
         <v>2174</v>
       </c>
-      <c r="F258" s="4" t="s">
+      <c r="G258" s="4" t="s">
         <v>2175</v>
-      </c>
-      <c r="G258" s="4" t="s">
-        <v>2176</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>8</v>
@@ -24429,19 +24458,19 @@
         <v>523</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="D259" s="4" t="s">
         <v>524</v>
       </c>
       <c r="E259" s="4" t="s">
+        <v>2177</v>
+      </c>
+      <c r="F259" s="4" t="s">
         <v>2178</v>
       </c>
-      <c r="F259" s="4" t="s">
+      <c r="G259" s="4" t="s">
         <v>2179</v>
-      </c>
-      <c r="G259" s="4" t="s">
-        <v>2180</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>8</v>
@@ -24455,7 +24484,7 @@
         <v>525</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="D260" s="3" t="s">
         <v>526</v>
@@ -24464,10 +24493,10 @@
         <v>527</v>
       </c>
       <c r="F260" s="4" t="s">
+        <v>2181</v>
+      </c>
+      <c r="G260" s="4" t="s">
         <v>2182</v>
-      </c>
-      <c r="G260" s="4" t="s">
-        <v>2183</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>8</v>
@@ -24481,7 +24510,7 @@
         <v>528</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="D261" s="4" t="s">
         <v>529</v>
@@ -24490,7 +24519,7 @@
         <v>1717</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="G261" s="3" t="s">
         <v>8</v>
@@ -24507,16 +24536,16 @@
         <v>530</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="D262" s="3" t="s">
         <v>1673</v>
       </c>
       <c r="E262" s="4" t="s">
+        <v>2186</v>
+      </c>
+      <c r="F262" s="4" t="s">
         <v>2187</v>
-      </c>
-      <c r="F262" s="4" t="s">
-        <v>2188</v>
       </c>
       <c r="G262" s="3" t="s">
         <v>8</v>
@@ -24533,19 +24562,19 @@
         <v>531</v>
       </c>
       <c r="C263" s="4" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D263" s="4" t="s">
         <v>2189</v>
       </c>
-      <c r="D263" s="4" t="s">
+      <c r="E263" s="4" t="s">
         <v>2190</v>
       </c>
-      <c r="E263" s="4" t="s">
+      <c r="F263" s="4" t="s">
         <v>2191</v>
       </c>
-      <c r="F263" s="4" t="s">
+      <c r="G263" s="4" t="s">
         <v>2192</v>
-      </c>
-      <c r="G263" s="4" t="s">
-        <v>2193</v>
       </c>
       <c r="H263" s="3" t="s">
         <v>8</v>
@@ -24559,19 +24588,19 @@
         <v>532</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="D264" s="3" t="s">
         <v>1674</v>
       </c>
       <c r="E264" s="4" t="s">
+        <v>2194</v>
+      </c>
+      <c r="F264" s="4" t="s">
         <v>2195</v>
       </c>
-      <c r="F264" s="4" t="s">
+      <c r="G264" s="4" t="s">
         <v>2196</v>
-      </c>
-      <c r="G264" s="4" t="s">
-        <v>2197</v>
       </c>
       <c r="H264" s="3" t="s">
         <v>8</v>
@@ -24585,19 +24614,19 @@
         <v>533</v>
       </c>
       <c r="C265" s="4" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D265" s="4" t="s">
         <v>2198</v>
       </c>
-      <c r="D265" s="4" t="s">
+      <c r="E265" s="4" t="s">
         <v>2199</v>
       </c>
-      <c r="E265" s="4" t="s">
+      <c r="F265" s="4" t="s">
         <v>2200</v>
       </c>
-      <c r="F265" s="4" t="s">
+      <c r="G265" s="4" t="s">
         <v>2201</v>
-      </c>
-      <c r="G265" s="4" t="s">
-        <v>2202</v>
       </c>
       <c r="H265" s="3" t="s">
         <v>8</v>
@@ -24611,16 +24640,16 @@
         <v>534</v>
       </c>
       <c r="C266" s="4" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D266" s="4" t="s">
         <v>2203</v>
       </c>
-      <c r="D266" s="4" t="s">
+      <c r="E266" s="4" t="s">
         <v>2204</v>
       </c>
-      <c r="E266" s="4" t="s">
+      <c r="F266" s="4" t="s">
         <v>2205</v>
-      </c>
-      <c r="F266" s="4" t="s">
-        <v>2206</v>
       </c>
       <c r="G266" s="3" t="s">
         <v>8</v>
@@ -24637,7 +24666,7 @@
         <v>535</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="D267" s="3" t="s">
         <v>536</v>
@@ -24646,7 +24675,7 @@
         <v>537</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="G267" s="3" t="s">
         <v>8</v>
@@ -24663,16 +24692,16 @@
         <v>538</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="D268" s="3" t="s">
         <v>539</v>
       </c>
       <c r="E268" s="4" t="s">
+        <v>2209</v>
+      </c>
+      <c r="F268" s="4" t="s">
         <v>2210</v>
-      </c>
-      <c r="F268" s="4" t="s">
-        <v>2211</v>
       </c>
       <c r="G268" s="4" t="s">
         <v>540</v>
@@ -24689,7 +24718,7 @@
         <v>541</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="D269" s="3" t="s">
         <v>1675</v>
@@ -24698,10 +24727,10 @@
         <v>542</v>
       </c>
       <c r="F269" s="4" t="s">
+        <v>2212</v>
+      </c>
+      <c r="G269" s="4" t="s">
         <v>2213</v>
-      </c>
-      <c r="G269" s="4" t="s">
-        <v>2214</v>
       </c>
       <c r="H269" s="3" t="s">
         <v>8</v>
@@ -24715,16 +24744,16 @@
         <v>543</v>
       </c>
       <c r="C270" s="4" t="s">
+        <v>2214</v>
+      </c>
+      <c r="D270" s="4" t="s">
         <v>2215</v>
       </c>
-      <c r="D270" s="4" t="s">
+      <c r="E270" s="4" t="s">
         <v>2216</v>
       </c>
-      <c r="E270" s="4" t="s">
+      <c r="F270" s="4" t="s">
         <v>2217</v>
-      </c>
-      <c r="F270" s="4" t="s">
-        <v>2218</v>
       </c>
       <c r="G270" s="3" t="s">
         <v>8</v>
@@ -24747,13 +24776,13 @@
         <v>546</v>
       </c>
       <c r="E271" s="4" t="s">
+        <v>2218</v>
+      </c>
+      <c r="F271" s="4" t="s">
+        <v>3392</v>
+      </c>
+      <c r="G271" s="4" t="s">
         <v>2219</v>
-      </c>
-      <c r="F271" s="4" t="s">
-        <v>3393</v>
-      </c>
-      <c r="G271" s="4" t="s">
-        <v>2220</v>
       </c>
       <c r="H271" s="3" t="s">
         <v>8</v>
@@ -24767,19 +24796,19 @@
         <v>547</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="D272" s="4" t="s">
         <v>548</v>
       </c>
       <c r="E272" s="4" t="s">
+        <v>2221</v>
+      </c>
+      <c r="F272" s="4" t="s">
         <v>2222</v>
       </c>
-      <c r="F272" s="4" t="s">
+      <c r="G272" s="4" t="s">
         <v>2223</v>
-      </c>
-      <c r="G272" s="4" t="s">
-        <v>2224</v>
       </c>
       <c r="H272" s="3" t="s">
         <v>8</v>
@@ -24793,16 +24822,16 @@
         <v>549</v>
       </c>
       <c r="C273" s="4" t="s">
+        <v>2224</v>
+      </c>
+      <c r="D273" s="4" t="s">
         <v>2225</v>
       </c>
-      <c r="D273" s="4" t="s">
+      <c r="E273" s="4" t="s">
         <v>2226</v>
       </c>
-      <c r="E273" s="4" t="s">
+      <c r="F273" s="4" t="s">
         <v>2227</v>
-      </c>
-      <c r="F273" s="4" t="s">
-        <v>2228</v>
       </c>
       <c r="G273" s="3" t="s">
         <v>8</v>
@@ -24825,10 +24854,10 @@
         <v>552</v>
       </c>
       <c r="E274" s="4" t="s">
+        <v>2228</v>
+      </c>
+      <c r="F274" s="4" t="s">
         <v>2229</v>
-      </c>
-      <c r="F274" s="4" t="s">
-        <v>2230</v>
       </c>
       <c r="G274" s="4" t="s">
         <v>1317</v>
@@ -24845,16 +24874,16 @@
         <v>553</v>
       </c>
       <c r="C275" s="4" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D275" s="4" t="s">
         <v>2231</v>
       </c>
-      <c r="D275" s="4" t="s">
+      <c r="E275" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F275" s="4" t="s">
         <v>2232</v>
-      </c>
-      <c r="E275" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F275" s="4" t="s">
-        <v>2233</v>
       </c>
       <c r="G275" s="3" t="s">
         <v>8</v>
@@ -24871,16 +24900,16 @@
         <v>554</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="D276" s="4" t="s">
         <v>555</v>
       </c>
       <c r="E276" s="4" t="s">
+        <v>2234</v>
+      </c>
+      <c r="F276" s="4" t="s">
         <v>2235</v>
-      </c>
-      <c r="F276" s="4" t="s">
-        <v>2236</v>
       </c>
       <c r="G276" s="3" t="s">
         <v>8</v>
@@ -24897,16 +24926,16 @@
         <v>556</v>
       </c>
       <c r="C277" s="4" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D277" s="4" t="s">
         <v>2237</v>
       </c>
-      <c r="D277" s="4" t="s">
+      <c r="E277" s="4" t="s">
         <v>2238</v>
       </c>
-      <c r="E277" s="4" t="s">
+      <c r="F277" s="4" t="s">
         <v>2239</v>
-      </c>
-      <c r="F277" s="4" t="s">
-        <v>2240</v>
       </c>
       <c r="G277" s="3" t="s">
         <v>8</v>
@@ -24923,16 +24952,16 @@
         <v>557</v>
       </c>
       <c r="C278" s="4" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D278" s="4" t="s">
         <v>2241</v>
       </c>
-      <c r="D278" s="4" t="s">
+      <c r="E278" s="4" t="s">
         <v>2242</v>
       </c>
-      <c r="E278" s="4" t="s">
+      <c r="F278" s="4" t="s">
         <v>2243</v>
-      </c>
-      <c r="F278" s="4" t="s">
-        <v>2244</v>
       </c>
       <c r="G278" s="4" t="s">
         <v>558</v>
@@ -24949,16 +24978,16 @@
         <v>559</v>
       </c>
       <c r="C279" s="4" t="s">
+        <v>2244</v>
+      </c>
+      <c r="D279" s="4" t="s">
         <v>2245</v>
       </c>
-      <c r="D279" s="4" t="s">
+      <c r="E279" s="4" t="s">
         <v>2246</v>
       </c>
-      <c r="E279" s="4" t="s">
+      <c r="F279" s="4" t="s">
         <v>2247</v>
-      </c>
-      <c r="F279" s="4" t="s">
-        <v>2248</v>
       </c>
       <c r="G279" s="3" t="s">
         <v>8</v>
@@ -24975,19 +25004,19 @@
         <v>560</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>561</v>
       </c>
       <c r="E280" s="4" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="F280" s="4" t="s">
         <v>562</v>
       </c>
       <c r="G280" s="4" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="H280" s="3" t="s">
         <v>8</v>
@@ -25001,19 +25030,19 @@
         <v>563</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="D281" s="3" t="s">
         <v>564</v>
       </c>
       <c r="E281" s="4" t="s">
+        <v>2252</v>
+      </c>
+      <c r="F281" s="4" t="s">
         <v>2253</v>
       </c>
-      <c r="F281" s="4" t="s">
+      <c r="G281" s="4" t="s">
         <v>2254</v>
-      </c>
-      <c r="G281" s="4" t="s">
-        <v>2255</v>
       </c>
       <c r="H281" s="3" t="s">
         <v>8</v>
@@ -25027,16 +25056,16 @@
         <v>565</v>
       </c>
       <c r="C282" s="4" t="s">
+        <v>2255</v>
+      </c>
+      <c r="D282" s="4" t="s">
         <v>2256</v>
       </c>
-      <c r="D282" s="4" t="s">
+      <c r="E282" s="4" t="s">
         <v>2257</v>
       </c>
-      <c r="E282" s="4" t="s">
+      <c r="F282" s="4" t="s">
         <v>2258</v>
-      </c>
-      <c r="F282" s="4" t="s">
-        <v>2259</v>
       </c>
       <c r="G282" s="3" t="s">
         <v>8</v>
@@ -25053,16 +25082,16 @@
         <v>566</v>
       </c>
       <c r="C283" s="4" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="D283" s="4" t="s">
         <v>567</v>
       </c>
       <c r="E283" s="4" t="s">
+        <v>2260</v>
+      </c>
+      <c r="F283" s="4" t="s">
         <v>2261</v>
-      </c>
-      <c r="F283" s="4" t="s">
-        <v>2262</v>
       </c>
       <c r="G283" s="4" t="s">
         <v>568</v>
@@ -25079,7 +25108,7 @@
         <v>569</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="D284" s="4" t="s">
         <v>570</v>
@@ -25088,10 +25117,10 @@
         <v>571</v>
       </c>
       <c r="F284" s="4" t="s">
+        <v>2263</v>
+      </c>
+      <c r="G284" s="4" t="s">
         <v>2264</v>
-      </c>
-      <c r="G284" s="4" t="s">
-        <v>2265</v>
       </c>
       <c r="H284" s="3" t="s">
         <v>8</v>
@@ -25105,16 +25134,16 @@
         <v>572</v>
       </c>
       <c r="C285" s="4" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D285" s="4" t="s">
         <v>2267</v>
       </c>
-      <c r="D285" s="4" t="s">
+      <c r="E285" s="4" t="s">
         <v>2268</v>
       </c>
-      <c r="E285" s="4" t="s">
+      <c r="F285" s="4" t="s">
         <v>2269</v>
-      </c>
-      <c r="F285" s="4" t="s">
-        <v>2270</v>
       </c>
       <c r="G285" s="3" t="s">
         <v>8</v>
@@ -25131,16 +25160,16 @@
         <v>573</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="D286" s="4" t="s">
         <v>574</v>
       </c>
       <c r="E286" s="4" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F286" s="4" t="s">
         <v>2272</v>
-      </c>
-      <c r="F286" s="4" t="s">
-        <v>2273</v>
       </c>
       <c r="G286" s="3" t="s">
         <v>8</v>
@@ -25157,16 +25186,16 @@
         <v>575</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="D287" s="4" t="s">
         <v>576</v>
       </c>
       <c r="E287" s="4" t="s">
+        <v>2274</v>
+      </c>
+      <c r="F287" s="4" t="s">
         <v>2275</v>
-      </c>
-      <c r="F287" s="4" t="s">
-        <v>2276</v>
       </c>
       <c r="G287" s="3" t="s">
         <v>8</v>
@@ -25183,22 +25212,22 @@
         <v>577</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>576</v>
       </c>
       <c r="E288" s="4" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F288" s="4" t="s">
         <v>2277</v>
       </c>
-      <c r="F288" s="4" t="s">
+      <c r="G288" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H288" s="4" t="s">
         <v>2278</v>
-      </c>
-      <c r="G288" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H288" s="4" t="s">
-        <v>2279</v>
       </c>
     </row>
     <row r="289" spans="1:8" ht="40" customHeight="1">
@@ -25215,10 +25244,10 @@
         <v>580</v>
       </c>
       <c r="E289" s="4" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="G289" s="3" t="s">
         <v>8</v>
@@ -25241,13 +25270,13 @@
         <v>580</v>
       </c>
       <c r="E290" s="4" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F290" s="4" t="s">
+        <v>3393</v>
+      </c>
+      <c r="G290" s="4" t="s">
         <v>2281</v>
-      </c>
-      <c r="F290" s="4" t="s">
-        <v>3394</v>
-      </c>
-      <c r="G290" s="4" t="s">
-        <v>2282</v>
       </c>
       <c r="H290" s="3" t="s">
         <v>8</v>
@@ -25261,16 +25290,16 @@
         <v>582</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="D291" s="4" t="s">
         <v>583</v>
       </c>
       <c r="E291" s="4" t="s">
+        <v>2284</v>
+      </c>
+      <c r="F291" s="4" t="s">
         <v>2285</v>
-      </c>
-      <c r="F291" s="4" t="s">
-        <v>2286</v>
       </c>
       <c r="G291" s="3" t="s">
         <v>8</v>
@@ -25287,19 +25316,19 @@
         <v>584</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="D292" s="4" t="s">
         <v>585</v>
       </c>
       <c r="E292" s="4" t="s">
+        <v>2287</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>3394</v>
+      </c>
+      <c r="G292" s="4" t="s">
         <v>2288</v>
-      </c>
-      <c r="F292" s="4" t="s">
-        <v>3395</v>
-      </c>
-      <c r="G292" s="4" t="s">
-        <v>2289</v>
       </c>
       <c r="H292" s="3" t="s">
         <v>8</v>
@@ -25313,16 +25342,16 @@
         <v>586</v>
       </c>
       <c r="C293" s="4" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D293" s="4" t="s">
         <v>2290</v>
-      </c>
-      <c r="D293" s="4" t="s">
-        <v>2291</v>
       </c>
       <c r="E293" s="4" t="s">
         <v>587</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="G293" s="3" t="s">
         <v>8</v>
@@ -25339,16 +25368,16 @@
         <v>588</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="D294" s="4" t="s">
         <v>1364</v>
       </c>
       <c r="E294" s="4" t="s">
+        <v>2292</v>
+      </c>
+      <c r="F294" s="4" t="s">
         <v>2293</v>
-      </c>
-      <c r="F294" s="4" t="s">
-        <v>2294</v>
       </c>
       <c r="G294" s="3" t="s">
         <v>8</v>
@@ -25365,16 +25394,16 @@
         <v>421</v>
       </c>
       <c r="C295" s="4" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D295" s="4" t="s">
         <v>2295</v>
       </c>
-      <c r="D295" s="4" t="s">
+      <c r="E295" s="4" t="s">
         <v>2296</v>
       </c>
-      <c r="E295" s="4" t="s">
+      <c r="F295" s="4" t="s">
         <v>2297</v>
-      </c>
-      <c r="F295" s="4" t="s">
-        <v>2298</v>
       </c>
       <c r="G295" s="3" t="s">
         <v>8</v>
@@ -25391,19 +25420,19 @@
         <v>589</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="D296" s="3" t="s">
         <v>590</v>
       </c>
       <c r="E296" s="4" t="s">
+        <v>2299</v>
+      </c>
+      <c r="F296" s="4" t="s">
         <v>2300</v>
       </c>
-      <c r="F296" s="4" t="s">
+      <c r="G296" s="4" t="s">
         <v>2301</v>
-      </c>
-      <c r="G296" s="4" t="s">
-        <v>2302</v>
       </c>
       <c r="H296" s="3" t="s">
         <v>8</v>
@@ -25417,16 +25446,16 @@
         <v>591</v>
       </c>
       <c r="C297" s="4" t="s">
+        <v>2302</v>
+      </c>
+      <c r="D297" s="4" t="s">
         <v>2303</v>
       </c>
-      <c r="D297" s="4" t="s">
+      <c r="E297" s="4" t="s">
         <v>2304</v>
       </c>
-      <c r="E297" s="4" t="s">
+      <c r="F297" s="4" t="s">
         <v>2305</v>
-      </c>
-      <c r="F297" s="4" t="s">
-        <v>2306</v>
       </c>
       <c r="G297" s="3" t="s">
         <v>8</v>
@@ -25443,16 +25472,16 @@
         <v>4213</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="D298" s="3" t="s">
         <v>592</v>
       </c>
       <c r="E298" s="4" t="s">
+        <v>2307</v>
+      </c>
+      <c r="F298" s="4" t="s">
         <v>2308</v>
-      </c>
-      <c r="F298" s="4" t="s">
-        <v>2309</v>
       </c>
       <c r="G298" s="3" t="s">
         <v>8</v>
@@ -25469,16 +25498,16 @@
         <v>593</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>1365</v>
       </c>
       <c r="E299" s="4" t="s">
+        <v>2310</v>
+      </c>
+      <c r="F299" s="4" t="s">
         <v>2311</v>
-      </c>
-      <c r="F299" s="4" t="s">
-        <v>2312</v>
       </c>
       <c r="G299" s="3" t="s">
         <v>8</v>
@@ -25495,16 +25524,16 @@
         <v>594</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="D300" s="4" t="s">
         <v>595</v>
       </c>
       <c r="E300" s="4" t="s">
+        <v>2313</v>
+      </c>
+      <c r="F300" s="4" t="s">
         <v>2314</v>
-      </c>
-      <c r="F300" s="4" t="s">
-        <v>2315</v>
       </c>
       <c r="G300" s="3" t="s">
         <v>8</v>
@@ -25521,19 +25550,19 @@
         <v>596</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="D301" s="4" t="s">
+        <v>2315</v>
+      </c>
+      <c r="E301" s="4" t="s">
         <v>2316</v>
       </c>
-      <c r="E301" s="4" t="s">
+      <c r="F301" s="4" t="s">
         <v>2317</v>
       </c>
-      <c r="F301" s="4" t="s">
+      <c r="G301" s="4" t="s">
         <v>2318</v>
-      </c>
-      <c r="G301" s="4" t="s">
-        <v>2319</v>
       </c>
       <c r="H301" s="3" t="s">
         <v>8</v>
@@ -25547,10 +25576,10 @@
         <v>597</v>
       </c>
       <c r="C302" s="4" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D302" s="4" t="s">
         <v>2321</v>
-      </c>
-      <c r="D302" s="4" t="s">
-        <v>2322</v>
       </c>
       <c r="E302" s="4" t="s">
         <v>598</v>
@@ -25559,7 +25588,7 @@
         <v>599</v>
       </c>
       <c r="G302" s="4" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="H302" s="4" t="s">
         <v>600</v>
@@ -25573,7 +25602,7 @@
         <v>601</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>602</v>
@@ -25582,7 +25611,7 @@
         <v>603</v>
       </c>
       <c r="F303" s="4" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="G303" s="3" t="s">
         <v>8</v>
@@ -25599,7 +25628,7 @@
         <v>604</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>605</v>
@@ -25608,7 +25637,7 @@
         <v>606</v>
       </c>
       <c r="F304" s="4" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="G304" s="3" t="s">
         <v>8</v>
@@ -25625,16 +25654,16 @@
         <v>607</v>
       </c>
       <c r="C305" s="4" t="s">
+        <v>2326</v>
+      </c>
+      <c r="D305" s="4" t="s">
         <v>2327</v>
       </c>
-      <c r="D305" s="4" t="s">
+      <c r="E305" s="4" t="s">
         <v>2328</v>
       </c>
-      <c r="E305" s="4" t="s">
+      <c r="F305" s="4" t="s">
         <v>2329</v>
-      </c>
-      <c r="F305" s="4" t="s">
-        <v>2330</v>
       </c>
       <c r="G305" s="3" t="s">
         <v>8</v>
@@ -25654,16 +25683,16 @@
         <v>609</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="E306" s="4" t="s">
         <v>610</v>
       </c>
       <c r="F306" s="4" t="s">
+        <v>2331</v>
+      </c>
+      <c r="G306" s="4" t="s">
         <v>2332</v>
-      </c>
-      <c r="G306" s="4" t="s">
-        <v>2333</v>
       </c>
       <c r="H306" s="3" t="s">
         <v>8</v>
@@ -25677,7 +25706,7 @@
         <v>611</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="D307" s="3" t="s">
         <v>612</v>
@@ -25686,7 +25715,7 @@
         <v>613</v>
       </c>
       <c r="F307" s="4" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="G307" s="3" t="s">
         <v>8</v>
@@ -25703,16 +25732,16 @@
         <v>614</v>
       </c>
       <c r="C308" s="4" t="s">
+        <v>2335</v>
+      </c>
+      <c r="D308" s="4" t="s">
         <v>2336</v>
       </c>
-      <c r="D308" s="4" t="s">
+      <c r="E308" s="4" t="s">
         <v>2337</v>
       </c>
-      <c r="E308" s="4" t="s">
+      <c r="F308" s="4" t="s">
         <v>2338</v>
-      </c>
-      <c r="F308" s="4" t="s">
-        <v>2339</v>
       </c>
       <c r="G308" s="3" t="s">
         <v>8</v>
@@ -25729,16 +25758,16 @@
         <v>615</v>
       </c>
       <c r="C309" s="4" t="s">
+        <v>2339</v>
+      </c>
+      <c r="D309" s="4" t="s">
         <v>2340</v>
       </c>
-      <c r="D309" s="4" t="s">
+      <c r="E309" s="4" t="s">
         <v>2341</v>
       </c>
-      <c r="E309" s="4" t="s">
+      <c r="F309" s="4" t="s">
         <v>2342</v>
-      </c>
-      <c r="F309" s="4" t="s">
-        <v>2343</v>
       </c>
       <c r="G309" s="3" t="s">
         <v>8</v>
@@ -25755,7 +25784,7 @@
         <v>616</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>617</v>
@@ -25764,7 +25793,7 @@
         <v>618</v>
       </c>
       <c r="F310" s="4" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="G310" s="3" t="s">
         <v>8</v>
@@ -25781,19 +25810,19 @@
         <v>619</v>
       </c>
       <c r="C311" s="4" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D311" s="4" t="s">
         <v>2346</v>
       </c>
-      <c r="D311" s="4" t="s">
+      <c r="E311" s="4" t="s">
         <v>2347</v>
       </c>
-      <c r="E311" s="4" t="s">
+      <c r="F311" s="4" t="s">
         <v>2348</v>
       </c>
-      <c r="F311" s="4" t="s">
+      <c r="G311" s="4" t="s">
         <v>2349</v>
-      </c>
-      <c r="G311" s="4" t="s">
-        <v>2350</v>
       </c>
       <c r="H311" s="3" t="s">
         <v>8</v>
@@ -25807,19 +25836,19 @@
         <v>620</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>621</v>
       </c>
       <c r="E312" s="4" t="s">
+        <v>2351</v>
+      </c>
+      <c r="F312" s="4" t="s">
         <v>2352</v>
       </c>
-      <c r="F312" s="4" t="s">
+      <c r="G312" s="4" t="s">
         <v>2353</v>
-      </c>
-      <c r="G312" s="4" t="s">
-        <v>2354</v>
       </c>
       <c r="H312" s="3" t="s">
         <v>8</v>
@@ -25833,19 +25862,19 @@
         <v>622</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>623</v>
       </c>
       <c r="E313" s="4" t="s">
+        <v>2355</v>
+      </c>
+      <c r="F313" s="4" t="s">
         <v>2356</v>
       </c>
-      <c r="F313" s="4" t="s">
+      <c r="G313" s="4" t="s">
         <v>2357</v>
-      </c>
-      <c r="G313" s="4" t="s">
-        <v>2358</v>
       </c>
       <c r="H313" s="3" t="s">
         <v>8</v>
@@ -25859,16 +25888,16 @@
         <v>624</v>
       </c>
       <c r="C314" s="4" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D314" s="4" t="s">
         <v>2359</v>
       </c>
-      <c r="D314" s="4" t="s">
+      <c r="E314" s="4" t="s">
         <v>2360</v>
       </c>
-      <c r="E314" s="4" t="s">
+      <c r="F314" s="4" t="s">
         <v>2361</v>
-      </c>
-      <c r="F314" s="4" t="s">
-        <v>2362</v>
       </c>
       <c r="G314" s="3" t="s">
         <v>8</v>
@@ -25885,7 +25914,7 @@
         <v>625</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>626</v>
@@ -25894,7 +25923,7 @@
         <v>627</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="G315" s="3" t="s">
         <v>8</v>
@@ -25911,7 +25940,7 @@
         <v>628</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>1718</v>
@@ -25920,7 +25949,7 @@
         <v>1719</v>
       </c>
       <c r="F316" s="4" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="G316" s="3" t="s">
         <v>8</v>
@@ -25937,7 +25966,7 @@
         <v>629</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>630</v>
@@ -25946,7 +25975,7 @@
         <v>631</v>
       </c>
       <c r="F317" s="4" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="G317" s="3" t="s">
         <v>8</v>
@@ -25963,16 +25992,16 @@
         <v>632</v>
       </c>
       <c r="C318" s="4" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D318" s="4" t="s">
         <v>2369</v>
       </c>
-      <c r="D318" s="4" t="s">
+      <c r="E318" s="4" t="s">
         <v>2370</v>
       </c>
-      <c r="E318" s="4" t="s">
+      <c r="F318" s="4" t="s">
         <v>2371</v>
-      </c>
-      <c r="F318" s="4" t="s">
-        <v>2372</v>
       </c>
       <c r="G318" s="3" t="s">
         <v>8</v>
@@ -25989,16 +26018,16 @@
         <v>633</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="E319" s="4" t="s">
         <v>634</v>
       </c>
       <c r="F319" s="4" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="G319" s="3" t="s">
         <v>8</v>
@@ -26015,16 +26044,16 @@
         <v>635</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>636</v>
       </c>
       <c r="E320" s="4" t="s">
+        <v>2375</v>
+      </c>
+      <c r="F320" s="4" t="s">
         <v>2376</v>
-      </c>
-      <c r="F320" s="4" t="s">
-        <v>2377</v>
       </c>
       <c r="G320" s="3" t="s">
         <v>8</v>
@@ -26041,7 +26070,7 @@
         <v>637</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>638</v>
@@ -26050,7 +26079,7 @@
         <v>639</v>
       </c>
       <c r="F321" s="4" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="G321" s="3" t="s">
         <v>8</v>
@@ -26067,16 +26096,16 @@
         <v>640</v>
       </c>
       <c r="C322" s="4" t="s">
+        <v>2379</v>
+      </c>
+      <c r="D322" s="4" t="s">
         <v>2380</v>
-      </c>
-      <c r="D322" s="4" t="s">
-        <v>2381</v>
       </c>
       <c r="E322" s="4" t="s">
         <v>641</v>
       </c>
       <c r="F322" s="4" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="G322" s="3" t="s">
         <v>8</v>
@@ -26093,13 +26122,13 @@
         <v>642</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="D323" s="3" t="s">
         <v>643</v>
       </c>
       <c r="E323" s="4" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="F323" s="4" t="s">
         <v>644</v>
@@ -26119,16 +26148,16 @@
         <v>645</v>
       </c>
       <c r="C324" s="4" t="s">
+        <v>2384</v>
+      </c>
+      <c r="D324" s="4" t="s">
         <v>2385</v>
       </c>
-      <c r="D324" s="4" t="s">
+      <c r="E324" s="4" t="s">
         <v>2386</v>
       </c>
-      <c r="E324" s="4" t="s">
+      <c r="F324" s="4" t="s">
         <v>2387</v>
-      </c>
-      <c r="F324" s="4" t="s">
-        <v>2388</v>
       </c>
       <c r="G324" s="3" t="s">
         <v>8</v>
@@ -26145,16 +26174,16 @@
         <v>646</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>647</v>
       </c>
       <c r="E325" s="4" t="s">
+        <v>2389</v>
+      </c>
+      <c r="F325" s="4" t="s">
         <v>2390</v>
-      </c>
-      <c r="F325" s="4" t="s">
-        <v>2391</v>
       </c>
       <c r="G325" s="3" t="s">
         <v>8</v>
@@ -26171,16 +26200,16 @@
         <v>648</v>
       </c>
       <c r="C326" s="4" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D326" s="4" t="s">
         <v>2392</v>
       </c>
-      <c r="D326" s="4" t="s">
+      <c r="E326" s="4" t="s">
         <v>2393</v>
       </c>
-      <c r="E326" s="4" t="s">
+      <c r="F326" s="4" t="s">
         <v>2394</v>
-      </c>
-      <c r="F326" s="4" t="s">
-        <v>2395</v>
       </c>
       <c r="G326" s="3" t="s">
         <v>8</v>
@@ -26197,16 +26226,16 @@
         <v>649</v>
       </c>
       <c r="C327" s="4" t="s">
+        <v>2395</v>
+      </c>
+      <c r="D327" s="4" t="s">
         <v>2396</v>
       </c>
-      <c r="D327" s="4" t="s">
+      <c r="E327" s="4" t="s">
         <v>2397</v>
       </c>
-      <c r="E327" s="4" t="s">
+      <c r="F327" s="4" t="s">
         <v>2398</v>
-      </c>
-      <c r="F327" s="4" t="s">
-        <v>2399</v>
       </c>
       <c r="G327" s="3" t="s">
         <v>8</v>
@@ -26223,16 +26252,16 @@
         <v>650</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>651</v>
       </c>
       <c r="E328" s="4" t="s">
+        <v>2400</v>
+      </c>
+      <c r="F328" s="4" t="s">
         <v>2401</v>
-      </c>
-      <c r="F328" s="4" t="s">
-        <v>2402</v>
       </c>
       <c r="G328" s="3" t="s">
         <v>8</v>
@@ -26249,7 +26278,7 @@
         <v>652</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>653</v>
@@ -26275,13 +26304,13 @@
         <v>656</v>
       </c>
       <c r="C330" s="4" t="s">
+        <v>2403</v>
+      </c>
+      <c r="D330" s="4" t="s">
         <v>2404</v>
       </c>
-      <c r="D330" s="4" t="s">
+      <c r="E330" s="4" t="s">
         <v>2405</v>
-      </c>
-      <c r="E330" s="4" t="s">
-        <v>2406</v>
       </c>
       <c r="F330" s="4" t="s">
         <v>657</v>
@@ -26301,7 +26330,7 @@
         <v>658</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="D331" s="3" t="s">
         <v>659</v>
@@ -26327,13 +26356,13 @@
         <v>662</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>663</v>
       </c>
       <c r="E332" s="4" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="F332" s="4" t="s">
         <v>664</v>
@@ -26356,10 +26385,10 @@
         <v>666</v>
       </c>
       <c r="D333" s="4" t="s">
+        <v>2409</v>
+      </c>
+      <c r="E333" s="4" t="s">
         <v>2410</v>
-      </c>
-      <c r="E333" s="4" t="s">
-        <v>2411</v>
       </c>
       <c r="F333" s="4" t="s">
         <v>667</v>
@@ -26382,10 +26411,10 @@
         <v>666</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="E334" s="4" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="F334" s="4" t="s">
         <v>669</v>
@@ -26405,13 +26434,13 @@
         <v>671</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>672</v>
       </c>
       <c r="E335" s="4" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="F335" s="4" t="s">
         <v>673</v>
@@ -26437,10 +26466,10 @@
         <v>676</v>
       </c>
       <c r="E336" s="4" t="s">
+        <v>2414</v>
+      </c>
+      <c r="F336" s="4" t="s">
         <v>2415</v>
-      </c>
-      <c r="F336" s="4" t="s">
-        <v>2416</v>
       </c>
       <c r="G336" s="4" t="s">
         <v>677</v>
@@ -26469,10 +26498,10 @@
         <v>682</v>
       </c>
       <c r="G337" s="4" t="s">
+        <v>2416</v>
+      </c>
+      <c r="H337" s="4" t="s">
         <v>2417</v>
-      </c>
-      <c r="H337" s="4" t="s">
-        <v>2418</v>
       </c>
     </row>
     <row r="338" spans="1:8" ht="40" customHeight="1">
@@ -26483,16 +26512,16 @@
         <v>683</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>684</v>
       </c>
       <c r="E338" s="4" t="s">
+        <v>2419</v>
+      </c>
+      <c r="F338" s="4" t="s">
         <v>2420</v>
-      </c>
-      <c r="F338" s="4" t="s">
-        <v>2421</v>
       </c>
       <c r="G338" s="3" t="s">
         <v>8</v>
@@ -26518,7 +26547,7 @@
         <v>688</v>
       </c>
       <c r="F339" s="4" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="G339" s="3" t="s">
         <v>8</v>
@@ -26535,16 +26564,16 @@
         <v>689</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>690</v>
       </c>
       <c r="E340" s="4" t="s">
+        <v>2423</v>
+      </c>
+      <c r="F340" s="4" t="s">
         <v>2424</v>
-      </c>
-      <c r="F340" s="4" t="s">
-        <v>2425</v>
       </c>
       <c r="G340" s="3" t="s">
         <v>8</v>
@@ -26561,16 +26590,16 @@
         <v>691</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="E341" s="4" t="s">
         <v>692</v>
       </c>
       <c r="F341" s="4" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="G341" s="3" t="s">
         <v>8</v>
@@ -26587,19 +26616,19 @@
         <v>693</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="D342" s="4" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E342" s="4" t="s">
         <v>2431</v>
-      </c>
-      <c r="E342" s="4" t="s">
-        <v>2432</v>
       </c>
       <c r="F342" s="4" t="s">
         <v>694</v>
       </c>
       <c r="G342" s="4" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="H342" s="3" t="s">
         <v>8</v>
@@ -26613,7 +26642,7 @@
         <v>695</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="D343" s="8" t="s">
         <v>1360</v>
@@ -26628,7 +26657,7 @@
         <v>698</v>
       </c>
       <c r="H343" s="4" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="344" spans="1:8" ht="40" customHeight="1">
@@ -26639,7 +26668,7 @@
         <v>699</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>700</v>
@@ -26665,16 +26694,16 @@
         <v>703</v>
       </c>
       <c r="C345" s="4" t="s">
+        <v>2435</v>
+      </c>
+      <c r="D345" s="4" t="s">
         <v>2436</v>
-      </c>
-      <c r="D345" s="4" t="s">
-        <v>2437</v>
       </c>
       <c r="E345" s="4" t="s">
         <v>704</v>
       </c>
       <c r="F345" s="4" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="G345" s="3" t="s">
         <v>8</v>
@@ -26691,7 +26720,7 @@
         <v>705</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>706</v>
@@ -26717,7 +26746,7 @@
         <v>710</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>711</v>
@@ -26729,7 +26758,7 @@
         <v>713</v>
       </c>
       <c r="G347" s="4" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="H347" s="3" t="s">
         <v>8</v>
@@ -26743,7 +26772,7 @@
         <v>714</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="D348" s="3" t="s">
         <v>715</v>
@@ -26769,16 +26798,16 @@
         <v>718</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="D349" s="3" t="s">
         <v>719</v>
       </c>
       <c r="E349" s="4" t="s">
+        <v>2443</v>
+      </c>
+      <c r="F349" s="4" t="s">
         <v>2444</v>
-      </c>
-      <c r="F349" s="4" t="s">
-        <v>2445</v>
       </c>
       <c r="G349" s="3" t="s">
         <v>8</v>
@@ -26795,7 +26824,7 @@
         <v>720</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="D350" s="3" t="s">
         <v>721</v>
@@ -26821,22 +26850,22 @@
         <v>725</v>
       </c>
       <c r="C351" s="4" t="s">
+        <v>2446</v>
+      </c>
+      <c r="D351" s="4" t="s">
         <v>2447</v>
-      </c>
-      <c r="D351" s="4" t="s">
-        <v>2448</v>
       </c>
       <c r="E351" s="4" t="s">
         <v>726</v>
       </c>
       <c r="F351" s="4" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="G351" s="4" t="s">
         <v>727</v>
       </c>
       <c r="H351" s="4" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="352" spans="1:8" ht="40" customHeight="1">
@@ -26847,22 +26876,22 @@
         <v>728</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>729</v>
       </c>
       <c r="E352" s="4" t="s">
+        <v>2451</v>
+      </c>
+      <c r="F352" s="4" t="s">
         <v>2452</v>
       </c>
-      <c r="F352" s="4" t="s">
+      <c r="G352" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H352" s="4" t="s">
         <v>2453</v>
-      </c>
-      <c r="G352" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H352" s="4" t="s">
-        <v>2454</v>
       </c>
     </row>
     <row r="353" spans="1:8" ht="40" customHeight="1">
@@ -26873,22 +26902,22 @@
         <v>730</v>
       </c>
       <c r="C353" s="4" t="s">
+        <v>2454</v>
+      </c>
+      <c r="D353" s="4" t="s">
         <v>2455</v>
       </c>
-      <c r="D353" s="4" t="s">
+      <c r="E353" s="4" t="s">
         <v>2456</v>
       </c>
-      <c r="E353" s="4" t="s">
+      <c r="F353" s="4" t="s">
         <v>2457</v>
       </c>
-      <c r="F353" s="4" t="s">
-        <v>2458</v>
-      </c>
       <c r="G353" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H353" s="4" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="354" spans="1:8" ht="40" customHeight="1">
@@ -26899,22 +26928,22 @@
         <v>731</v>
       </c>
       <c r="C354" s="4" t="s">
+        <v>2458</v>
+      </c>
+      <c r="D354" s="4" t="s">
         <v>2459</v>
       </c>
-      <c r="D354" s="4" t="s">
+      <c r="E354" s="4" t="s">
         <v>2460</v>
       </c>
-      <c r="E354" s="4" t="s">
+      <c r="F354" s="4" t="s">
         <v>2461</v>
       </c>
-      <c r="F354" s="4" t="s">
+      <c r="G354" s="4" t="s">
         <v>2462</v>
       </c>
-      <c r="G354" s="4" t="s">
-        <v>2463</v>
-      </c>
       <c r="H354" s="4" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="355" spans="1:8" ht="40" customHeight="1">
@@ -26925,22 +26954,22 @@
         <v>732</v>
       </c>
       <c r="C355" s="4" t="s">
+        <v>2465</v>
+      </c>
+      <c r="D355" s="4" t="s">
         <v>2466</v>
       </c>
-      <c r="D355" s="4" t="s">
+      <c r="E355" s="4" t="s">
         <v>2467</v>
       </c>
-      <c r="E355" s="4" t="s">
+      <c r="F355" s="4" t="s">
         <v>2468</v>
       </c>
-      <c r="F355" s="4" t="s">
+      <c r="G355" s="4" t="s">
         <v>2469</v>
       </c>
-      <c r="G355" s="4" t="s">
+      <c r="H355" s="4" t="s">
         <v>2470</v>
-      </c>
-      <c r="H355" s="4" t="s">
-        <v>2471</v>
       </c>
     </row>
     <row r="356" spans="1:8" ht="40" customHeight="1">
@@ -26951,16 +26980,16 @@
         <v>733</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>3423</v>
+        <v>3422</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>734</v>
       </c>
       <c r="E356" s="4" t="s">
+        <v>2471</v>
+      </c>
+      <c r="F356" s="4" t="s">
         <v>2472</v>
-      </c>
-      <c r="F356" s="4" t="s">
-        <v>2473</v>
       </c>
       <c r="G356" s="3" t="s">
         <v>8</v>
@@ -26983,16 +27012,16 @@
         <v>737</v>
       </c>
       <c r="E357" s="4" t="s">
+        <v>2473</v>
+      </c>
+      <c r="F357" s="4" t="s">
         <v>2474</v>
       </c>
-      <c r="F357" s="4" t="s">
+      <c r="G357" s="4" t="s">
         <v>2475</v>
       </c>
-      <c r="G357" s="4" t="s">
+      <c r="H357" s="4" t="s">
         <v>2476</v>
-      </c>
-      <c r="H357" s="4" t="s">
-        <v>2477</v>
       </c>
     </row>
     <row r="358" spans="1:8" ht="40" customHeight="1">
@@ -27003,22 +27032,22 @@
         <v>738</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>739</v>
       </c>
       <c r="E358" s="4" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="F358" s="4" t="s">
         <v>740</v>
       </c>
       <c r="G358" s="4" t="s">
+        <v>2479</v>
+      </c>
+      <c r="H358" s="4" t="s">
         <v>2480</v>
-      </c>
-      <c r="H358" s="4" t="s">
-        <v>2481</v>
       </c>
     </row>
     <row r="359" spans="1:8" ht="40" customHeight="1">
@@ -27029,7 +27058,7 @@
         <v>741</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>742</v>
@@ -27055,16 +27084,16 @@
         <v>746</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>747</v>
       </c>
       <c r="E360" s="4" t="s">
+        <v>2483</v>
+      </c>
+      <c r="F360" s="4" t="s">
         <v>2484</v>
-      </c>
-      <c r="F360" s="4" t="s">
-        <v>2485</v>
       </c>
       <c r="G360" s="3" t="s">
         <v>8</v>
@@ -27081,16 +27110,16 @@
         <v>748</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>747</v>
       </c>
       <c r="E361" s="4" t="s">
+        <v>2485</v>
+      </c>
+      <c r="F361" s="4" t="s">
         <v>2486</v>
-      </c>
-      <c r="F361" s="4" t="s">
-        <v>2487</v>
       </c>
       <c r="G361" s="4" t="s">
         <v>749</v>
@@ -27107,22 +27136,22 @@
         <v>750</v>
       </c>
       <c r="C362" s="4" t="s">
+        <v>2487</v>
+      </c>
+      <c r="D362" s="4" t="s">
         <v>2488</v>
       </c>
-      <c r="D362" s="4" t="s">
+      <c r="E362" s="4" t="s">
         <v>2489</v>
       </c>
-      <c r="E362" s="4" t="s">
+      <c r="F362" s="4" t="s">
         <v>2490</v>
       </c>
-      <c r="F362" s="4" t="s">
+      <c r="G362" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H362" s="4" t="s">
         <v>2491</v>
-      </c>
-      <c r="G362" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H362" s="4" t="s">
-        <v>2492</v>
       </c>
     </row>
     <row r="363" spans="1:8" ht="40" customHeight="1">
@@ -27133,13 +27162,13 @@
         <v>751</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="D363" s="3" t="s">
         <v>752</v>
       </c>
       <c r="E363" s="4" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="F363" s="4" t="s">
         <v>753</v>
@@ -27159,7 +27188,7 @@
         <v>755</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="D364" s="3" t="s">
         <v>756</v>
@@ -27171,7 +27200,7 @@
         <v>758</v>
       </c>
       <c r="G364" s="4" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="H364" s="3" t="s">
         <v>8</v>
@@ -27185,16 +27214,16 @@
         <v>759</v>
       </c>
       <c r="C365" s="4" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D365" s="4" t="s">
         <v>2497</v>
-      </c>
-      <c r="D365" s="4" t="s">
-        <v>2498</v>
       </c>
       <c r="E365" s="4" t="s">
         <v>760</v>
       </c>
       <c r="F365" s="4" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="G365" s="4" t="s">
         <v>761</v>
@@ -27211,7 +27240,7 @@
         <v>762</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>763</v>
@@ -27237,22 +27266,22 @@
         <v>767</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>768</v>
       </c>
       <c r="E367" s="4" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="F367" s="4" t="s">
         <v>769</v>
       </c>
       <c r="G367" s="4" t="s">
+        <v>2502</v>
+      </c>
+      <c r="H367" s="4" t="s">
         <v>2503</v>
-      </c>
-      <c r="H367" s="4" t="s">
-        <v>2504</v>
       </c>
     </row>
     <row r="368" spans="1:8" ht="40" customHeight="1">
@@ -27263,22 +27292,22 @@
         <v>770</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>771</v>
       </c>
       <c r="E368" s="4" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="F368" s="4" t="s">
         <v>772</v>
       </c>
       <c r="G368" s="4" t="s">
+        <v>2506</v>
+      </c>
+      <c r="H368" s="4" t="s">
         <v>2507</v>
-      </c>
-      <c r="H368" s="4" t="s">
-        <v>2508</v>
       </c>
     </row>
     <row r="369" spans="1:8" ht="40" customHeight="1">
@@ -27289,10 +27318,10 @@
         <v>773</v>
       </c>
       <c r="C369" s="4" t="s">
+        <v>2508</v>
+      </c>
+      <c r="D369" s="4" t="s">
         <v>2509</v>
-      </c>
-      <c r="D369" s="4" t="s">
-        <v>2510</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>8</v>
@@ -27315,16 +27344,16 @@
         <v>775</v>
       </c>
       <c r="C370" s="4" t="s">
+        <v>2510</v>
+      </c>
+      <c r="D370" s="4" t="s">
         <v>2511</v>
-      </c>
-      <c r="D370" s="4" t="s">
-        <v>2512</v>
       </c>
       <c r="E370" s="4" t="s">
         <v>776</v>
       </c>
       <c r="F370" s="4" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="G370" s="3" t="s">
         <v>8</v>
@@ -27341,13 +27370,13 @@
         <v>777</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="D371" s="3" t="s">
         <v>778</v>
       </c>
       <c r="E371" s="4" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="F371" s="4" t="s">
         <v>779</v>
@@ -27367,19 +27396,19 @@
         <v>780</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>781</v>
       </c>
       <c r="E372" s="4" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="F372" s="4" t="s">
         <v>782</v>
       </c>
       <c r="G372" s="4" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="H372" s="3" t="s">
         <v>8</v>
@@ -27393,13 +27422,13 @@
         <v>783</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>784</v>
       </c>
       <c r="E373" s="4" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="F373" s="4" t="s">
         <v>785</v>
@@ -27419,16 +27448,16 @@
         <v>786</v>
       </c>
       <c r="C374" s="4" t="s">
+        <v>2520</v>
+      </c>
+      <c r="D374" s="4" t="s">
         <v>2521</v>
-      </c>
-      <c r="D374" s="4" t="s">
-        <v>2522</v>
       </c>
       <c r="E374" s="4" t="s">
         <v>787</v>
       </c>
       <c r="F374" s="4" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="G374" s="3" t="s">
         <v>8</v>
@@ -27445,22 +27474,22 @@
         <v>788</v>
       </c>
       <c r="C375" s="4" t="s">
+        <v>2523</v>
+      </c>
+      <c r="D375" s="4" t="s">
         <v>2524</v>
       </c>
-      <c r="D375" s="4" t="s">
+      <c r="E375" s="4" t="s">
         <v>2525</v>
       </c>
-      <c r="E375" s="4" t="s">
+      <c r="F375" s="4" t="s">
         <v>2526</v>
-      </c>
-      <c r="F375" s="4" t="s">
-        <v>2527</v>
       </c>
       <c r="G375" s="4" t="s">
         <v>789</v>
       </c>
       <c r="H375" s="4" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="376" spans="1:8" ht="40" customHeight="1">
@@ -27471,22 +27500,22 @@
         <v>790</v>
       </c>
       <c r="C376" s="4" t="s">
+        <v>2528</v>
+      </c>
+      <c r="D376" s="4" t="s">
         <v>2529</v>
       </c>
-      <c r="D376" s="4" t="s">
+      <c r="E376" s="4" t="s">
         <v>2530</v>
       </c>
-      <c r="E376" s="4" t="s">
+      <c r="F376" s="4" t="s">
         <v>2531</v>
-      </c>
-      <c r="F376" s="4" t="s">
-        <v>2532</v>
       </c>
       <c r="G376" s="4" t="s">
         <v>791</v>
       </c>
       <c r="H376" s="4" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="377" spans="1:8" ht="40" customHeight="1">
@@ -27497,19 +27526,19 @@
         <v>792</v>
       </c>
       <c r="C377" s="4" t="s">
+        <v>2533</v>
+      </c>
+      <c r="D377" s="4" t="s">
         <v>2534</v>
       </c>
-      <c r="D377" s="4" t="s">
+      <c r="E377" s="4" t="s">
         <v>2535</v>
       </c>
-      <c r="E377" s="4" t="s">
+      <c r="F377" s="4" t="s">
         <v>2536</v>
       </c>
-      <c r="F377" s="4" t="s">
+      <c r="G377" s="4" t="s">
         <v>2537</v>
-      </c>
-      <c r="G377" s="4" t="s">
-        <v>2538</v>
       </c>
       <c r="H377" s="3" t="s">
         <v>8</v>
@@ -27523,16 +27552,16 @@
         <v>793</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>794</v>
       </c>
       <c r="E378" s="4" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F378" s="4" t="s">
         <v>2540</v>
-      </c>
-      <c r="F378" s="4" t="s">
-        <v>2541</v>
       </c>
       <c r="G378" s="3" t="s">
         <v>8</v>
@@ -27549,16 +27578,16 @@
         <v>795</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>796</v>
       </c>
       <c r="E379" s="4" t="s">
+        <v>2541</v>
+      </c>
+      <c r="F379" s="4" t="s">
         <v>2542</v>
-      </c>
-      <c r="F379" s="4" t="s">
-        <v>2543</v>
       </c>
       <c r="G379" s="3" t="s">
         <v>8</v>
@@ -27575,7 +27604,7 @@
         <v>797</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>798</v>
@@ -27584,7 +27613,7 @@
         <v>799</v>
       </c>
       <c r="F380" s="4" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="G380" s="4" t="s">
         <v>800</v>
@@ -27601,16 +27630,16 @@
         <v>801</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="D381" s="3" t="s">
         <v>802</v>
       </c>
       <c r="E381" s="4" t="s">
+        <v>2546</v>
+      </c>
+      <c r="F381" s="4" t="s">
         <v>2547</v>
-      </c>
-      <c r="F381" s="4" t="s">
-        <v>2548</v>
       </c>
       <c r="G381" s="4" t="s">
         <v>803</v>
@@ -27627,13 +27656,13 @@
         <v>804</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="D382" s="3" t="s">
         <v>805</v>
       </c>
       <c r="E382" s="4" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="F382" s="4" t="s">
         <v>806</v>
@@ -27653,7 +27682,7 @@
         <v>807</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>808</v>
@@ -27679,19 +27708,19 @@
         <v>812</v>
       </c>
       <c r="C384" s="4" t="s">
+        <v>2551</v>
+      </c>
+      <c r="D384" s="4" t="s">
         <v>2552</v>
-      </c>
-      <c r="D384" s="4" t="s">
-        <v>2553</v>
       </c>
       <c r="E384" s="4" t="s">
         <v>813</v>
       </c>
       <c r="F384" s="4" t="s">
+        <v>2553</v>
+      </c>
+      <c r="G384" s="4" t="s">
         <v>2554</v>
-      </c>
-      <c r="G384" s="4" t="s">
-        <v>2555</v>
       </c>
       <c r="H384" s="3" t="s">
         <v>8</v>
@@ -27705,16 +27734,16 @@
         <v>814</v>
       </c>
       <c r="C385" s="4" t="s">
+        <v>2555</v>
+      </c>
+      <c r="D385" s="4" t="s">
         <v>2556</v>
       </c>
-      <c r="D385" s="4" t="s">
+      <c r="E385" s="4" t="s">
         <v>2557</v>
       </c>
-      <c r="E385" s="4" t="s">
+      <c r="F385" s="4" t="s">
         <v>2558</v>
-      </c>
-      <c r="F385" s="4" t="s">
-        <v>2559</v>
       </c>
       <c r="G385" s="3" t="s">
         <v>8</v>
@@ -27731,22 +27760,22 @@
         <v>815</v>
       </c>
       <c r="C386" s="4" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D386" s="4" t="s">
         <v>2560</v>
       </c>
-      <c r="D386" s="4" t="s">
+      <c r="E386" s="4" t="s">
         <v>2561</v>
       </c>
-      <c r="E386" s="4" t="s">
+      <c r="F386" s="4" t="s">
         <v>2562</v>
       </c>
-      <c r="F386" s="4" t="s">
+      <c r="G386" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H386" s="4" t="s">
         <v>2563</v>
-      </c>
-      <c r="G386" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H386" s="4" t="s">
-        <v>2564</v>
       </c>
     </row>
     <row r="387" spans="1:8" ht="40" customHeight="1">
@@ -27757,16 +27786,16 @@
         <v>816</v>
       </c>
       <c r="C387" s="4" t="s">
+        <v>2564</v>
+      </c>
+      <c r="D387" s="4" t="s">
         <v>2565</v>
       </c>
-      <c r="D387" s="4" t="s">
+      <c r="E387" s="4" t="s">
         <v>2566</v>
       </c>
-      <c r="E387" s="4" t="s">
+      <c r="F387" s="4" t="s">
         <v>2567</v>
-      </c>
-      <c r="F387" s="4" t="s">
-        <v>2568</v>
       </c>
       <c r="G387" s="3" t="s">
         <v>8</v>
@@ -27783,13 +27812,13 @@
         <v>817</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>818</v>
       </c>
       <c r="E388" s="4" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="F388" s="4" t="s">
         <v>819</v>
@@ -27798,7 +27827,7 @@
         <v>820</v>
       </c>
       <c r="H388" s="4" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="389" spans="1:8" ht="40" customHeight="1">
@@ -27809,16 +27838,16 @@
         <v>821</v>
       </c>
       <c r="C389" s="4" t="s">
+        <v>2571</v>
+      </c>
+      <c r="D389" s="4" t="s">
         <v>2572</v>
       </c>
-      <c r="D389" s="4" t="s">
+      <c r="E389" s="4" t="s">
         <v>2573</v>
       </c>
-      <c r="E389" s="4" t="s">
+      <c r="F389" s="4" t="s">
         <v>2574</v>
-      </c>
-      <c r="F389" s="4" t="s">
-        <v>2575</v>
       </c>
       <c r="G389" s="4" t="s">
         <v>822</v>
@@ -27835,13 +27864,13 @@
         <v>823</v>
       </c>
       <c r="C390" s="4" t="s">
+        <v>2575</v>
+      </c>
+      <c r="D390" s="4" t="s">
         <v>2576</v>
       </c>
-      <c r="D390" s="4" t="s">
+      <c r="E390" s="4" t="s">
         <v>2577</v>
-      </c>
-      <c r="E390" s="4" t="s">
-        <v>2578</v>
       </c>
       <c r="F390" s="4" t="s">
         <v>824</v>
@@ -27850,7 +27879,7 @@
         <v>825</v>
       </c>
       <c r="H390" s="4" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="391" spans="1:8" ht="40" customHeight="1">
@@ -27861,13 +27890,13 @@
         <v>826</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>827</v>
       </c>
       <c r="E391" s="4" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="F391" s="4" t="s">
         <v>828</v>
@@ -27887,16 +27916,16 @@
         <v>830</v>
       </c>
       <c r="C392" s="4" t="s">
+        <v>2581</v>
+      </c>
+      <c r="D392" s="4" t="s">
         <v>2582</v>
       </c>
-      <c r="D392" s="4" t="s">
+      <c r="E392" s="4" t="s">
         <v>2583</v>
       </c>
-      <c r="E392" s="4" t="s">
+      <c r="F392" s="4" t="s">
         <v>2584</v>
-      </c>
-      <c r="F392" s="4" t="s">
-        <v>2585</v>
       </c>
       <c r="G392" s="3" t="s">
         <v>8</v>
@@ -27913,13 +27942,13 @@
         <v>831</v>
       </c>
       <c r="C393" s="4" t="s">
+        <v>2585</v>
+      </c>
+      <c r="D393" s="4" t="s">
         <v>2586</v>
       </c>
-      <c r="D393" s="4" t="s">
+      <c r="E393" s="4" t="s">
         <v>2587</v>
-      </c>
-      <c r="E393" s="4" t="s">
-        <v>2588</v>
       </c>
       <c r="F393" s="4" t="s">
         <v>832</v>
@@ -27928,7 +27957,7 @@
         <v>833</v>
       </c>
       <c r="H393" s="4" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="394" spans="1:8" ht="40" customHeight="1">
@@ -27939,22 +27968,22 @@
         <v>834</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>835</v>
       </c>
       <c r="E394" s="4" t="s">
+        <v>2590</v>
+      </c>
+      <c r="F394" s="4" t="s">
         <v>2591</v>
       </c>
-      <c r="F394" s="4" t="s">
+      <c r="G394" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H394" s="4" t="s">
         <v>2592</v>
-      </c>
-      <c r="G394" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H394" s="4" t="s">
-        <v>2593</v>
       </c>
     </row>
     <row r="395" spans="1:8" ht="40" customHeight="1">
@@ -27965,13 +27994,13 @@
         <v>836</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>837</v>
       </c>
       <c r="E395" s="4" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="F395" s="4" t="s">
         <v>838</v>
@@ -27991,13 +28020,13 @@
         <v>839</v>
       </c>
       <c r="C396" s="4" t="s">
+        <v>2595</v>
+      </c>
+      <c r="D396" s="4" t="s">
         <v>2596</v>
       </c>
-      <c r="D396" s="4" t="s">
+      <c r="E396" s="4" t="s">
         <v>2597</v>
-      </c>
-      <c r="E396" s="4" t="s">
-        <v>2598</v>
       </c>
       <c r="F396" s="4" t="s">
         <v>840</v>
@@ -28017,16 +28046,16 @@
         <v>842</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>843</v>
       </c>
       <c r="E397" s="4" t="s">
+        <v>2599</v>
+      </c>
+      <c r="F397" s="4" t="s">
         <v>2600</v>
-      </c>
-      <c r="F397" s="4" t="s">
-        <v>2601</v>
       </c>
       <c r="G397" s="3" t="s">
         <v>8</v>
@@ -28043,13 +28072,13 @@
         <v>844</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>843</v>
       </c>
       <c r="E398" s="4" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="F398" s="4" t="s">
         <v>845</v>
@@ -28058,7 +28087,7 @@
         <v>846</v>
       </c>
       <c r="H398" s="4" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="399" spans="1:8" ht="40" customHeight="1">
@@ -28069,22 +28098,22 @@
         <v>847</v>
       </c>
       <c r="C399" s="4" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D399" s="4" t="s">
         <v>2604</v>
       </c>
-      <c r="D399" s="4" t="s">
+      <c r="E399" s="4" t="s">
         <v>2605</v>
       </c>
-      <c r="E399" s="4" t="s">
+      <c r="F399" s="4" t="s">
         <v>2606</v>
       </c>
-      <c r="F399" s="4" t="s">
+      <c r="G399" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H399" s="4" t="s">
         <v>2607</v>
-      </c>
-      <c r="G399" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H399" s="4" t="s">
-        <v>2608</v>
       </c>
     </row>
     <row r="400" spans="1:8" ht="40" customHeight="1">
@@ -28095,16 +28124,16 @@
         <v>848</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>849</v>
       </c>
       <c r="E400" s="4" t="s">
+        <v>2609</v>
+      </c>
+      <c r="F400" s="4" t="s">
         <v>2610</v>
-      </c>
-      <c r="F400" s="4" t="s">
-        <v>2611</v>
       </c>
       <c r="G400" s="3" t="s">
         <v>8</v>
@@ -28121,13 +28150,13 @@
         <v>850</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>849</v>
       </c>
       <c r="E401" s="4" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F401" s="4" t="s">
         <v>851</v>
@@ -28147,16 +28176,16 @@
         <v>853</v>
       </c>
       <c r="C402" s="4" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D402" s="4" t="s">
         <v>2613</v>
       </c>
-      <c r="D402" s="4" t="s">
+      <c r="E402" s="4" t="s">
         <v>2614</v>
       </c>
-      <c r="E402" s="4" t="s">
+      <c r="F402" s="4" t="s">
         <v>2615</v>
-      </c>
-      <c r="F402" s="4" t="s">
-        <v>2616</v>
       </c>
       <c r="G402" s="3" t="s">
         <v>8</v>
@@ -28173,13 +28202,13 @@
         <v>854</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>855</v>
       </c>
       <c r="E403" s="4" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="F403" s="4" t="s">
         <v>856</v>
@@ -28199,19 +28228,19 @@
         <v>858</v>
       </c>
       <c r="C404" s="4" t="s">
+        <v>2618</v>
+      </c>
+      <c r="D404" s="4" t="s">
         <v>2619</v>
       </c>
-      <c r="D404" s="4" t="s">
+      <c r="E404" s="4" t="s">
         <v>2620</v>
       </c>
-      <c r="E404" s="4" t="s">
+      <c r="F404" s="4" t="s">
         <v>2621</v>
       </c>
-      <c r="F404" s="4" t="s">
-        <v>2622</v>
-      </c>
       <c r="G404" s="4" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="H404" s="3" t="s">
         <v>8</v>
@@ -28225,19 +28254,19 @@
         <v>859</v>
       </c>
       <c r="C405" s="4" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D405" s="4" t="s">
         <v>2623</v>
       </c>
-      <c r="D405" s="4" t="s">
+      <c r="E405" s="4" t="s">
         <v>2624</v>
       </c>
-      <c r="E405" s="4" t="s">
+      <c r="F405" s="4" t="s">
         <v>2625</v>
       </c>
-      <c r="F405" s="4" t="s">
+      <c r="G405" s="4" t="s">
         <v>2626</v>
-      </c>
-      <c r="G405" s="4" t="s">
-        <v>2627</v>
       </c>
       <c r="H405" s="3" t="s">
         <v>8</v>
@@ -28251,10 +28280,10 @@
         <v>860</v>
       </c>
       <c r="C406" s="4" t="s">
+        <v>2627</v>
+      </c>
+      <c r="D406" s="4" t="s">
         <v>2628</v>
-      </c>
-      <c r="D406" s="4" t="s">
-        <v>2629</v>
       </c>
       <c r="E406" s="4" t="s">
         <v>861</v>
@@ -28277,22 +28306,22 @@
         <v>863</v>
       </c>
       <c r="C407" s="4" t="s">
+        <v>2629</v>
+      </c>
+      <c r="D407" s="4" t="s">
         <v>2630</v>
       </c>
-      <c r="D407" s="4" t="s">
+      <c r="E407" s="4" t="s">
         <v>2631</v>
       </c>
-      <c r="E407" s="4" t="s">
+      <c r="F407" s="4" t="s">
         <v>2632</v>
       </c>
-      <c r="F407" s="4" t="s">
+      <c r="G407" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H407" s="4" t="s">
         <v>2633</v>
-      </c>
-      <c r="G407" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H407" s="4" t="s">
-        <v>2634</v>
       </c>
     </row>
     <row r="408" spans="1:8" ht="40" customHeight="1">
@@ -28303,16 +28332,16 @@
         <v>864</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E408" s="4" t="s">
+        <v>2635</v>
+      </c>
+      <c r="F408" s="4" t="s">
         <v>2636</v>
-      </c>
-      <c r="F408" s="4" t="s">
-        <v>2637</v>
       </c>
       <c r="G408" s="3" t="s">
         <v>8</v>
@@ -28329,22 +28358,22 @@
         <v>866</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E409" s="4" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="F409" s="4" t="s">
         <v>867</v>
       </c>
       <c r="G409" s="4" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="H409" s="4" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="410" spans="1:8" ht="40" customHeight="1">
@@ -28355,7 +28384,7 @@
         <v>868</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>871</v>
@@ -28364,7 +28393,7 @@
         <v>869</v>
       </c>
       <c r="F410" s="4" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="G410" s="3" t="s">
         <v>8</v>
@@ -28381,22 +28410,22 @@
         <v>870</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="D411" s="3" t="s">
         <v>871</v>
       </c>
       <c r="E411" s="4" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
       <c r="F411" s="4" t="s">
         <v>872</v>
       </c>
       <c r="G411" s="4" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="H411" s="4" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="412" spans="1:8" ht="40" customHeight="1">
@@ -28407,16 +28436,16 @@
         <v>873</v>
       </c>
       <c r="C412" s="4" t="s">
+        <v>2643</v>
+      </c>
+      <c r="D412" s="4" t="s">
         <v>2644</v>
       </c>
-      <c r="D412" s="4" t="s">
+      <c r="E412" s="4" t="s">
         <v>2645</v>
       </c>
-      <c r="E412" s="4" t="s">
+      <c r="F412" s="4" t="s">
         <v>2646</v>
-      </c>
-      <c r="F412" s="4" t="s">
-        <v>2647</v>
       </c>
       <c r="G412" s="3" t="s">
         <v>8</v>
@@ -28433,13 +28462,13 @@
         <v>874</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="D413" s="4" t="s">
+        <v>2647</v>
+      </c>
+      <c r="E413" s="4" t="s">
         <v>2648</v>
-      </c>
-      <c r="E413" s="4" t="s">
-        <v>2649</v>
       </c>
       <c r="F413" s="4" t="s">
         <v>875</v>
@@ -28448,7 +28477,7 @@
         <v>8</v>
       </c>
       <c r="H413" s="4" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="414" spans="1:8" ht="40" customHeight="1">
@@ -28459,7 +28488,7 @@
         <v>876</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>877</v>
@@ -28468,7 +28497,7 @@
         <v>878</v>
       </c>
       <c r="F414" s="4" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="G414" s="3" t="s">
         <v>8</v>
@@ -28485,22 +28514,22 @@
         <v>879</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="D415" s="4" t="s">
+        <v>2652</v>
+      </c>
+      <c r="E415" s="4" t="s">
         <v>2653</v>
       </c>
-      <c r="E415" s="4" t="s">
+      <c r="F415" s="4" t="s">
         <v>2654</v>
       </c>
-      <c r="F415" s="4" t="s">
-        <v>2655</v>
-      </c>
       <c r="G415" s="4" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
       <c r="H415" s="4" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="416" spans="1:8" ht="40" customHeight="1">
@@ -28511,16 +28540,16 @@
         <v>880</v>
       </c>
       <c r="C416" s="4" t="s">
+        <v>2655</v>
+      </c>
+      <c r="D416" s="4" t="s">
         <v>2656</v>
       </c>
-      <c r="D416" s="4" t="s">
+      <c r="E416" s="4" t="s">
         <v>2657</v>
       </c>
-      <c r="E416" s="4" t="s">
+      <c r="F416" s="4" t="s">
         <v>2658</v>
-      </c>
-      <c r="F416" s="4" t="s">
-        <v>2659</v>
       </c>
       <c r="G416" s="4" t="s">
         <v>8</v>
@@ -28537,16 +28566,16 @@
         <v>881</v>
       </c>
       <c r="C417" s="4" t="s">
+        <v>2659</v>
+      </c>
+      <c r="D417" s="4" t="s">
         <v>2660</v>
       </c>
-      <c r="D417" s="4" t="s">
+      <c r="E417" s="4" t="s">
         <v>2661</v>
       </c>
-      <c r="E417" s="4" t="s">
+      <c r="F417" s="4" t="s">
         <v>2662</v>
-      </c>
-      <c r="F417" s="4" t="s">
-        <v>2663</v>
       </c>
       <c r="G417" s="4" t="s">
         <v>8</v>
@@ -28563,16 +28592,16 @@
         <v>882</v>
       </c>
       <c r="C418" s="4" t="s">
+        <v>2663</v>
+      </c>
+      <c r="D418" s="4" t="s">
         <v>2664</v>
-      </c>
-      <c r="D418" s="4" t="s">
-        <v>2665</v>
       </c>
       <c r="E418" s="4" t="s">
         <v>883</v>
       </c>
       <c r="F418" s="4" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="G418" s="4" t="s">
         <v>8</v>
@@ -28589,13 +28618,13 @@
         <v>884</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>885</v>
       </c>
       <c r="E419" s="4" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="F419" s="4" t="s">
         <v>886</v>
@@ -28615,7 +28644,7 @@
         <v>888</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>889</v>
@@ -28624,7 +28653,7 @@
         <v>890</v>
       </c>
       <c r="F420" s="4" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
       <c r="G420" s="4" t="s">
         <v>891</v>
@@ -28641,19 +28670,19 @@
         <v>892</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>893</v>
       </c>
       <c r="E421" s="4" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="F421" s="4" t="s">
+        <v>3400</v>
+      </c>
+      <c r="G421" s="4" t="s">
         <v>3401</v>
-      </c>
-      <c r="G421" s="4" t="s">
-        <v>3402</v>
       </c>
       <c r="H421" s="4" t="s">
         <v>8</v>
@@ -28667,10 +28696,10 @@
         <v>894</v>
       </c>
       <c r="C422" s="4" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D422" s="4" t="s">
         <v>2673</v>
-      </c>
-      <c r="D422" s="4" t="s">
-        <v>2674</v>
       </c>
       <c r="E422" s="4" t="s">
         <v>895</v>
@@ -28693,19 +28722,19 @@
         <v>898</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>899</v>
       </c>
       <c r="E423" s="4" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="F423" s="4" t="s">
         <v>900</v>
       </c>
       <c r="G423" s="4" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="H423" s="4" t="s">
         <v>8</v>
@@ -28719,19 +28748,19 @@
         <v>901</v>
       </c>
       <c r="C424" s="4" t="s">
+        <v>2676</v>
+      </c>
+      <c r="D424" s="4" t="s">
         <v>2677</v>
-      </c>
-      <c r="D424" s="4" t="s">
-        <v>2678</v>
       </c>
       <c r="E424" s="4" t="s">
         <v>902</v>
       </c>
       <c r="F424" s="4" t="s">
+        <v>2678</v>
+      </c>
+      <c r="G424" s="4" t="s">
         <v>2679</v>
-      </c>
-      <c r="G424" s="4" t="s">
-        <v>2680</v>
       </c>
       <c r="H424" s="4" t="s">
         <v>8</v>
@@ -28745,7 +28774,7 @@
         <v>903</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>904</v>
@@ -28754,7 +28783,7 @@
         <v>905</v>
       </c>
       <c r="F425" s="4" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="G425" s="4" t="s">
         <v>8</v>
@@ -28777,16 +28806,16 @@
         <v>908</v>
       </c>
       <c r="E426" s="4" t="s">
+        <v>2682</v>
+      </c>
+      <c r="F426" s="4" t="s">
         <v>2683</v>
       </c>
-      <c r="F426" s="4" t="s">
+      <c r="G426" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H426" s="4" t="s">
         <v>2684</v>
-      </c>
-      <c r="G426" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H426" s="4" t="s">
-        <v>2685</v>
       </c>
     </row>
     <row r="427" spans="1:8" ht="40" customHeight="1">
@@ -28797,7 +28826,7 @@
         <v>909</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>910</v>
@@ -28806,7 +28835,7 @@
         <v>911</v>
       </c>
       <c r="F427" s="4" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="G427" s="4" t="s">
         <v>8</v>
@@ -28832,7 +28861,7 @@
         <v>915</v>
       </c>
       <c r="F428" s="4" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="G428" s="4" t="s">
         <v>8</v>
@@ -28849,16 +28878,16 @@
         <v>916</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>917</v>
       </c>
       <c r="E429" s="4" t="s">
+        <v>2688</v>
+      </c>
+      <c r="F429" s="4" t="s">
         <v>2689</v>
-      </c>
-      <c r="F429" s="4" t="s">
-        <v>2690</v>
       </c>
       <c r="G429" s="4" t="s">
         <v>8</v>
@@ -28901,22 +28930,22 @@
         <v>924</v>
       </c>
       <c r="C431" s="4" t="s">
+        <v>2690</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>2692</v>
+      </c>
+      <c r="E431" s="4" t="s">
         <v>2691</v>
       </c>
-      <c r="D431" s="4" t="s">
+      <c r="F431" s="4" t="s">
         <v>2693</v>
-      </c>
-      <c r="E431" s="4" t="s">
-        <v>2692</v>
-      </c>
-      <c r="F431" s="4" t="s">
-        <v>2694</v>
       </c>
       <c r="G431" s="4" t="s">
         <v>925</v>
       </c>
       <c r="H431" s="4" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="432" spans="1:8" ht="40" customHeight="1">
@@ -28927,13 +28956,13 @@
         <v>926</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>927</v>
       </c>
       <c r="E432" s="4" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="F432" s="4" t="s">
         <v>928</v>
@@ -28953,16 +28982,16 @@
         <v>930</v>
       </c>
       <c r="C433" s="4" t="s">
+        <v>2697</v>
+      </c>
+      <c r="D433" s="4" t="s">
         <v>2698</v>
-      </c>
-      <c r="D433" s="4" t="s">
-        <v>2699</v>
       </c>
       <c r="E433" s="4" t="s">
         <v>931</v>
       </c>
       <c r="F433" s="4" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="G433" s="3" t="s">
         <v>8</v>
@@ -28979,7 +29008,7 @@
         <v>932</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>933</v>
@@ -29005,7 +29034,7 @@
         <v>936</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>937</v>
@@ -29014,10 +29043,10 @@
         <v>938</v>
       </c>
       <c r="F435" s="4" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="G435" s="4" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="H435" s="3" t="s">
         <v>8</v>
@@ -29031,16 +29060,16 @@
         <v>939</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>940</v>
       </c>
       <c r="E436" s="4" t="s">
+        <v>2704</v>
+      </c>
+      <c r="F436" s="4" t="s">
         <v>2705</v>
-      </c>
-      <c r="F436" s="4" t="s">
-        <v>2706</v>
       </c>
       <c r="G436" s="4" t="s">
         <v>941</v>
@@ -29057,16 +29086,16 @@
         <v>942</v>
       </c>
       <c r="C437" s="4" t="s">
+        <v>2706</v>
+      </c>
+      <c r="D437" s="4" t="s">
         <v>2707</v>
       </c>
-      <c r="D437" s="4" t="s">
+      <c r="E437" s="4" t="s">
         <v>2708</v>
       </c>
-      <c r="E437" s="4" t="s">
+      <c r="F437" s="4" t="s">
         <v>2709</v>
-      </c>
-      <c r="F437" s="4" t="s">
-        <v>2710</v>
       </c>
       <c r="G437" s="3" t="s">
         <v>8</v>
@@ -29083,16 +29112,16 @@
         <v>943</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>944</v>
       </c>
       <c r="E438" s="4" t="s">
+        <v>2711</v>
+      </c>
+      <c r="F438" s="4" t="s">
         <v>2712</v>
-      </c>
-      <c r="F438" s="4" t="s">
-        <v>2713</v>
       </c>
       <c r="G438" s="3" t="s">
         <v>8</v>
@@ -29109,7 +29138,7 @@
         <v>945</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>2714</v>
+        <v>2713</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>946</v>
@@ -29135,13 +29164,13 @@
         <v>949</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>950</v>
       </c>
       <c r="E440" s="4" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="F440" s="4" t="s">
         <v>951</v>
@@ -29161,10 +29190,10 @@
         <v>952</v>
       </c>
       <c r="C441" s="4" t="s">
+        <v>2716</v>
+      </c>
+      <c r="D441" s="4" t="s">
         <v>2717</v>
-      </c>
-      <c r="D441" s="4" t="s">
-        <v>2718</v>
       </c>
       <c r="E441" s="4" t="s">
         <v>953</v>
@@ -29176,7 +29205,7 @@
         <v>8</v>
       </c>
       <c r="H441" s="4" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="442" spans="1:8" ht="40" customHeight="1">
@@ -29187,13 +29216,13 @@
         <v>955</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>956</v>
       </c>
       <c r="E442" s="4" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="F442" s="4" t="s">
         <v>957</v>
@@ -29213,16 +29242,16 @@
         <v>959</v>
       </c>
       <c r="C443" s="4" t="s">
+        <v>2721</v>
+      </c>
+      <c r="D443" s="4" t="s">
         <v>2722</v>
       </c>
-      <c r="D443" s="4" t="s">
+      <c r="E443" s="4" t="s">
         <v>2723</v>
       </c>
-      <c r="E443" s="4" t="s">
+      <c r="F443" s="4" t="s">
         <v>2724</v>
-      </c>
-      <c r="F443" s="4" t="s">
-        <v>2725</v>
       </c>
       <c r="G443" s="4" t="s">
         <v>960</v>
@@ -29239,16 +29268,16 @@
         <v>961</v>
       </c>
       <c r="C444" s="4" t="s">
+        <v>2725</v>
+      </c>
+      <c r="D444" s="4" t="s">
         <v>2726</v>
       </c>
-      <c r="D444" s="4" t="s">
+      <c r="E444" s="4" t="s">
         <v>2727</v>
       </c>
-      <c r="E444" s="4" t="s">
+      <c r="F444" s="4" t="s">
         <v>2728</v>
-      </c>
-      <c r="F444" s="4" t="s">
-        <v>2729</v>
       </c>
       <c r="G444" s="3" t="s">
         <v>8</v>
@@ -29265,19 +29294,19 @@
         <v>962</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>963</v>
       </c>
       <c r="E445" s="4" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="F445" s="4" t="s">
         <v>964</v>
       </c>
       <c r="G445" s="4" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="H445" s="3" t="s">
         <v>8</v>
@@ -29291,13 +29320,13 @@
         <v>965</v>
       </c>
       <c r="C446" s="4" t="s">
+        <v>2732</v>
+      </c>
+      <c r="D446" s="4" t="s">
         <v>2733</v>
       </c>
-      <c r="D446" s="4" t="s">
+      <c r="E446" s="4" t="s">
         <v>2734</v>
-      </c>
-      <c r="E446" s="4" t="s">
-        <v>2735</v>
       </c>
       <c r="F446" s="4" t="s">
         <v>966</v>
@@ -29317,16 +29346,16 @@
         <v>968</v>
       </c>
       <c r="C447" s="4" t="s">
+        <v>2735</v>
+      </c>
+      <c r="D447" s="4" t="s">
         <v>2736</v>
       </c>
-      <c r="D447" s="4" t="s">
+      <c r="E447" s="4" t="s">
         <v>2737</v>
       </c>
-      <c r="E447" s="4" t="s">
+      <c r="F447" s="4" t="s">
         <v>2738</v>
-      </c>
-      <c r="F447" s="4" t="s">
-        <v>2739</v>
       </c>
       <c r="G447" s="3" t="s">
         <v>8</v>
@@ -29343,16 +29372,16 @@
         <v>969</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>2740</v>
+        <v>2739</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>970</v>
       </c>
       <c r="E448" s="4" t="s">
+        <v>2740</v>
+      </c>
+      <c r="F448" s="4" t="s">
         <v>2741</v>
-      </c>
-      <c r="F448" s="4" t="s">
-        <v>2742</v>
       </c>
       <c r="G448" s="4" t="s">
         <v>971</v>
@@ -29369,7 +29398,7 @@
         <v>972</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>973</v>
@@ -29378,13 +29407,13 @@
         <v>974</v>
       </c>
       <c r="F449" s="4" t="s">
+        <v>2743</v>
+      </c>
+      <c r="G449" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H449" s="4" t="s">
         <v>2744</v>
-      </c>
-      <c r="G449" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H449" s="4" t="s">
-        <v>2745</v>
       </c>
     </row>
     <row r="450" spans="1:8" ht="40" customHeight="1">
@@ -29395,7 +29424,7 @@
         <v>975</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>976</v>
@@ -29404,7 +29433,7 @@
         <v>977</v>
       </c>
       <c r="F450" s="4" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="G450" s="4" t="s">
         <v>978</v>
@@ -29421,16 +29450,16 @@
         <v>979</v>
       </c>
       <c r="C451" s="4" t="s">
+        <v>2746</v>
+      </c>
+      <c r="D451" s="4" t="s">
         <v>2747</v>
       </c>
-      <c r="D451" s="4" t="s">
+      <c r="E451" s="4" t="s">
         <v>2748</v>
       </c>
-      <c r="E451" s="4" t="s">
-        <v>2749</v>
-      </c>
       <c r="F451" s="4" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
       <c r="G451" s="4" t="s">
         <v>980</v>
@@ -29447,7 +29476,7 @@
         <v>981</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>2750</v>
+        <v>2749</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>982</v>
@@ -29473,13 +29502,13 @@
         <v>986</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>987</v>
       </c>
       <c r="E453" s="4" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="F453" s="4" t="s">
         <v>988</v>
@@ -29499,16 +29528,16 @@
         <v>990</v>
       </c>
       <c r="C454" s="4" t="s">
+        <v>2752</v>
+      </c>
+      <c r="D454" s="4" t="s">
         <v>2753</v>
       </c>
-      <c r="D454" s="4" t="s">
+      <c r="E454" s="4" t="s">
         <v>2754</v>
       </c>
-      <c r="E454" s="4" t="s">
+      <c r="F454" s="4" t="s">
         <v>2755</v>
-      </c>
-      <c r="F454" s="4" t="s">
-        <v>2756</v>
       </c>
       <c r="G454" s="3" t="s">
         <v>8</v>
@@ -29525,16 +29554,16 @@
         <v>991</v>
       </c>
       <c r="C455" s="4" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D455" s="4" t="s">
         <v>2757</v>
       </c>
-      <c r="D455" s="4" t="s">
+      <c r="E455" s="4" t="s">
         <v>2758</v>
       </c>
-      <c r="E455" s="4" t="s">
+      <c r="F455" s="4" t="s">
         <v>2759</v>
-      </c>
-      <c r="F455" s="4" t="s">
-        <v>2760</v>
       </c>
       <c r="G455" s="3" t="s">
         <v>8</v>
@@ -29551,19 +29580,19 @@
         <v>992</v>
       </c>
       <c r="C456" s="4" t="s">
+        <v>2760</v>
+      </c>
+      <c r="D456" s="4" t="s">
         <v>2761</v>
       </c>
-      <c r="D456" s="4" t="s">
+      <c r="E456" s="4" t="s">
         <v>2762</v>
       </c>
-      <c r="E456" s="4" t="s">
+      <c r="F456" s="4" t="s">
         <v>2763</v>
       </c>
-      <c r="F456" s="4" t="s">
-        <v>2764</v>
-      </c>
       <c r="G456" s="4" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
       <c r="H456" s="3" t="s">
         <v>8</v>
@@ -29577,13 +29606,13 @@
         <v>993</v>
       </c>
       <c r="C457" s="4" t="s">
+        <v>2764</v>
+      </c>
+      <c r="D457" s="4" t="s">
         <v>2765</v>
       </c>
-      <c r="D457" s="4" t="s">
+      <c r="E457" s="4" t="s">
         <v>2766</v>
-      </c>
-      <c r="E457" s="4" t="s">
-        <v>2767</v>
       </c>
       <c r="F457" s="4" t="s">
         <v>994</v>
@@ -29603,16 +29632,16 @@
         <v>995</v>
       </c>
       <c r="C458" s="4" t="s">
+        <v>2767</v>
+      </c>
+      <c r="D458" s="4" t="s">
         <v>2768</v>
       </c>
-      <c r="D458" s="4" t="s">
+      <c r="E458" s="4" t="s">
         <v>2769</v>
       </c>
-      <c r="E458" s="4" t="s">
+      <c r="F458" s="4" t="s">
         <v>2770</v>
-      </c>
-      <c r="F458" s="4" t="s">
-        <v>2771</v>
       </c>
       <c r="G458" s="3" t="s">
         <v>8</v>
@@ -29629,16 +29658,16 @@
         <v>996</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>997</v>
       </c>
       <c r="E459" s="4" t="s">
+        <v>2772</v>
+      </c>
+      <c r="F459" s="4" t="s">
         <v>2773</v>
-      </c>
-      <c r="F459" s="4" t="s">
-        <v>2774</v>
       </c>
       <c r="G459" s="4" t="s">
         <v>998</v>
@@ -29655,13 +29684,13 @@
         <v>999</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>1000</v>
       </c>
       <c r="E460" s="4" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="F460" s="4" t="s">
         <v>1001</v>
@@ -29681,19 +29710,19 @@
         <v>1003</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>1004</v>
       </c>
       <c r="E461" s="4" t="s">
+        <v>2777</v>
+      </c>
+      <c r="F461" s="4" t="s">
         <v>2778</v>
       </c>
-      <c r="F461" s="4" t="s">
+      <c r="G461" s="4" t="s">
         <v>2779</v>
-      </c>
-      <c r="G461" s="4" t="s">
-        <v>2780</v>
       </c>
       <c r="H461" s="3" t="s">
         <v>8</v>
@@ -29707,19 +29736,19 @@
         <v>1005</v>
       </c>
       <c r="C462" s="4" t="s">
+        <v>2780</v>
+      </c>
+      <c r="D462" s="4" t="s">
         <v>2781</v>
       </c>
-      <c r="D462" s="4" t="s">
+      <c r="E462" s="4" t="s">
         <v>2782</v>
       </c>
-      <c r="E462" s="4" t="s">
+      <c r="F462" s="4" t="s">
         <v>2783</v>
       </c>
-      <c r="F462" s="4" t="s">
+      <c r="G462" s="4" t="s">
         <v>2784</v>
-      </c>
-      <c r="G462" s="4" t="s">
-        <v>2785</v>
       </c>
       <c r="H462" s="3" t="s">
         <v>8</v>
@@ -29733,16 +29762,16 @@
         <v>1006</v>
       </c>
       <c r="C463" s="4" t="s">
+        <v>2785</v>
+      </c>
+      <c r="D463" s="4" t="s">
         <v>2786</v>
       </c>
-      <c r="D463" s="4" t="s">
+      <c r="E463" s="4" t="s">
         <v>2787</v>
       </c>
-      <c r="E463" s="4" t="s">
+      <c r="F463" s="4" t="s">
         <v>2788</v>
-      </c>
-      <c r="F463" s="4" t="s">
-        <v>2789</v>
       </c>
       <c r="G463" s="4" t="s">
         <v>1007</v>
@@ -29759,7 +29788,7 @@
         <v>1008</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>1009</v>
@@ -29768,7 +29797,7 @@
         <v>8</v>
       </c>
       <c r="F464" s="4" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="G464" s="3" t="s">
         <v>8</v>
@@ -29785,16 +29814,16 @@
         <v>1010</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>1011</v>
       </c>
       <c r="E465" s="4" t="s">
+        <v>2792</v>
+      </c>
+      <c r="F465" s="4" t="s">
         <v>2793</v>
-      </c>
-      <c r="F465" s="4" t="s">
-        <v>2794</v>
       </c>
       <c r="G465" s="3" t="s">
         <v>8</v>
@@ -29811,16 +29840,16 @@
         <v>1012</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>1013</v>
       </c>
       <c r="E466" s="4" t="s">
+        <v>2795</v>
+      </c>
+      <c r="F466" s="4" t="s">
         <v>2796</v>
-      </c>
-      <c r="F466" s="4" t="s">
-        <v>2797</v>
       </c>
       <c r="G466" s="3" t="s">
         <v>8</v>
@@ -29843,10 +29872,10 @@
         <v>1016</v>
       </c>
       <c r="E467" s="4" t="s">
+        <v>2797</v>
+      </c>
+      <c r="F467" s="4" t="s">
         <v>2798</v>
-      </c>
-      <c r="F467" s="4" t="s">
-        <v>2799</v>
       </c>
       <c r="G467" s="3" t="s">
         <v>8</v>
@@ -29863,16 +29892,16 @@
         <v>1017</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>1018</v>
       </c>
       <c r="E468" s="4" t="s">
+        <v>2800</v>
+      </c>
+      <c r="F468" s="4" t="s">
         <v>2801</v>
-      </c>
-      <c r="F468" s="4" t="s">
-        <v>2802</v>
       </c>
       <c r="G468" s="3" t="s">
         <v>8</v>
@@ -29889,16 +29918,16 @@
         <v>1019</v>
       </c>
       <c r="C469" s="4" t="s">
+        <v>2802</v>
+      </c>
+      <c r="D469" s="4" t="s">
         <v>2803</v>
-      </c>
-      <c r="D469" s="4" t="s">
-        <v>2804</v>
       </c>
       <c r="E469" s="4" t="s">
         <v>1020</v>
       </c>
       <c r="F469" s="4" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
       <c r="G469" s="3" t="s">
         <v>8</v>
@@ -29915,7 +29944,7 @@
         <v>1021</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>1022</v>
@@ -29924,7 +29953,7 @@
         <v>1023</v>
       </c>
       <c r="F470" s="4" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="G470" s="3" t="s">
         <v>8</v>
@@ -29941,16 +29970,16 @@
         <v>1024</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>1025</v>
       </c>
       <c r="E471" s="4" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="F471" s="4" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
       <c r="G471" s="4" t="s">
         <v>1026</v>
@@ -29967,7 +29996,7 @@
         <v>1027</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>1028</v>
@@ -29993,13 +30022,13 @@
         <v>1032</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>1033</v>
       </c>
       <c r="E473" s="4" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="F473" s="4" t="s">
         <v>1034</v>
@@ -30019,16 +30048,16 @@
         <v>1036</v>
       </c>
       <c r="C474" s="4" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D474" s="4" t="s">
         <v>2813</v>
       </c>
-      <c r="D474" s="4" t="s">
+      <c r="E474" s="4" t="s">
         <v>2814</v>
       </c>
-      <c r="E474" s="4" t="s">
+      <c r="F474" s="4" t="s">
         <v>2815</v>
-      </c>
-      <c r="F474" s="4" t="s">
-        <v>2816</v>
       </c>
       <c r="G474" s="3" t="s">
         <v>8</v>
@@ -30045,16 +30074,16 @@
         <v>1037</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>1038</v>
       </c>
       <c r="E475" s="4" t="s">
+        <v>2817</v>
+      </c>
+      <c r="F475" s="4" t="s">
         <v>2818</v>
-      </c>
-      <c r="F475" s="4" t="s">
-        <v>2819</v>
       </c>
       <c r="G475" s="4" t="s">
         <v>1039</v>
@@ -30071,16 +30100,16 @@
         <v>1040</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
       <c r="D476" s="4" t="s">
         <v>1041</v>
       </c>
       <c r="E476" s="4" t="s">
+        <v>2820</v>
+      </c>
+      <c r="F476" s="4" t="s">
         <v>2821</v>
-      </c>
-      <c r="F476" s="4" t="s">
-        <v>2822</v>
       </c>
       <c r="G476" s="4" t="s">
         <v>1042</v>
@@ -30097,16 +30126,16 @@
         <v>1043</v>
       </c>
       <c r="C477" s="4" t="s">
+        <v>2822</v>
+      </c>
+      <c r="D477" s="4" t="s">
         <v>2823</v>
       </c>
-      <c r="D477" s="4" t="s">
+      <c r="E477" s="4" t="s">
         <v>2824</v>
       </c>
-      <c r="E477" s="4" t="s">
+      <c r="F477" s="4" t="s">
         <v>2825</v>
-      </c>
-      <c r="F477" s="4" t="s">
-        <v>2826</v>
       </c>
       <c r="G477" s="3" t="s">
         <v>8</v>
@@ -30123,16 +30152,16 @@
         <v>1044</v>
       </c>
       <c r="C478" s="4" t="s">
+        <v>2826</v>
+      </c>
+      <c r="D478" s="4" t="s">
         <v>2827</v>
-      </c>
-      <c r="D478" s="4" t="s">
-        <v>2828</v>
       </c>
       <c r="E478" s="4" t="s">
         <v>1045</v>
       </c>
       <c r="F478" s="4" t="s">
-        <v>3410</v>
+        <v>3409</v>
       </c>
       <c r="G478" s="3" t="s">
         <v>8</v>
@@ -30149,13 +30178,13 @@
         <v>1046</v>
       </c>
       <c r="C479" s="4" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D479" s="4" t="s">
         <v>2829</v>
       </c>
-      <c r="D479" s="4" t="s">
+      <c r="E479" s="4" t="s">
         <v>2830</v>
-      </c>
-      <c r="E479" s="4" t="s">
-        <v>2831</v>
       </c>
       <c r="F479" s="4" t="s">
         <v>1047</v>
@@ -30175,19 +30204,19 @@
         <v>1049</v>
       </c>
       <c r="C480" s="4" t="s">
+        <v>2831</v>
+      </c>
+      <c r="D480" s="4" t="s">
         <v>2832</v>
       </c>
-      <c r="D480" s="4" t="s">
+      <c r="E480" s="4" t="s">
         <v>2833</v>
       </c>
-      <c r="E480" s="4" t="s">
+      <c r="F480" s="4" t="s">
         <v>2834</v>
       </c>
-      <c r="F480" s="4" t="s">
-        <v>2835</v>
-      </c>
       <c r="G480" s="4" t="s">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="H480" s="3" t="s">
         <v>8</v>
@@ -30201,7 +30230,7 @@
         <v>1050</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="D481" s="4" t="s">
         <v>1051</v>
@@ -30213,7 +30242,7 @@
         <v>1053</v>
       </c>
       <c r="G481" s="4" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="H481" s="3" t="s">
         <v>8</v>
@@ -30227,13 +30256,13 @@
         <v>1054</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="D482" s="4" t="s">
         <v>1055</v>
       </c>
       <c r="E482" s="4" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="F482" s="4" t="s">
         <v>1056</v>
@@ -30253,13 +30282,13 @@
         <v>1058</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="D483" s="4" t="s">
         <v>1059</v>
       </c>
       <c r="E483" s="4" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="F483" s="4" t="s">
         <v>1060</v>
@@ -30279,7 +30308,7 @@
         <v>1061</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="D484" s="4" t="s">
         <v>1062</v>
@@ -30291,7 +30320,7 @@
         <v>1064</v>
       </c>
       <c r="G484" s="4" t="s">
-        <v>3412</v>
+        <v>3411</v>
       </c>
       <c r="H484" s="3" t="s">
         <v>8</v>
@@ -30305,16 +30334,16 @@
         <v>1065</v>
       </c>
       <c r="C485" s="4" t="s">
+        <v>2842</v>
+      </c>
+      <c r="D485" s="4" t="s">
         <v>2843</v>
       </c>
-      <c r="D485" s="4" t="s">
+      <c r="E485" s="4" t="s">
         <v>2844</v>
       </c>
-      <c r="E485" s="4" t="s">
+      <c r="F485" s="4" t="s">
         <v>2845</v>
-      </c>
-      <c r="F485" s="4" t="s">
-        <v>2846</v>
       </c>
       <c r="G485" s="3" t="s">
         <v>8</v>
@@ -30331,16 +30360,16 @@
         <v>1066</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="D486" s="4" t="s">
         <v>1067</v>
       </c>
       <c r="E486" s="4" t="s">
+        <v>2847</v>
+      </c>
+      <c r="F486" s="4" t="s">
         <v>2848</v>
-      </c>
-      <c r="F486" s="4" t="s">
-        <v>2849</v>
       </c>
       <c r="G486" s="4" t="s">
         <v>1068</v>
@@ -30357,7 +30386,7 @@
         <v>1069</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="D487" s="4" t="s">
         <v>1070</v>
@@ -30366,10 +30395,10 @@
         <v>1071</v>
       </c>
       <c r="F487" s="4" t="s">
-        <v>3413</v>
+        <v>3412</v>
       </c>
       <c r="G487" s="4" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="H487" s="3" t="s">
         <v>8</v>
@@ -30383,13 +30412,13 @@
         <v>1072</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="D488" s="4" t="s">
         <v>1073</v>
       </c>
       <c r="E488" s="4" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="F488" s="4" t="s">
         <v>1074</v>
@@ -30409,16 +30438,16 @@
         <v>1076</v>
       </c>
       <c r="C489" s="4" t="s">
+        <v>2853</v>
+      </c>
+      <c r="D489" s="4" t="s">
         <v>2854</v>
       </c>
-      <c r="D489" s="4" t="s">
+      <c r="E489" s="4" t="s">
         <v>2855</v>
       </c>
-      <c r="E489" s="4" t="s">
+      <c r="F489" s="4" t="s">
         <v>2856</v>
-      </c>
-      <c r="F489" s="4" t="s">
-        <v>2857</v>
       </c>
       <c r="G489" s="3" t="s">
         <v>8</v>
@@ -30435,16 +30464,16 @@
         <v>1077</v>
       </c>
       <c r="C490" s="4" t="s">
+        <v>2857</v>
+      </c>
+      <c r="D490" s="4" t="s">
         <v>2858</v>
       </c>
-      <c r="D490" s="4" t="s">
+      <c r="E490" s="4" t="s">
         <v>2859</v>
       </c>
-      <c r="E490" s="4" t="s">
-        <v>2860</v>
-      </c>
       <c r="F490" s="4" t="s">
-        <v>3414</v>
+        <v>3413</v>
       </c>
       <c r="G490" s="4" t="s">
         <v>1078</v>
@@ -30461,19 +30490,19 @@
         <v>1079</v>
       </c>
       <c r="C491" s="4" t="s">
+        <v>2860</v>
+      </c>
+      <c r="D491" s="4" t="s">
         <v>2861</v>
       </c>
-      <c r="D491" s="4" t="s">
+      <c r="E491" s="4" t="s">
         <v>2862</v>
       </c>
-      <c r="E491" s="4" t="s">
+      <c r="F491" s="4" t="s">
+        <v>3414</v>
+      </c>
+      <c r="G491" s="4" t="s">
         <v>2863</v>
-      </c>
-      <c r="F491" s="4" t="s">
-        <v>3415</v>
-      </c>
-      <c r="G491" s="4" t="s">
-        <v>2864</v>
       </c>
       <c r="H491" s="3" t="s">
         <v>8</v>
@@ -30487,19 +30516,19 @@
         <v>1080</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="D492" s="4" t="s">
         <v>1081</v>
       </c>
       <c r="E492" s="4" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="F492" s="4" t="s">
         <v>1082</v>
       </c>
       <c r="G492" s="4" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="H492" s="3" t="s">
         <v>8</v>
@@ -30513,16 +30542,16 @@
         <v>1083</v>
       </c>
       <c r="C493" s="4" t="s">
+        <v>2867</v>
+      </c>
+      <c r="D493" s="4" t="s">
         <v>2868</v>
       </c>
-      <c r="D493" s="4" t="s">
+      <c r="E493" s="4" t="s">
         <v>2869</v>
       </c>
-      <c r="E493" s="4" t="s">
+      <c r="F493" s="4" t="s">
         <v>2870</v>
-      </c>
-      <c r="F493" s="4" t="s">
-        <v>2871</v>
       </c>
       <c r="G493" s="4" t="s">
         <v>1084</v>
@@ -30539,13 +30568,13 @@
         <v>1085</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="D494" s="4" t="s">
         <v>1086</v>
       </c>
       <c r="E494" s="4" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="F494" s="4" t="s">
         <v>1087</v>
@@ -30565,19 +30594,19 @@
         <v>1089</v>
       </c>
       <c r="C495" s="4" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="D495" s="4" t="s">
         <v>1090</v>
       </c>
       <c r="E495" s="4" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F495" s="4" t="s">
         <v>2875</v>
       </c>
-      <c r="F495" s="4" t="s">
+      <c r="G495" s="4" t="s">
         <v>2876</v>
-      </c>
-      <c r="G495" s="4" t="s">
-        <v>2877</v>
       </c>
       <c r="H495" s="3" t="s">
         <v>8</v>
@@ -30591,16 +30620,16 @@
         <v>1091</v>
       </c>
       <c r="C496" s="4" t="s">
+        <v>2877</v>
+      </c>
+      <c r="D496" s="4" t="s">
         <v>2878</v>
-      </c>
-      <c r="D496" s="4" t="s">
-        <v>2879</v>
       </c>
       <c r="E496" s="4" t="s">
         <v>1092</v>
       </c>
       <c r="F496" s="4" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="G496" s="3" t="s">
         <v>8</v>
@@ -30617,13 +30646,13 @@
         <v>1093</v>
       </c>
       <c r="C497" s="4" t="s">
+        <v>2880</v>
+      </c>
+      <c r="D497" s="4" t="s">
         <v>2881</v>
       </c>
-      <c r="D497" s="4" t="s">
+      <c r="E497" s="4" t="s">
         <v>2882</v>
-      </c>
-      <c r="E497" s="4" t="s">
-        <v>2883</v>
       </c>
       <c r="F497" s="4" t="s">
         <v>1094</v>
@@ -30643,19 +30672,19 @@
         <v>1096</v>
       </c>
       <c r="C498" s="4" t="s">
+        <v>2883</v>
+      </c>
+      <c r="D498" s="4" t="s">
         <v>2884</v>
       </c>
-      <c r="D498" s="4" t="s">
+      <c r="E498" s="4" t="s">
         <v>2885</v>
-      </c>
-      <c r="E498" s="4" t="s">
-        <v>2886</v>
       </c>
       <c r="F498" s="4" t="s">
         <v>1097</v>
       </c>
       <c r="G498" s="4" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="H498" s="3" t="s">
         <v>8</v>
@@ -30669,19 +30698,19 @@
         <v>1098</v>
       </c>
       <c r="C499" s="4" t="s">
+        <v>2887</v>
+      </c>
+      <c r="D499" s="4" t="s">
         <v>2888</v>
       </c>
-      <c r="D499" s="4" t="s">
+      <c r="E499" s="4" t="s">
         <v>2889</v>
       </c>
-      <c r="E499" s="4" t="s">
+      <c r="F499" s="4" t="s">
         <v>2890</v>
       </c>
-      <c r="F499" s="4" t="s">
+      <c r="G499" s="4" t="s">
         <v>2891</v>
-      </c>
-      <c r="G499" s="4" t="s">
-        <v>2892</v>
       </c>
       <c r="H499" s="3" t="s">
         <v>8</v>
@@ -30695,13 +30724,13 @@
         <v>1099</v>
       </c>
       <c r="C500" s="4" t="s">
+        <v>2892</v>
+      </c>
+      <c r="D500" s="4" t="s">
         <v>2893</v>
       </c>
-      <c r="D500" s="4" t="s">
+      <c r="E500" s="4" t="s">
         <v>2894</v>
-      </c>
-      <c r="E500" s="4" t="s">
-        <v>2895</v>
       </c>
       <c r="F500" s="4" t="s">
         <v>1100</v>
@@ -30721,10 +30750,10 @@
         <v>1102</v>
       </c>
       <c r="C501" s="4" t="s">
+        <v>2895</v>
+      </c>
+      <c r="D501" s="4" t="s">
         <v>2896</v>
-      </c>
-      <c r="D501" s="4" t="s">
-        <v>2897</v>
       </c>
       <c r="E501" s="4" t="s">
         <v>1103</v>
@@ -30747,22 +30776,22 @@
         <v>1105</v>
       </c>
       <c r="C502" s="4" t="s">
+        <v>2897</v>
+      </c>
+      <c r="D502" s="4" t="s">
         <v>2898</v>
       </c>
-      <c r="D502" s="4" t="s">
+      <c r="E502" s="4" t="s">
         <v>2899</v>
       </c>
-      <c r="E502" s="4" t="s">
+      <c r="F502" s="4" t="s">
         <v>2900</v>
       </c>
-      <c r="F502" s="4" t="s">
+      <c r="G502" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H502" s="4" t="s">
         <v>2901</v>
-      </c>
-      <c r="G502" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H502" s="4" t="s">
-        <v>2902</v>
       </c>
     </row>
     <row r="503" spans="1:8" ht="40" customHeight="1">
@@ -30773,22 +30802,22 @@
         <v>1106</v>
       </c>
       <c r="C503" s="4" t="s">
+        <v>2902</v>
+      </c>
+      <c r="D503" s="4" t="s">
         <v>2903</v>
-      </c>
-      <c r="D503" s="4" t="s">
-        <v>2904</v>
       </c>
       <c r="E503" s="4" t="s">
         <v>1107</v>
       </c>
       <c r="F503" s="4" t="s">
+        <v>2904</v>
+      </c>
+      <c r="G503" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H503" s="4" t="s">
         <v>2905</v>
-      </c>
-      <c r="G503" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H503" s="4" t="s">
-        <v>2906</v>
       </c>
     </row>
     <row r="504" spans="1:8" ht="40" customHeight="1">
@@ -30799,7 +30828,7 @@
         <v>1108</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="D504" s="4" t="s">
         <v>1109</v>
@@ -30808,13 +30837,13 @@
         <v>1110</v>
       </c>
       <c r="F504" s="4" t="s">
+        <v>2907</v>
+      </c>
+      <c r="G504" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H504" s="4" t="s">
         <v>2908</v>
-      </c>
-      <c r="G504" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H504" s="4" t="s">
-        <v>2909</v>
       </c>
     </row>
     <row r="505" spans="1:8" ht="40" customHeight="1">
@@ -30825,16 +30854,16 @@
         <v>1111</v>
       </c>
       <c r="C505" s="4" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="D505" s="4" t="s">
         <v>1112</v>
       </c>
       <c r="E505" s="4" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="F505" s="4" t="s">
-        <v>3416</v>
+        <v>3415</v>
       </c>
       <c r="G505" s="4" t="s">
         <v>1113</v>
@@ -30851,19 +30880,19 @@
         <v>1114</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="D506" s="4" t="s">
         <v>1115</v>
       </c>
       <c r="E506" s="4" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="F506" s="4" t="s">
         <v>1116</v>
       </c>
       <c r="G506" s="4" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="H506" s="3" t="s">
         <v>8</v>
@@ -30877,16 +30906,16 @@
         <v>1117</v>
       </c>
       <c r="C507" s="4" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="D507" s="4" t="s">
         <v>1118</v>
       </c>
       <c r="E507" s="4" t="s">
+        <v>2920</v>
+      </c>
+      <c r="F507" s="4" t="s">
         <v>2921</v>
-      </c>
-      <c r="F507" s="4" t="s">
-        <v>2922</v>
       </c>
       <c r="G507" s="4" t="s">
         <v>1119</v>
@@ -30903,19 +30932,19 @@
         <v>1120</v>
       </c>
       <c r="C508" s="4" t="s">
+        <v>2922</v>
+      </c>
+      <c r="D508" s="4" t="s">
         <v>2923</v>
       </c>
-      <c r="D508" s="4" t="s">
+      <c r="E508" s="4" t="s">
         <v>2924</v>
       </c>
-      <c r="E508" s="4" t="s">
+      <c r="F508" s="4" t="s">
         <v>2925</v>
       </c>
-      <c r="F508" s="4" t="s">
+      <c r="G508" s="4" t="s">
         <v>2926</v>
-      </c>
-      <c r="G508" s="4" t="s">
-        <v>2927</v>
       </c>
       <c r="H508" s="4" t="s">
         <v>1121</v>
@@ -30929,16 +30958,16 @@
         <v>1122</v>
       </c>
       <c r="C509" s="4" t="s">
+        <v>2927</v>
+      </c>
+      <c r="D509" s="4" t="s">
         <v>2928</v>
       </c>
-      <c r="D509" s="4" t="s">
+      <c r="E509" s="4" t="s">
         <v>2929</v>
       </c>
-      <c r="E509" s="4" t="s">
+      <c r="F509" s="4" t="s">
         <v>2930</v>
-      </c>
-      <c r="F509" s="4" t="s">
-        <v>2931</v>
       </c>
       <c r="G509" s="3" t="s">
         <v>8</v>
@@ -30955,16 +30984,16 @@
         <v>1123</v>
       </c>
       <c r="C510" s="4" t="s">
+        <v>2931</v>
+      </c>
+      <c r="D510" s="4" t="s">
         <v>2932</v>
       </c>
-      <c r="D510" s="4" t="s">
+      <c r="E510" s="4" t="s">
         <v>2933</v>
       </c>
-      <c r="E510" s="4" t="s">
+      <c r="F510" s="4" t="s">
         <v>2934</v>
-      </c>
-      <c r="F510" s="4" t="s">
-        <v>2935</v>
       </c>
       <c r="G510" s="4" t="s">
         <v>1124</v>
@@ -30981,19 +31010,19 @@
         <v>1125</v>
       </c>
       <c r="C511" s="4" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="D511" s="4" t="s">
         <v>1131</v>
       </c>
       <c r="E511" s="4" t="s">
+        <v>2936</v>
+      </c>
+      <c r="F511" s="4" t="s">
         <v>2937</v>
       </c>
-      <c r="F511" s="4" t="s">
+      <c r="G511" s="4" t="s">
         <v>2938</v>
-      </c>
-      <c r="G511" s="4" t="s">
-        <v>2939</v>
       </c>
       <c r="H511" s="3" t="s">
         <v>8</v>
@@ -31007,16 +31036,16 @@
         <v>1126</v>
       </c>
       <c r="C512" s="4" t="s">
+        <v>2939</v>
+      </c>
+      <c r="D512" s="4" t="s">
         <v>2940</v>
-      </c>
-      <c r="D512" s="4" t="s">
-        <v>2941</v>
       </c>
       <c r="E512" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="F512" s="4" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="G512" s="3" t="s">
         <v>8</v>
@@ -31033,16 +31062,16 @@
         <v>1128</v>
       </c>
       <c r="C513" s="4" t="s">
+        <v>2942</v>
+      </c>
+      <c r="D513" s="4" t="s">
+        <v>2946</v>
+      </c>
+      <c r="E513" s="4" t="s">
         <v>2943</v>
       </c>
-      <c r="D513" s="4" t="s">
-        <v>2947</v>
-      </c>
-      <c r="E513" s="4" t="s">
+      <c r="F513" s="4" t="s">
         <v>2944</v>
-      </c>
-      <c r="F513" s="4" t="s">
-        <v>2945</v>
       </c>
       <c r="G513" s="4" t="s">
         <v>1129</v>
@@ -31059,19 +31088,19 @@
         <v>1130</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="D514" s="4" t="s">
+        <v>2947</v>
+      </c>
+      <c r="E514" s="4" t="s">
+        <v>2950</v>
+      </c>
+      <c r="F514" s="4" t="s">
         <v>2948</v>
       </c>
-      <c r="E514" s="4" t="s">
-        <v>2951</v>
-      </c>
-      <c r="F514" s="4" t="s">
+      <c r="G514" s="4" t="s">
         <v>2949</v>
-      </c>
-      <c r="G514" s="4" t="s">
-        <v>2950</v>
       </c>
       <c r="H514" s="3" t="s">
         <v>8</v>
@@ -31085,16 +31114,16 @@
         <v>1132</v>
       </c>
       <c r="C515" s="4" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D515" s="4" t="s">
         <v>2952</v>
       </c>
-      <c r="D515" s="4" t="s">
+      <c r="E515" s="4" t="s">
         <v>2953</v>
       </c>
-      <c r="E515" s="4" t="s">
+      <c r="F515" s="4" t="s">
         <v>2954</v>
-      </c>
-      <c r="F515" s="4" t="s">
-        <v>2955</v>
       </c>
       <c r="G515" s="3" t="s">
         <v>8</v>
@@ -31111,16 +31140,16 @@
         <v>1133</v>
       </c>
       <c r="C516" s="4" t="s">
+        <v>2955</v>
+      </c>
+      <c r="D516" s="4" t="s">
         <v>2956</v>
       </c>
-      <c r="D516" s="4" t="s">
+      <c r="E516" s="4" t="s">
         <v>2957</v>
       </c>
-      <c r="E516" s="4" t="s">
+      <c r="F516" s="4" t="s">
         <v>2958</v>
-      </c>
-      <c r="F516" s="4" t="s">
-        <v>2959</v>
       </c>
       <c r="G516" s="3" t="s">
         <v>8</v>
@@ -31137,16 +31166,16 @@
         <v>1134</v>
       </c>
       <c r="C517" s="4" t="s">
+        <v>2959</v>
+      </c>
+      <c r="D517" s="4" t="s">
         <v>2960</v>
       </c>
-      <c r="D517" s="4" t="s">
+      <c r="E517" s="4" t="s">
         <v>2961</v>
       </c>
-      <c r="E517" s="4" t="s">
+      <c r="F517" s="4" t="s">
         <v>2962</v>
-      </c>
-      <c r="F517" s="4" t="s">
-        <v>2963</v>
       </c>
       <c r="G517" s="3" t="s">
         <v>8</v>
@@ -31163,10 +31192,10 @@
         <v>1135</v>
       </c>
       <c r="C518" s="4" t="s">
+        <v>2963</v>
+      </c>
+      <c r="D518" s="4" t="s">
         <v>2964</v>
-      </c>
-      <c r="D518" s="4" t="s">
-        <v>2965</v>
       </c>
       <c r="E518" s="4" t="s">
         <v>1136</v>
@@ -31189,16 +31218,16 @@
         <v>1138</v>
       </c>
       <c r="C519" s="4" t="s">
+        <v>2965</v>
+      </c>
+      <c r="D519" s="4" t="s">
         <v>2966</v>
       </c>
-      <c r="D519" s="4" t="s">
+      <c r="E519" s="4" t="s">
         <v>2967</v>
       </c>
-      <c r="E519" s="4" t="s">
+      <c r="F519" s="4" t="s">
         <v>2968</v>
-      </c>
-      <c r="F519" s="4" t="s">
-        <v>2969</v>
       </c>
       <c r="G519" s="3" t="s">
         <v>8</v>
@@ -31215,16 +31244,16 @@
         <v>1139</v>
       </c>
       <c r="C520" s="4" t="s">
+        <v>2969</v>
+      </c>
+      <c r="D520" s="4" t="s">
         <v>2970</v>
       </c>
-      <c r="D520" s="4" t="s">
+      <c r="E520" s="4" t="s">
         <v>2971</v>
       </c>
-      <c r="E520" s="4" t="s">
+      <c r="F520" s="4" t="s">
         <v>2972</v>
-      </c>
-      <c r="F520" s="4" t="s">
-        <v>2973</v>
       </c>
       <c r="G520" s="3" t="s">
         <v>8</v>
@@ -31241,19 +31270,19 @@
         <v>1140</v>
       </c>
       <c r="C521" s="4" t="s">
+        <v>2973</v>
+      </c>
+      <c r="D521" s="4" t="s">
         <v>2974</v>
       </c>
-      <c r="D521" s="4" t="s">
+      <c r="E521" s="4" t="s">
         <v>2975</v>
       </c>
-      <c r="E521" s="4" t="s">
+      <c r="F521" s="4" t="s">
         <v>2976</v>
       </c>
-      <c r="F521" s="4" t="s">
+      <c r="G521" s="4" t="s">
         <v>2977</v>
-      </c>
-      <c r="G521" s="4" t="s">
-        <v>2978</v>
       </c>
       <c r="H521" s="3" t="s">
         <v>8</v>
@@ -31267,19 +31296,19 @@
         <v>1141</v>
       </c>
       <c r="C522" s="4" t="s">
+        <v>2978</v>
+      </c>
+      <c r="D522" s="4" t="s">
         <v>2979</v>
       </c>
-      <c r="D522" s="4" t="s">
+      <c r="E522" s="4" t="s">
         <v>2980</v>
       </c>
-      <c r="E522" s="4" t="s">
+      <c r="F522" s="4" t="s">
         <v>2981</v>
       </c>
-      <c r="F522" s="4" t="s">
+      <c r="G522" s="4" t="s">
         <v>2982</v>
-      </c>
-      <c r="G522" s="4" t="s">
-        <v>2983</v>
       </c>
       <c r="H522" s="3" t="s">
         <v>8</v>
@@ -31293,13 +31322,13 @@
         <v>1142</v>
       </c>
       <c r="C523" s="4" t="s">
+        <v>2983</v>
+      </c>
+      <c r="D523" s="4" t="s">
         <v>2984</v>
       </c>
-      <c r="D523" s="4" t="s">
+      <c r="E523" s="4" t="s">
         <v>2985</v>
-      </c>
-      <c r="E523" s="4" t="s">
-        <v>2986</v>
       </c>
       <c r="F523" s="4" t="s">
         <v>1143</v>
@@ -31319,13 +31348,13 @@
         <v>1145</v>
       </c>
       <c r="C524" s="4" t="s">
+        <v>2986</v>
+      </c>
+      <c r="D524" s="4" t="s">
         <v>2987</v>
       </c>
-      <c r="D524" s="4" t="s">
+      <c r="E524" s="4" t="s">
         <v>2988</v>
-      </c>
-      <c r="E524" s="4" t="s">
-        <v>2989</v>
       </c>
       <c r="F524" s="4" t="s">
         <v>1146</v>
@@ -31345,19 +31374,19 @@
         <v>1148</v>
       </c>
       <c r="C525" s="4" t="s">
+        <v>2989</v>
+      </c>
+      <c r="D525" s="4" t="s">
         <v>2990</v>
       </c>
-      <c r="D525" s="4" t="s">
+      <c r="E525" s="4" t="s">
         <v>2991</v>
-      </c>
-      <c r="E525" s="4" t="s">
-        <v>2992</v>
       </c>
       <c r="F525" s="4" t="s">
         <v>1149</v>
       </c>
       <c r="G525" s="4" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="H525" s="3" t="s">
         <v>8</v>
@@ -31371,13 +31400,13 @@
         <v>1150</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="D526" s="4" t="s">
         <v>1151</v>
       </c>
       <c r="E526" s="4" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="F526" s="4" t="s">
         <v>1152</v>
@@ -31397,16 +31426,16 @@
         <v>1154</v>
       </c>
       <c r="C527" s="4" t="s">
+        <v>2995</v>
+      </c>
+      <c r="D527" s="4" t="s">
         <v>2996</v>
       </c>
-      <c r="D527" s="4" t="s">
+      <c r="E527" s="4" t="s">
         <v>2997</v>
       </c>
-      <c r="E527" s="4" t="s">
-        <v>2998</v>
-      </c>
       <c r="F527" s="4" t="s">
-        <v>3417</v>
+        <v>3416</v>
       </c>
       <c r="G527" s="3" t="s">
         <v>8</v>
@@ -31423,16 +31452,16 @@
         <v>1155</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="D528" s="4" t="s">
         <v>1156</v>
       </c>
       <c r="E528" s="4" t="s">
+        <v>2999</v>
+      </c>
+      <c r="F528" s="4" t="s">
         <v>3000</v>
-      </c>
-      <c r="F528" s="4" t="s">
-        <v>3001</v>
       </c>
       <c r="G528" s="3" t="s">
         <v>8</v>
@@ -31449,16 +31478,16 @@
         <v>1157</v>
       </c>
       <c r="C529" s="4" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="D529" s="4" t="s">
+        <v>3001</v>
+      </c>
+      <c r="E529" s="4" t="s">
         <v>3002</v>
       </c>
-      <c r="E529" s="4" t="s">
+      <c r="F529" s="4" t="s">
         <v>3003</v>
-      </c>
-      <c r="F529" s="4" t="s">
-        <v>3004</v>
       </c>
       <c r="G529" s="4" t="s">
         <v>1158</v>
@@ -31475,16 +31504,16 @@
         <v>1159</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="D530" s="4" t="s">
         <v>1160</v>
       </c>
       <c r="E530" s="4" t="s">
+        <v>3005</v>
+      </c>
+      <c r="F530" s="4" t="s">
         <v>3006</v>
-      </c>
-      <c r="F530" s="4" t="s">
-        <v>3007</v>
       </c>
       <c r="G530" s="3" t="s">
         <v>8</v>
@@ -31501,19 +31530,19 @@
         <v>1161</v>
       </c>
       <c r="C531" s="4" t="s">
+        <v>3007</v>
+      </c>
+      <c r="D531" s="4" t="s">
         <v>3008</v>
       </c>
-      <c r="D531" s="4" t="s">
+      <c r="E531" s="4" t="s">
         <v>3009</v>
-      </c>
-      <c r="E531" s="4" t="s">
-        <v>3010</v>
       </c>
       <c r="F531" s="4" t="s">
         <v>1162</v>
       </c>
       <c r="G531" s="4" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="H531" s="3" t="s">
         <v>8</v>
@@ -31527,19 +31556,19 @@
         <v>1163</v>
       </c>
       <c r="C532" s="4" t="s">
+        <v>3011</v>
+      </c>
+      <c r="D532" s="4" t="s">
         <v>3012</v>
       </c>
-      <c r="D532" s="4" t="s">
+      <c r="E532" s="4" t="s">
         <v>3013</v>
       </c>
-      <c r="E532" s="4" t="s">
+      <c r="F532" s="4" t="s">
         <v>3014</v>
       </c>
-      <c r="F532" s="4" t="s">
+      <c r="G532" s="4" t="s">
         <v>3015</v>
-      </c>
-      <c r="G532" s="4" t="s">
-        <v>3016</v>
       </c>
       <c r="H532" s="3" t="s">
         <v>8</v>
@@ -31553,16 +31582,16 @@
         <v>1164</v>
       </c>
       <c r="C533" s="4" t="s">
+        <v>3016</v>
+      </c>
+      <c r="D533" s="4" t="s">
         <v>3017</v>
       </c>
-      <c r="D533" s="4" t="s">
+      <c r="E533" s="4" t="s">
         <v>3018</v>
       </c>
-      <c r="E533" s="4" t="s">
+      <c r="F533" s="4" t="s">
         <v>3019</v>
-      </c>
-      <c r="F533" s="4" t="s">
-        <v>3020</v>
       </c>
       <c r="G533" s="3" t="s">
         <v>8</v>
@@ -31579,16 +31608,16 @@
         <v>1165</v>
       </c>
       <c r="C534" s="4" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="D534" s="4" t="s">
         <v>1166</v>
       </c>
       <c r="E534" s="4" t="s">
+        <v>3021</v>
+      </c>
+      <c r="F534" s="4" t="s">
         <v>3022</v>
-      </c>
-      <c r="F534" s="4" t="s">
-        <v>3023</v>
       </c>
       <c r="G534" s="4" t="s">
         <v>1167</v>
@@ -31605,13 +31634,13 @@
         <v>1168</v>
       </c>
       <c r="C535" s="4" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="D535" s="4" t="s">
         <v>1169</v>
       </c>
       <c r="E535" s="4" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="F535" s="4" t="s">
         <v>1170</v>
@@ -31631,16 +31660,16 @@
         <v>1172</v>
       </c>
       <c r="C536" s="4" t="s">
+        <v>3025</v>
+      </c>
+      <c r="D536" s="4" t="s">
         <v>3026</v>
       </c>
-      <c r="D536" s="4" t="s">
+      <c r="E536" s="4" t="s">
         <v>3027</v>
       </c>
-      <c r="E536" s="4" t="s">
+      <c r="F536" s="4" t="s">
         <v>3028</v>
-      </c>
-      <c r="F536" s="4" t="s">
-        <v>3029</v>
       </c>
       <c r="G536" s="4" t="s">
         <v>1173</v>
@@ -31657,16 +31686,16 @@
         <v>1174</v>
       </c>
       <c r="C537" s="4" t="s">
+        <v>3029</v>
+      </c>
+      <c r="D537" s="4" t="s">
+        <v>3017</v>
+      </c>
+      <c r="E537" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F537" s="4" t="s">
         <v>3030</v>
-      </c>
-      <c r="D537" s="4" t="s">
-        <v>3018</v>
-      </c>
-      <c r="E537" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F537" s="4" t="s">
-        <v>3031</v>
       </c>
       <c r="G537" s="3" t="s">
         <v>8</v>
@@ -31686,10 +31715,10 @@
         <v>1176</v>
       </c>
       <c r="D538" s="4" t="s">
+        <v>3031</v>
+      </c>
+      <c r="E538" s="4" t="s">
         <v>3032</v>
-      </c>
-      <c r="E538" s="4" t="s">
-        <v>3033</v>
       </c>
       <c r="F538" s="4" t="s">
         <v>1177</v>
@@ -31712,13 +31741,13 @@
         <v>1176</v>
       </c>
       <c r="D539" s="4" t="s">
+        <v>3033</v>
+      </c>
+      <c r="E539" s="4" t="s">
         <v>3034</v>
       </c>
-      <c r="E539" s="4" t="s">
+      <c r="F539" s="4" t="s">
         <v>3035</v>
-      </c>
-      <c r="F539" s="4" t="s">
-        <v>3036</v>
       </c>
       <c r="G539" s="3" t="s">
         <v>8</v>
@@ -31735,19 +31764,19 @@
         <v>1179</v>
       </c>
       <c r="C540" s="4" t="s">
+        <v>3036</v>
+      </c>
+      <c r="D540" s="4" t="s">
         <v>3037</v>
-      </c>
-      <c r="D540" s="4" t="s">
-        <v>3038</v>
       </c>
       <c r="E540" s="4" t="s">
         <v>1180</v>
       </c>
       <c r="F540" s="4" t="s">
+        <v>3038</v>
+      </c>
+      <c r="G540" s="4" t="s">
         <v>3039</v>
-      </c>
-      <c r="G540" s="4" t="s">
-        <v>3040</v>
       </c>
       <c r="H540" s="3" t="s">
         <v>8</v>
@@ -31761,19 +31790,19 @@
         <v>1181</v>
       </c>
       <c r="C541" s="4" t="s">
+        <v>3040</v>
+      </c>
+      <c r="D541" s="4" t="s">
         <v>3041</v>
       </c>
-      <c r="D541" s="4" t="s">
+      <c r="E541" s="4" t="s">
         <v>3042</v>
       </c>
-      <c r="E541" s="4" t="s">
+      <c r="F541" s="4" t="s">
         <v>3043</v>
       </c>
-      <c r="F541" s="4" t="s">
+      <c r="G541" s="4" t="s">
         <v>3044</v>
-      </c>
-      <c r="G541" s="4" t="s">
-        <v>3045</v>
       </c>
       <c r="H541" s="3" t="s">
         <v>8</v>
@@ -31787,16 +31816,16 @@
         <v>1182</v>
       </c>
       <c r="C542" s="4" t="s">
+        <v>3045</v>
+      </c>
+      <c r="D542" s="4" t="s">
         <v>3046</v>
       </c>
-      <c r="D542" s="4" t="s">
+      <c r="E542" s="4" t="s">
         <v>3047</v>
       </c>
-      <c r="E542" s="4" t="s">
+      <c r="F542" s="4" t="s">
         <v>3048</v>
-      </c>
-      <c r="F542" s="4" t="s">
-        <v>3049</v>
       </c>
       <c r="G542" s="3" t="s">
         <v>8</v>
@@ -31813,16 +31842,16 @@
         <v>1183</v>
       </c>
       <c r="C543" s="4" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="D543" s="4" t="s">
         <v>1184</v>
       </c>
       <c r="E543" s="4" t="s">
+        <v>3050</v>
+      </c>
+      <c r="F543" s="4" t="s">
         <v>3051</v>
-      </c>
-      <c r="F543" s="4" t="s">
-        <v>3052</v>
       </c>
       <c r="G543" s="3" t="s">
         <v>8</v>
@@ -31839,16 +31868,16 @@
         <v>1185</v>
       </c>
       <c r="C544" s="4" t="s">
+        <v>3052</v>
+      </c>
+      <c r="D544" s="4" t="s">
         <v>3053</v>
       </c>
-      <c r="D544" s="4" t="s">
+      <c r="E544" s="4" t="s">
         <v>3054</v>
       </c>
-      <c r="E544" s="4" t="s">
+      <c r="F544" s="4" t="s">
         <v>3055</v>
-      </c>
-      <c r="F544" s="4" t="s">
-        <v>3056</v>
       </c>
       <c r="G544" s="3" t="s">
         <v>8</v>
@@ -31865,10 +31894,10 @@
         <v>1186</v>
       </c>
       <c r="C545" s="4" t="s">
+        <v>3056</v>
+      </c>
+      <c r="D545" s="4" t="s">
         <v>3057</v>
-      </c>
-      <c r="D545" s="4" t="s">
-        <v>3058</v>
       </c>
       <c r="E545" s="4" t="s">
         <v>1187</v>
@@ -31880,7 +31909,7 @@
         <v>1189</v>
       </c>
       <c r="H545" s="4" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="546" spans="1:8" ht="40" customHeight="1">
@@ -31891,7 +31920,7 @@
         <v>1190</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="D546" s="4" t="s">
         <v>1191</v>
@@ -31917,16 +31946,16 @@
         <v>1194</v>
       </c>
       <c r="C547" s="4" t="s">
+        <v>3060</v>
+      </c>
+      <c r="D547" s="4" t="s">
         <v>3061</v>
       </c>
-      <c r="D547" s="4" t="s">
+      <c r="E547" s="4" t="s">
         <v>3062</v>
       </c>
-      <c r="E547" s="4" t="s">
+      <c r="F547" s="4" t="s">
         <v>3063</v>
-      </c>
-      <c r="F547" s="4" t="s">
-        <v>3064</v>
       </c>
       <c r="G547" s="3" t="s">
         <v>8</v>
@@ -31943,13 +31972,13 @@
         <v>1195</v>
       </c>
       <c r="C548" s="4" t="s">
+        <v>3064</v>
+      </c>
+      <c r="D548" s="4" t="s">
         <v>3065</v>
       </c>
-      <c r="D548" s="4" t="s">
+      <c r="E548" s="4" t="s">
         <v>3066</v>
-      </c>
-      <c r="E548" s="4" t="s">
-        <v>3067</v>
       </c>
       <c r="F548" s="4" t="s">
         <v>1196</v>
@@ -31969,19 +31998,19 @@
         <v>1198</v>
       </c>
       <c r="C549" s="4" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="D549" s="4" t="s">
         <v>1199</v>
       </c>
       <c r="E549" s="4" t="s">
+        <v>3068</v>
+      </c>
+      <c r="F549" s="4" t="s">
         <v>3069</v>
       </c>
-      <c r="F549" s="4" t="s">
+      <c r="G549" s="4" t="s">
         <v>3070</v>
-      </c>
-      <c r="G549" s="4" t="s">
-        <v>3071</v>
       </c>
       <c r="H549" s="3" t="s">
         <v>8</v>
@@ -31995,7 +32024,7 @@
         <v>1200</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="D550" s="4" t="s">
         <v>1201</v>
@@ -32004,7 +32033,7 @@
         <v>1202</v>
       </c>
       <c r="F550" s="4" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="G550" s="3" t="s">
         <v>8</v>
@@ -32021,16 +32050,16 @@
         <v>1203</v>
       </c>
       <c r="C551" s="4" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="D551" s="4" t="s">
         <v>1204</v>
       </c>
       <c r="E551" s="4" t="s">
+        <v>3074</v>
+      </c>
+      <c r="F551" s="4" t="s">
         <v>3075</v>
-      </c>
-      <c r="F551" s="4" t="s">
-        <v>3076</v>
       </c>
       <c r="G551" s="3" t="s">
         <v>8</v>
@@ -32047,16 +32076,16 @@
         <v>1205</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="D552" s="4" t="s">
         <v>1206</v>
       </c>
       <c r="E552" s="4" t="s">
+        <v>3077</v>
+      </c>
+      <c r="F552" s="4" t="s">
         <v>3078</v>
-      </c>
-      <c r="F552" s="4" t="s">
-        <v>3079</v>
       </c>
       <c r="G552" s="4" t="s">
         <v>1207</v>
@@ -32073,16 +32102,16 @@
         <v>1208</v>
       </c>
       <c r="C553" s="4" t="s">
+        <v>3079</v>
+      </c>
+      <c r="D553" s="4" t="s">
         <v>3080</v>
-      </c>
-      <c r="D553" s="4" t="s">
-        <v>3081</v>
       </c>
       <c r="E553" s="4" t="s">
         <v>1209</v>
       </c>
       <c r="F553" s="4" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="G553" s="3" t="s">
         <v>8</v>
@@ -32099,13 +32128,13 @@
         <v>1210</v>
       </c>
       <c r="C554" s="4" t="s">
+        <v>3082</v>
+      </c>
+      <c r="D554" s="4" t="s">
         <v>3083</v>
       </c>
-      <c r="D554" s="4" t="s">
+      <c r="E554" s="4" t="s">
         <v>3084</v>
-      </c>
-      <c r="E554" s="4" t="s">
-        <v>3085</v>
       </c>
       <c r="F554" s="4" t="s">
         <v>1211</v>
@@ -32125,7 +32154,7 @@
         <v>1213</v>
       </c>
       <c r="C555" s="4" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="D555" s="4" t="s">
         <v>1214</v>
@@ -32134,7 +32163,7 @@
         <v>1215</v>
       </c>
       <c r="F555" s="4" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="G555" s="3" t="s">
         <v>8</v>
@@ -32160,7 +32189,7 @@
         <v>1219</v>
       </c>
       <c r="F556" s="4" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="G556" s="3" t="s">
         <v>8</v>
@@ -32177,13 +32206,13 @@
         <v>1220</v>
       </c>
       <c r="C557" s="4" t="s">
+        <v>3088</v>
+      </c>
+      <c r="D557" s="4" t="s">
         <v>3089</v>
       </c>
-      <c r="D557" s="4" t="s">
+      <c r="E557" s="4" t="s">
         <v>3090</v>
-      </c>
-      <c r="E557" s="4" t="s">
-        <v>3091</v>
       </c>
       <c r="F557" s="4" t="s">
         <v>1221</v>
@@ -32203,16 +32232,16 @@
         <v>1222</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="D558" s="4" t="s">
         <v>1223</v>
       </c>
       <c r="E558" s="4" t="s">
+        <v>3092</v>
+      </c>
+      <c r="F558" s="4" t="s">
         <v>3093</v>
-      </c>
-      <c r="F558" s="4" t="s">
-        <v>3094</v>
       </c>
       <c r="G558" s="3" t="s">
         <v>8</v>
@@ -32229,16 +32258,16 @@
         <v>1224</v>
       </c>
       <c r="C559" s="4" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="D559" s="4" t="s">
         <v>1223</v>
       </c>
       <c r="E559" s="4" t="s">
+        <v>3094</v>
+      </c>
+      <c r="F559" s="4" t="s">
         <v>3095</v>
-      </c>
-      <c r="F559" s="4" t="s">
-        <v>3096</v>
       </c>
       <c r="G559" s="3" t="s">
         <v>8</v>
@@ -32255,16 +32284,16 @@
         <v>1225</v>
       </c>
       <c r="C560" s="4" t="s">
+        <v>3096</v>
+      </c>
+      <c r="D560" s="4" t="s">
         <v>3097</v>
       </c>
-      <c r="D560" s="4" t="s">
+      <c r="E560" s="4" t="s">
         <v>3098</v>
       </c>
-      <c r="E560" s="4" t="s">
+      <c r="F560" s="4" t="s">
         <v>3099</v>
-      </c>
-      <c r="F560" s="4" t="s">
-        <v>3100</v>
       </c>
       <c r="G560" s="3" t="s">
         <v>8</v>
@@ -32281,16 +32310,16 @@
         <v>1226</v>
       </c>
       <c r="C561" s="4" t="s">
+        <v>3100</v>
+      </c>
+      <c r="D561" s="4" t="s">
         <v>3101</v>
       </c>
-      <c r="D561" s="4" t="s">
+      <c r="E561" s="4" t="s">
         <v>3102</v>
       </c>
-      <c r="E561" s="4" t="s">
+      <c r="F561" s="4" t="s">
         <v>3103</v>
-      </c>
-      <c r="F561" s="4" t="s">
-        <v>3104</v>
       </c>
       <c r="G561" s="3" t="s">
         <v>8</v>
@@ -32307,16 +32336,16 @@
         <v>1227</v>
       </c>
       <c r="C562" s="4" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="D562" s="4" t="s">
         <v>1228</v>
       </c>
       <c r="E562" s="4" t="s">
+        <v>3105</v>
+      </c>
+      <c r="F562" s="4" t="s">
         <v>3106</v>
-      </c>
-      <c r="F562" s="4" t="s">
-        <v>3107</v>
       </c>
       <c r="G562" s="3" t="s">
         <v>8</v>
@@ -32333,19 +32362,19 @@
         <v>1229</v>
       </c>
       <c r="C563" s="4" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="D563" s="4" t="s">
         <v>1230</v>
       </c>
       <c r="E563" s="4" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="F563" s="4" t="s">
         <v>1231</v>
       </c>
       <c r="G563" s="4" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="H563" s="3" t="s">
         <v>8</v>
@@ -32359,22 +32388,22 @@
         <v>1232</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="D564" s="4" t="s">
         <v>1233</v>
       </c>
       <c r="E564" s="4" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="F564" s="4" t="s">
         <v>1234</v>
       </c>
       <c r="G564" s="4" t="s">
+        <v>3112</v>
+      </c>
+      <c r="H564" s="4" t="s">
         <v>3113</v>
-      </c>
-      <c r="H564" s="4" t="s">
-        <v>3114</v>
       </c>
     </row>
     <row r="565" spans="1:8" ht="40" customHeight="1">
@@ -32385,16 +32414,16 @@
         <v>1235</v>
       </c>
       <c r="C565" s="4" t="s">
+        <v>3114</v>
+      </c>
+      <c r="D565" s="4" t="s">
         <v>3115</v>
       </c>
-      <c r="D565" s="4" t="s">
+      <c r="E565" s="4" t="s">
         <v>3116</v>
       </c>
-      <c r="E565" s="4" t="s">
+      <c r="F565" s="4" t="s">
         <v>3117</v>
-      </c>
-      <c r="F565" s="4" t="s">
-        <v>3118</v>
       </c>
       <c r="G565" s="3" t="s">
         <v>8</v>
@@ -32411,7 +32440,7 @@
         <v>1236</v>
       </c>
       <c r="C566" s="4" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="D566" s="4" t="s">
         <v>1237</v>
@@ -32437,16 +32466,16 @@
         <v>1241</v>
       </c>
       <c r="C567" s="4" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="D567" s="4" t="s">
         <v>1242</v>
       </c>
       <c r="E567" s="4" t="s">
+        <v>3120</v>
+      </c>
+      <c r="F567" s="4" t="s">
         <v>3121</v>
-      </c>
-      <c r="F567" s="4" t="s">
-        <v>3122</v>
       </c>
       <c r="G567" s="3" t="s">
         <v>8</v>
@@ -32463,13 +32492,13 @@
         <v>1243</v>
       </c>
       <c r="C568" s="4" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="D568" s="4" t="s">
         <v>1244</v>
       </c>
       <c r="E568" s="4" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="F568" s="4" t="s">
         <v>1245</v>
@@ -32489,16 +32518,16 @@
         <v>1246</v>
       </c>
       <c r="C569" s="4" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="D569" s="4" t="s">
         <v>1247</v>
       </c>
       <c r="E569" s="4" t="s">
+        <v>3125</v>
+      </c>
+      <c r="F569" s="4" t="s">
         <v>3126</v>
-      </c>
-      <c r="F569" s="4" t="s">
-        <v>3127</v>
       </c>
       <c r="G569" s="3" t="s">
         <v>8</v>
@@ -32515,16 +32544,16 @@
         <v>1248</v>
       </c>
       <c r="C570" s="4" t="s">
+        <v>3127</v>
+      </c>
+      <c r="D570" s="4" t="s">
         <v>3128</v>
       </c>
-      <c r="D570" s="4" t="s">
+      <c r="E570" s="4" t="s">
         <v>3129</v>
       </c>
-      <c r="E570" s="4" t="s">
+      <c r="F570" s="4" t="s">
         <v>3130</v>
-      </c>
-      <c r="F570" s="4" t="s">
-        <v>3131</v>
       </c>
       <c r="G570" s="3" t="s">
         <v>8</v>
@@ -32541,22 +32570,22 @@
         <v>1249</v>
       </c>
       <c r="C571" s="4" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="D571" s="4" t="s">
+        <v>3131</v>
+      </c>
+      <c r="E571" s="4" t="s">
         <v>3132</v>
       </c>
-      <c r="E571" s="4" t="s">
+      <c r="F571" s="4" t="s">
         <v>3133</v>
       </c>
-      <c r="F571" s="4" t="s">
+      <c r="G571" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H571" s="4" t="s">
         <v>3134</v>
-      </c>
-      <c r="G571" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H571" s="4" t="s">
-        <v>3135</v>
       </c>
     </row>
     <row r="572" spans="1:8" ht="40" customHeight="1">
@@ -32567,10 +32596,10 @@
         <v>1250</v>
       </c>
       <c r="C572" s="4" t="s">
+        <v>3135</v>
+      </c>
+      <c r="D572" s="4" t="s">
         <v>3136</v>
-      </c>
-      <c r="D572" s="4" t="s">
-        <v>3137</v>
       </c>
       <c r="E572" s="4" t="s">
         <v>1251</v>
@@ -32579,7 +32608,7 @@
         <v>1252</v>
       </c>
       <c r="G572" s="4" t="s">
-        <v>3418</v>
+        <v>3417</v>
       </c>
       <c r="H572" s="3" t="s">
         <v>8</v>
@@ -32593,19 +32622,19 @@
         <v>1253</v>
       </c>
       <c r="C573" s="4" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="D573" s="4" t="s">
         <v>1254</v>
       </c>
       <c r="E573" s="4" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="F573" s="4" t="s">
         <v>1255</v>
       </c>
       <c r="G573" s="4" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="H573" s="3" t="s">
         <v>8</v>
@@ -32619,19 +32648,19 @@
         <v>1256</v>
       </c>
       <c r="C574" s="4" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="D574" s="4" t="s">
         <v>1257</v>
       </c>
       <c r="E574" s="4" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="F574" s="4" t="s">
         <v>1258</v>
       </c>
       <c r="G574" s="4" t="s">
-        <v>3419</v>
+        <v>3418</v>
       </c>
       <c r="H574" s="3" t="s">
         <v>8</v>
@@ -32645,7 +32674,7 @@
         <v>1259</v>
       </c>
       <c r="C575" s="4" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="D575" s="4" t="s">
         <v>1260</v>
@@ -32657,7 +32686,7 @@
         <v>1262</v>
       </c>
       <c r="G575" s="4" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="H575" s="3" t="s">
         <v>8</v>
@@ -32671,13 +32700,13 @@
         <v>1263</v>
       </c>
       <c r="C576" s="4" t="s">
+        <v>3144</v>
+      </c>
+      <c r="D576" s="4" t="s">
         <v>3145</v>
       </c>
-      <c r="D576" s="4" t="s">
+      <c r="E576" s="4" t="s">
         <v>3146</v>
-      </c>
-      <c r="E576" s="4" t="s">
-        <v>3147</v>
       </c>
       <c r="F576" s="4" t="s">
         <v>1264</v>
@@ -32697,19 +32726,19 @@
         <v>1266</v>
       </c>
       <c r="C577" s="4" t="s">
+        <v>3147</v>
+      </c>
+      <c r="D577" s="4" t="s">
         <v>3148</v>
       </c>
-      <c r="D577" s="4" t="s">
+      <c r="E577" s="4" t="s">
         <v>3149</v>
-      </c>
-      <c r="E577" s="4" t="s">
-        <v>3150</v>
       </c>
       <c r="F577" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="G577" s="4" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="H577" s="3" t="s">
         <v>8</v>
@@ -32723,16 +32752,16 @@
         <v>1268</v>
       </c>
       <c r="C578" s="4" t="s">
+        <v>3150</v>
+      </c>
+      <c r="D578" s="4" t="s">
         <v>3151</v>
       </c>
-      <c r="D578" s="4" t="s">
+      <c r="E578" s="4" t="s">
         <v>3152</v>
       </c>
-      <c r="E578" s="4" t="s">
+      <c r="F578" s="4" t="s">
         <v>3153</v>
-      </c>
-      <c r="F578" s="4" t="s">
-        <v>3154</v>
       </c>
       <c r="G578" s="3" t="s">
         <v>8</v>
@@ -32749,16 +32778,16 @@
         <v>1269</v>
       </c>
       <c r="C579" s="4" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="D579" s="4" t="s">
         <v>1270</v>
       </c>
       <c r="E579" s="4" t="s">
+        <v>3155</v>
+      </c>
+      <c r="F579" s="4" t="s">
         <v>3156</v>
-      </c>
-      <c r="F579" s="4" t="s">
-        <v>3157</v>
       </c>
       <c r="G579" s="3" t="s">
         <v>8</v>
@@ -32775,7 +32804,7 @@
         <v>1271</v>
       </c>
       <c r="C580" s="4" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="D580" s="4" t="s">
         <v>1272</v>
@@ -32784,7 +32813,7 @@
         <v>1273</v>
       </c>
       <c r="F580" s="4" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="G580" s="4" t="s">
         <v>1274</v>
@@ -32801,7 +32830,7 @@
         <v>1275</v>
       </c>
       <c r="C581" s="4" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="D581" s="4" t="s">
         <v>1276</v>
@@ -32810,7 +32839,7 @@
         <v>1277</v>
       </c>
       <c r="F581" s="4" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="G581" s="3" t="s">
         <v>8</v>
@@ -32827,7 +32856,7 @@
         <v>1278</v>
       </c>
       <c r="C582" s="4" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="D582" s="4" t="s">
         <v>1279</v>
@@ -32839,7 +32868,7 @@
         <v>1281</v>
       </c>
       <c r="G582" s="4" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="H582" s="3" t="s">
         <v>8</v>
@@ -32853,7 +32882,7 @@
         <v>1282</v>
       </c>
       <c r="C583" s="4" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="D583" s="4" t="s">
         <v>1283</v>
@@ -32862,7 +32891,7 @@
         <v>1284</v>
       </c>
       <c r="F583" s="4" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="G583" s="3" t="s">
         <v>8</v>
@@ -32879,7 +32908,7 @@
         <v>1285</v>
       </c>
       <c r="C584" s="4" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="D584" s="4" t="s">
         <v>1286</v>
@@ -32905,19 +32934,19 @@
         <v>1290</v>
       </c>
       <c r="C585" s="4" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="D585" s="4" t="s">
         <v>1291</v>
       </c>
       <c r="E585" s="4" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="F585" s="4" t="s">
         <v>1292</v>
       </c>
       <c r="G585" s="4" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="H585" s="3" t="s">
         <v>8</v>
@@ -32931,16 +32960,16 @@
         <v>1293</v>
       </c>
       <c r="C586" s="4" t="s">
+        <v>3169</v>
+      </c>
+      <c r="D586" s="4" t="s">
         <v>3170</v>
       </c>
-      <c r="D586" s="4" t="s">
+      <c r="E586" s="4" t="s">
         <v>3171</v>
       </c>
-      <c r="E586" s="4" t="s">
+      <c r="F586" s="4" t="s">
         <v>3172</v>
-      </c>
-      <c r="F586" s="4" t="s">
-        <v>3173</v>
       </c>
       <c r="G586" s="3" t="s">
         <v>8</v>
@@ -32957,7 +32986,7 @@
         <v>1294</v>
       </c>
       <c r="C587" s="4" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="D587" s="4" t="s">
         <v>1295</v>
@@ -32966,7 +32995,7 @@
         <v>1296</v>
       </c>
       <c r="F587" s="4" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="G587" s="4" t="s">
         <v>1297</v>
@@ -32983,13 +33012,13 @@
         <v>1298</v>
       </c>
       <c r="C588" s="4" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="D588" s="4" t="s">
         <v>1299</v>
       </c>
       <c r="E588" s="4" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="F588" s="4" t="s">
         <v>1300</v>
@@ -33009,19 +33038,19 @@
         <v>1302</v>
       </c>
       <c r="C589" s="4" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="D589" s="4" t="s">
         <v>1303</v>
       </c>
       <c r="E589" s="4" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="F589" s="4" t="s">
         <v>1304</v>
       </c>
       <c r="G589" s="4" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="H589" s="3" t="s">
         <v>8</v>
@@ -33035,7 +33064,7 @@
         <v>1305</v>
       </c>
       <c r="C590" s="4" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="D590" s="4" t="s">
         <v>1306</v>
@@ -33061,16 +33090,16 @@
         <v>1309</v>
       </c>
       <c r="C591" s="4" t="s">
+        <v>3181</v>
+      </c>
+      <c r="D591" s="4" t="s">
         <v>3182</v>
       </c>
-      <c r="D591" s="4" t="s">
+      <c r="E591" s="4" t="s">
         <v>3183</v>
       </c>
-      <c r="E591" s="4" t="s">
+      <c r="F591" s="4" t="s">
         <v>3184</v>
-      </c>
-      <c r="F591" s="4" t="s">
-        <v>3185</v>
       </c>
       <c r="G591" s="3" t="s">
         <v>8</v>
@@ -33087,7 +33116,7 @@
         <v>1310</v>
       </c>
       <c r="C592" s="4" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="D592" s="4" t="s">
         <v>1311</v>
@@ -33096,7 +33125,7 @@
         <v>1312</v>
       </c>
       <c r="F592" s="4" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="G592" s="3" t="s">
         <v>8</v>
@@ -33113,22 +33142,22 @@
         <v>1313</v>
       </c>
       <c r="C593" s="4" t="s">
+        <v>3186</v>
+      </c>
+      <c r="D593" s="4" t="s">
         <v>3187</v>
       </c>
-      <c r="D593" s="4" t="s">
+      <c r="E593" s="4" t="s">
         <v>3188</v>
       </c>
-      <c r="E593" s="4" t="s">
+      <c r="F593" s="4" t="s">
         <v>3189</v>
-      </c>
-      <c r="F593" s="4" t="s">
-        <v>3190</v>
       </c>
       <c r="G593" s="4" t="s">
         <v>1314</v>
       </c>
       <c r="H593" s="4" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="594" spans="1:8" ht="40" customHeight="1">
@@ -33139,16 +33168,16 @@
         <v>1315</v>
       </c>
       <c r="C594" s="4" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="D594" s="4" t="s">
         <v>1316</v>
       </c>
       <c r="E594" s="4" t="s">
+        <v>3192</v>
+      </c>
+      <c r="F594" s="4" t="s">
         <v>3193</v>
-      </c>
-      <c r="F594" s="4" t="s">
-        <v>3194</v>
       </c>
       <c r="G594" s="4" t="s">
         <v>1317</v>
@@ -33165,16 +33194,16 @@
         <v>1318</v>
       </c>
       <c r="C595" s="4" t="s">
+        <v>3194</v>
+      </c>
+      <c r="D595" s="4" t="s">
         <v>3195</v>
-      </c>
-      <c r="D595" s="4" t="s">
-        <v>3196</v>
       </c>
       <c r="E595" s="4" t="s">
         <v>1319</v>
       </c>
       <c r="F595" s="4" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="G595" s="3" t="s">
         <v>8</v>
@@ -33191,7 +33220,7 @@
         <v>1320</v>
       </c>
       <c r="C596" s="4" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="D596" s="4" t="s">
         <v>1321</v>
@@ -33200,7 +33229,7 @@
         <v>1322</v>
       </c>
       <c r="F596" s="4" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="G596" s="3" t="s">
         <v>8</v>
@@ -33217,19 +33246,19 @@
         <v>1323</v>
       </c>
       <c r="C597" s="4" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="D597" s="4" t="s">
         <v>1324</v>
       </c>
       <c r="E597" s="4" t="s">
+        <v>3199</v>
+      </c>
+      <c r="F597" s="4" t="s">
         <v>3200</v>
       </c>
-      <c r="F597" s="4" t="s">
+      <c r="G597" s="4" t="s">
         <v>3201</v>
-      </c>
-      <c r="G597" s="4" t="s">
-        <v>3202</v>
       </c>
       <c r="H597" s="3" t="s">
         <v>8</v>
@@ -33243,16 +33272,16 @@
         <v>1325</v>
       </c>
       <c r="C598" s="4" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="D598" s="4" t="s">
         <v>1326</v>
       </c>
       <c r="E598" s="4" t="s">
+        <v>3203</v>
+      </c>
+      <c r="F598" s="4" t="s">
         <v>3204</v>
-      </c>
-      <c r="F598" s="4" t="s">
-        <v>3205</v>
       </c>
       <c r="G598" s="3" t="s">
         <v>8</v>
@@ -33269,22 +33298,22 @@
         <v>1327</v>
       </c>
       <c r="C599" s="4" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="D599" s="4" t="s">
         <v>1326</v>
       </c>
       <c r="E599" s="4" t="s">
+        <v>3205</v>
+      </c>
+      <c r="F599" s="4" t="s">
         <v>3206</v>
       </c>
-      <c r="F599" s="4" t="s">
+      <c r="G599" s="4" t="s">
         <v>3207</v>
       </c>
-      <c r="G599" s="4" t="s">
+      <c r="H599" s="4" t="s">
         <v>3208</v>
-      </c>
-      <c r="H599" s="4" t="s">
-        <v>3209</v>
       </c>
     </row>
     <row r="600" spans="1:8" ht="40" customHeight="1">
@@ -33295,16 +33324,16 @@
         <v>1328</v>
       </c>
       <c r="C600" s="4" t="s">
+        <v>3209</v>
+      </c>
+      <c r="D600" s="4" t="s">
         <v>3210</v>
       </c>
-      <c r="D600" s="4" t="s">
+      <c r="E600" s="4" t="s">
         <v>3211</v>
       </c>
-      <c r="E600" s="4" t="s">
+      <c r="F600" s="4" t="s">
         <v>3212</v>
-      </c>
-      <c r="F600" s="4" t="s">
-        <v>3213</v>
       </c>
       <c r="G600" s="3" t="s">
         <v>8</v>
@@ -33321,16 +33350,16 @@
         <v>1329</v>
       </c>
       <c r="C601" s="4" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="D601" s="4" t="s">
         <v>1330</v>
       </c>
       <c r="E601" s="4" t="s">
+        <v>3214</v>
+      </c>
+      <c r="F601" s="4" t="s">
         <v>3215</v>
-      </c>
-      <c r="F601" s="4" t="s">
-        <v>3216</v>
       </c>
       <c r="G601" s="3" t="s">
         <v>8</v>
@@ -33347,7 +33376,7 @@
         <v>1331</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="D602" s="4" t="s">
         <v>1332</v>
@@ -33356,7 +33385,7 @@
         <v>1333</v>
       </c>
       <c r="F602" s="4" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="G602" s="4" t="s">
         <v>1334</v>
@@ -33373,19 +33402,19 @@
         <v>1335</v>
       </c>
       <c r="C603" s="4" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="D603" s="4" t="s">
         <v>1336</v>
       </c>
       <c r="E603" s="4" t="s">
+        <v>3219</v>
+      </c>
+      <c r="F603" s="4" t="s">
         <v>3220</v>
       </c>
-      <c r="F603" s="4" t="s">
+      <c r="G603" s="4" t="s">
         <v>3221</v>
-      </c>
-      <c r="G603" s="4" t="s">
-        <v>3222</v>
       </c>
       <c r="H603" s="3" t="s">
         <v>8</v>
@@ -33399,7 +33428,7 @@
         <v>1337</v>
       </c>
       <c r="C604" s="4" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="D604" s="4" t="s">
         <v>1338</v>
@@ -33425,16 +33454,16 @@
         <v>1341</v>
       </c>
       <c r="C605" s="4" t="s">
+        <v>3223</v>
+      </c>
+      <c r="D605" s="4" t="s">
         <v>3224</v>
       </c>
-      <c r="D605" s="4" t="s">
+      <c r="E605" s="4" t="s">
         <v>3225</v>
       </c>
-      <c r="E605" s="4" t="s">
+      <c r="F605" s="4" t="s">
         <v>3226</v>
-      </c>
-      <c r="F605" s="4" t="s">
-        <v>3227</v>
       </c>
       <c r="G605" s="3" t="s">
         <v>8</v>
@@ -33451,16 +33480,16 @@
         <v>1342</v>
       </c>
       <c r="C606" s="4" t="s">
+        <v>3227</v>
+      </c>
+      <c r="D606" s="4" t="s">
         <v>3228</v>
-      </c>
-      <c r="D606" s="4" t="s">
-        <v>3229</v>
       </c>
       <c r="E606" s="4" t="s">
         <v>1343</v>
       </c>
       <c r="F606" s="4" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="G606" s="4" t="s">
         <v>1344</v>
@@ -33477,7 +33506,7 @@
         <v>1345</v>
       </c>
       <c r="C607" s="4" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="D607" s="4" t="s">
         <v>1346</v>
@@ -33503,13 +33532,13 @@
         <v>1349</v>
       </c>
       <c r="C608" s="4" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="D608" s="4" t="s">
         <v>1350</v>
       </c>
       <c r="E608" s="4" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="F608" s="4" t="s">
         <v>1351</v>
@@ -33529,13 +33558,13 @@
         <v>1352</v>
       </c>
       <c r="C609" s="4" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="D609" s="4" t="s">
         <v>1353</v>
       </c>
       <c r="E609" s="4" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="F609" s="4" t="s">
         <v>1354</v>
@@ -33555,13 +33584,13 @@
         <v>1355</v>
       </c>
       <c r="C610" s="4" t="s">
+        <v>3235</v>
+      </c>
+      <c r="D610" s="4" t="s">
         <v>3236</v>
       </c>
-      <c r="D610" s="4" t="s">
+      <c r="E610" s="4" t="s">
         <v>3237</v>
-      </c>
-      <c r="E610" s="4" t="s">
-        <v>3238</v>
       </c>
       <c r="F610" s="4" t="s">
         <v>1356</v>
@@ -33581,20 +33610,20 @@
         <v>7</v>
       </c>
       <c r="C611" s="4" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D611" s="4" t="s">
         <v>3239</v>
-      </c>
-      <c r="D611" s="4" t="s">
-        <v>3240</v>
       </c>
       <c r="E611" s="3"/>
       <c r="F611" s="4" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="G611" s="4" t="s">
         <v>9</v>
       </c>
       <c r="H611" s="4" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="612" spans="1:8" ht="40" customHeight="1">
@@ -33605,7 +33634,7 @@
         <v>10</v>
       </c>
       <c r="C612" s="4" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="D612" s="4" t="s">
         <v>11</v>
@@ -33614,7 +33643,7 @@
         <v>8</v>
       </c>
       <c r="F612" s="4" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="G612" s="4" t="s">
         <v>12</v>
@@ -33631,7 +33660,7 @@
         <v>13</v>
       </c>
       <c r="C613" s="4" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="D613" s="4" t="s">
         <v>14</v>
@@ -33640,7 +33669,7 @@
         <v>8</v>
       </c>
       <c r="F613" s="4" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="G613" s="4" t="s">
         <v>9</v>
@@ -33657,7 +33686,7 @@
         <v>15</v>
       </c>
       <c r="C614" s="4" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="D614" s="4" t="s">
         <v>14</v>
@@ -33666,7 +33695,7 @@
         <v>8</v>
       </c>
       <c r="F614" s="4" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
       <c r="G614" s="4" t="s">
         <v>9</v>
@@ -33683,16 +33712,16 @@
         <v>16</v>
       </c>
       <c r="C615" s="4" t="s">
+        <v>3246</v>
+      </c>
+      <c r="D615" s="4" t="s">
         <v>3247</v>
       </c>
-      <c r="D615" s="4" t="s">
+      <c r="E615" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F615" s="4" t="s">
         <v>3248</v>
-      </c>
-      <c r="E615" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F615" s="4" t="s">
-        <v>3249</v>
       </c>
       <c r="G615" s="4" t="s">
         <v>9</v>
@@ -33709,16 +33738,16 @@
         <v>17</v>
       </c>
       <c r="C616" s="4" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="D616" s="4" t="s">
+        <v>3249</v>
+      </c>
+      <c r="E616" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F616" s="4" t="s">
         <v>3250</v>
-      </c>
-      <c r="E616" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F616" s="4" t="s">
-        <v>3251</v>
       </c>
       <c r="G616" s="4" t="s">
         <v>9</v>
@@ -33735,16 +33764,16 @@
         <v>18</v>
       </c>
       <c r="C617" s="4" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="D617" s="4" t="s">
+        <v>3251</v>
+      </c>
+      <c r="E617" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F617" s="4" t="s">
         <v>3252</v>
-      </c>
-      <c r="E617" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F617" s="4" t="s">
-        <v>3253</v>
       </c>
       <c r="G617" s="4" t="s">
         <v>9</v>
@@ -33761,16 +33790,16 @@
         <v>19</v>
       </c>
       <c r="C618" s="4" t="s">
+        <v>3253</v>
+      </c>
+      <c r="D618" s="4" t="s">
         <v>3254</v>
       </c>
-      <c r="D618" s="4" t="s">
-        <v>3255</v>
-      </c>
       <c r="E618" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F618" s="4" t="s">
-        <v>3422</v>
+        <v>3421</v>
       </c>
       <c r="G618" s="4" t="s">
         <v>9</v>
@@ -33787,19 +33816,19 @@
         <v>20</v>
       </c>
       <c r="C619" s="4" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="D619" s="4" t="s">
+        <v>3255</v>
+      </c>
+      <c r="E619" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F619" s="4" t="s">
         <v>3256</v>
       </c>
-      <c r="E619" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F619" s="4" t="s">
+      <c r="G619" s="4" t="s">
         <v>3257</v>
-      </c>
-      <c r="G619" s="4" t="s">
-        <v>3258</v>
       </c>
       <c r="H619" s="3" t="s">
         <v>8</v>
@@ -33813,16 +33842,16 @@
         <v>21</v>
       </c>
       <c r="C620" s="4" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="D620" s="4" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="E620" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F620" s="4" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="G620" s="4" t="s">
         <v>9</v>
@@ -33834,12 +33863,13 @@
   </sheetData>
   <autoFilter ref="A1:H620" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <customSheetViews>
-    <customSheetView guid="{61C7386F-07EB-4198-B2FD-4D1A7B0F335F}">
-      <pane ySplit="1" topLeftCell="A2" activePane="bottomLeft" state="frozen"/>
-      <selection pane="bottomLeft" activeCell="E4" sqref="E4"/>
+    <customSheetView guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" showAutoFilter="1">
+      <pane ySplit="3" topLeftCell="A247" activePane="bottomLeft" state="frozen"/>
+      <selection pane="bottomLeft" activeCell="C255" sqref="C255"/>
       <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
       <pageSetup paperSize="0" orientation="portrait" r:id="rId1"/>
       <headerFooter alignWithMargins="0"/>
+      <autoFilter ref="A1:H620" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
     </customSheetView>
     <customSheetView guid="{B0EC71A6-F8E8-4D42-9918-972E5566A443}" topLeftCell="B1">
       <pane ySplit="1" topLeftCell="A101" activePane="bottomLeft" state="frozen"/>
@@ -33848,13 +33878,12 @@
       <pageSetup paperSize="0" orientation="portrait" r:id="rId2"/>
       <headerFooter alignWithMargins="0"/>
     </customSheetView>
-    <customSheetView guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" showAutoFilter="1">
-      <pane ySplit="3" topLeftCell="A4" activePane="bottomLeft" state="frozen"/>
-      <selection pane="bottomLeft" activeCell="F5" sqref="F5"/>
+    <customSheetView guid="{61C7386F-07EB-4198-B2FD-4D1A7B0F335F}">
+      <pane ySplit="1" topLeftCell="A2" activePane="bottomLeft" state="frozen"/>
+      <selection pane="bottomLeft" activeCell="E4" sqref="E4"/>
       <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
       <pageSetup paperSize="0" orientation="portrait" r:id="rId3"/>
       <headerFooter alignWithMargins="0"/>
-      <autoFilter ref="A1:H620" xr:uid="{3A37A857-4445-744C-836A-3A25027DD9B4}"/>
     </customSheetView>
   </customSheetViews>
   <phoneticPr fontId="0" type="noConversion"/>
@@ -33875,7 +33904,7 @@
     <row r="1" ht="158.25" customHeight="1"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{61C7386F-07EB-4198-B2FD-4D1A7B0F335F}" state="hidden">
+    <customSheetView guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" state="hidden">
       <selection activeCell="C11" sqref="C11"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
@@ -33883,7 +33912,7 @@
       <selection activeCell="C11" sqref="C11"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
-    <customSheetView guid="{89EF2E2A-048C-1241-BCF7-95B4122206B1}" state="hidden">
+    <customSheetView guid="{61C7386F-07EB-4198-B2FD-4D1A7B0F335F}" state="hidden">
       <selection activeCell="C11" sqref="C11"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>

--- a/src/bonn_thesis/data/raw/ISCO-08 EN Structure and definitions.xlsx
+++ b/src/bonn_thesis/data/raw/ISCO-08 EN Structure and definitions.xlsx
@@ -17439,8 +17439,9 @@
 </file>
 
 <file path=xl/revisions/userNames.xml><?xml version="1.0" encoding="utf-8"?>
-<users xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" count="1">
+<users xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" count="2">
   <userInfo guid="{F8BADF6E-2CEC-0149-8604-9EC9585B97B3}" name="William Backes" id="-2128202053" dateTime="2025-12-03T00:56:22"/>
+  <userInfo guid="{2A03940B-BA22-2443-A262-D3437AAE9996}" name="William Backes" id="-2128158681" dateTime="2026-01-14T14:30:37"/>
 </users>
 </file>
 
